--- a/Test_Results/Excel/selenium-report.xlsx
+++ b/Test_Results/Excel/selenium-report.xlsx
@@ -4265,7 +4265,7 @@
         <v>10</v>
       </c>
       <c r="F2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G2" t="s">
         <v>11</v>
@@ -4288,7 +4288,7 @@
         <v>10</v>
       </c>
       <c r="F3" s="3">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>11</v>
@@ -4311,7 +4311,7 @@
         <v>10</v>
       </c>
       <c r="F4">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G4" t="s">
         <v>11</v>
@@ -4334,7 +4334,7 @@
         <v>10</v>
       </c>
       <c r="F5" s="3">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>11</v>
@@ -4357,7 +4357,7 @@
         <v>10</v>
       </c>
       <c r="F6">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G6" t="s">
         <v>11</v>
@@ -4380,7 +4380,7 @@
         <v>10</v>
       </c>
       <c r="F7" s="3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>11</v>
@@ -4403,7 +4403,7 @@
         <v>10</v>
       </c>
       <c r="F8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G8" t="s">
         <v>11</v>
@@ -4426,7 +4426,7 @@
         <v>10</v>
       </c>
       <c r="F9" s="3">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>11</v>
@@ -4449,7 +4449,7 @@
         <v>10</v>
       </c>
       <c r="F10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G10" t="s">
         <v>11</v>
@@ -4472,7 +4472,7 @@
         <v>10</v>
       </c>
       <c r="F11" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>11</v>
@@ -4495,7 +4495,7 @@
         <v>10</v>
       </c>
       <c r="F12">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G12" t="s">
         <v>11</v>
@@ -4518,7 +4518,7 @@
         <v>10</v>
       </c>
       <c r="F13" s="3">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>11</v>
@@ -4541,7 +4541,7 @@
         <v>10</v>
       </c>
       <c r="F14">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G14" t="s">
         <v>11</v>
@@ -4587,7 +4587,7 @@
         <v>10</v>
       </c>
       <c r="F16">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G16" t="s">
         <v>11</v>
@@ -4610,7 +4610,7 @@
         <v>10</v>
       </c>
       <c r="F17" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>11</v>
@@ -4633,7 +4633,7 @@
         <v>10</v>
       </c>
       <c r="F18">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G18" t="s">
         <v>11</v>
@@ -4656,7 +4656,7 @@
         <v>10</v>
       </c>
       <c r="F19" s="3">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>11</v>
@@ -4679,7 +4679,7 @@
         <v>10</v>
       </c>
       <c r="F20">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G20" t="s">
         <v>11</v>
@@ -4702,7 +4702,7 @@
         <v>10</v>
       </c>
       <c r="F21" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>11</v>
@@ -4725,7 +4725,7 @@
         <v>10</v>
       </c>
       <c r="F22">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G22" t="s">
         <v>11</v>
@@ -4748,7 +4748,7 @@
         <v>10</v>
       </c>
       <c r="F23" s="3">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>11</v>
@@ -4794,7 +4794,7 @@
         <v>10</v>
       </c>
       <c r="F25" s="3">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>11</v>
@@ -4817,7 +4817,7 @@
         <v>10</v>
       </c>
       <c r="F26">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G26" t="s">
         <v>11</v>
@@ -4840,7 +4840,7 @@
         <v>10</v>
       </c>
       <c r="F27" s="3">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>11</v>
@@ -4863,7 +4863,7 @@
         <v>10</v>
       </c>
       <c r="F28">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G28" t="s">
         <v>11</v>
@@ -4886,7 +4886,7 @@
         <v>10</v>
       </c>
       <c r="F29" s="3">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>11</v>
@@ -4932,7 +4932,7 @@
         <v>10</v>
       </c>
       <c r="F31" s="3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>11</v>
@@ -4978,7 +4978,7 @@
         <v>10</v>
       </c>
       <c r="F33" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>11</v>
@@ -5001,7 +5001,7 @@
         <v>10</v>
       </c>
       <c r="F34">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G34" t="s">
         <v>11</v>
@@ -5024,7 +5024,7 @@
         <v>10</v>
       </c>
       <c r="F35" s="3">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>11</v>
@@ -5047,7 +5047,7 @@
         <v>10</v>
       </c>
       <c r="F36">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G36" t="s">
         <v>11</v>
@@ -5070,7 +5070,7 @@
         <v>10</v>
       </c>
       <c r="F37" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>11</v>
@@ -5093,7 +5093,7 @@
         <v>10</v>
       </c>
       <c r="F38">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G38" t="s">
         <v>11</v>
@@ -5139,7 +5139,7 @@
         <v>10</v>
       </c>
       <c r="F40">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G40" t="s">
         <v>11</v>
@@ -5162,7 +5162,7 @@
         <v>10</v>
       </c>
       <c r="F41" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>11</v>
@@ -5185,7 +5185,7 @@
         <v>10</v>
       </c>
       <c r="F42">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G42" t="s">
         <v>11</v>
@@ -5208,7 +5208,7 @@
         <v>10</v>
       </c>
       <c r="F43" s="3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>11</v>
@@ -5231,7 +5231,7 @@
         <v>10</v>
       </c>
       <c r="F44">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G44" t="s">
         <v>11</v>
@@ -5254,7 +5254,7 @@
         <v>10</v>
       </c>
       <c r="F45" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>11</v>
@@ -5300,7 +5300,7 @@
         <v>10</v>
       </c>
       <c r="F47" s="3">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>11</v>
@@ -5323,7 +5323,7 @@
         <v>10</v>
       </c>
       <c r="F48">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G48" t="s">
         <v>11</v>
@@ -5346,7 +5346,7 @@
         <v>10</v>
       </c>
       <c r="F49" s="3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>11</v>
@@ -5369,7 +5369,7 @@
         <v>10</v>
       </c>
       <c r="F50">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G50" t="s">
         <v>11</v>
@@ -5392,7 +5392,7 @@
         <v>10</v>
       </c>
       <c r="F51" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>11</v>
@@ -5438,7 +5438,7 @@
         <v>10</v>
       </c>
       <c r="F53" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G53" s="3" t="s">
         <v>11</v>
@@ -5461,7 +5461,7 @@
         <v>10</v>
       </c>
       <c r="F54">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G54" t="s">
         <v>11</v>
@@ -5484,7 +5484,7 @@
         <v>10</v>
       </c>
       <c r="F55" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G55" s="3" t="s">
         <v>11</v>
@@ -5507,7 +5507,7 @@
         <v>10</v>
       </c>
       <c r="F56">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G56" t="s">
         <v>11</v>
@@ -5530,7 +5530,7 @@
         <v>10</v>
       </c>
       <c r="F57" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G57" s="3" t="s">
         <v>11</v>
@@ -5553,7 +5553,7 @@
         <v>10</v>
       </c>
       <c r="F58">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G58" t="s">
         <v>11</v>
@@ -5576,7 +5576,7 @@
         <v>10</v>
       </c>
       <c r="F59" s="3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G59" s="3" t="s">
         <v>11</v>
@@ -5599,7 +5599,7 @@
         <v>10</v>
       </c>
       <c r="F60">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G60" t="s">
         <v>11</v>
@@ -5622,7 +5622,7 @@
         <v>10</v>
       </c>
       <c r="F61" s="3">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G61" s="3" t="s">
         <v>11</v>
@@ -5645,7 +5645,7 @@
         <v>10</v>
       </c>
       <c r="F62">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G62" t="s">
         <v>11</v>
@@ -5668,7 +5668,7 @@
         <v>10</v>
       </c>
       <c r="F63" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G63" s="3" t="s">
         <v>11</v>
@@ -5691,7 +5691,7 @@
         <v>10</v>
       </c>
       <c r="F64">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G64" t="s">
         <v>11</v>
@@ -5714,7 +5714,7 @@
         <v>10</v>
       </c>
       <c r="F65" s="3">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G65" s="3" t="s">
         <v>11</v>
@@ -5737,7 +5737,7 @@
         <v>10</v>
       </c>
       <c r="F66">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G66" t="s">
         <v>11</v>
@@ -5760,7 +5760,7 @@
         <v>10</v>
       </c>
       <c r="F67" s="3">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G67" s="3" t="s">
         <v>11</v>
@@ -5783,7 +5783,7 @@
         <v>10</v>
       </c>
       <c r="F68">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G68" t="s">
         <v>11</v>
@@ -5806,7 +5806,7 @@
         <v>10</v>
       </c>
       <c r="F69" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G69" s="3" t="s">
         <v>11</v>
@@ -5829,7 +5829,7 @@
         <v>10</v>
       </c>
       <c r="F70">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G70" t="s">
         <v>11</v>
@@ -5852,7 +5852,7 @@
         <v>10</v>
       </c>
       <c r="F71" s="3">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G71" s="3" t="s">
         <v>11</v>
@@ -5875,7 +5875,7 @@
         <v>10</v>
       </c>
       <c r="F72">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G72" t="s">
         <v>11</v>
@@ -5898,7 +5898,7 @@
         <v>10</v>
       </c>
       <c r="F73" s="3">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G73" s="3" t="s">
         <v>11</v>
@@ -5921,7 +5921,7 @@
         <v>10</v>
       </c>
       <c r="F74">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G74" t="s">
         <v>11</v>
@@ -5944,7 +5944,7 @@
         <v>10</v>
       </c>
       <c r="F75" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G75" s="3" t="s">
         <v>11</v>
@@ -5967,7 +5967,7 @@
         <v>10</v>
       </c>
       <c r="F76">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G76" t="s">
         <v>11</v>
@@ -5990,7 +5990,7 @@
         <v>10</v>
       </c>
       <c r="F77" s="3">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G77" s="3" t="s">
         <v>11</v>
@@ -6013,7 +6013,7 @@
         <v>10</v>
       </c>
       <c r="F78">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G78" t="s">
         <v>11</v>
@@ -6036,7 +6036,7 @@
         <v>10</v>
       </c>
       <c r="F79" s="3">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G79" s="3" t="s">
         <v>11</v>
@@ -6059,7 +6059,7 @@
         <v>10</v>
       </c>
       <c r="F80">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G80" t="s">
         <v>11</v>
@@ -6082,7 +6082,7 @@
         <v>10</v>
       </c>
       <c r="F81" s="3">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G81" s="3" t="s">
         <v>11</v>
@@ -6105,7 +6105,7 @@
         <v>10</v>
       </c>
       <c r="F82">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G82" t="s">
         <v>11</v>
@@ -6128,7 +6128,7 @@
         <v>10</v>
       </c>
       <c r="F83" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G83" s="3" t="s">
         <v>11</v>
@@ -6151,7 +6151,7 @@
         <v>10</v>
       </c>
       <c r="F84">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G84" t="s">
         <v>11</v>
@@ -6174,7 +6174,7 @@
         <v>10</v>
       </c>
       <c r="F85" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G85" s="3" t="s">
         <v>11</v>
@@ -6197,7 +6197,7 @@
         <v>10</v>
       </c>
       <c r="F86">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G86" t="s">
         <v>11</v>
@@ -6220,7 +6220,7 @@
         <v>10</v>
       </c>
       <c r="F87" s="3">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G87" s="3" t="s">
         <v>11</v>
@@ -6243,7 +6243,7 @@
         <v>10</v>
       </c>
       <c r="F88">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G88" t="s">
         <v>11</v>
@@ -6266,7 +6266,7 @@
         <v>10</v>
       </c>
       <c r="F89" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G89" s="3" t="s">
         <v>11</v>
@@ -6289,7 +6289,7 @@
         <v>10</v>
       </c>
       <c r="F90">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G90" t="s">
         <v>11</v>
@@ -6312,7 +6312,7 @@
         <v>10</v>
       </c>
       <c r="F91" s="3">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G91" s="3" t="s">
         <v>11</v>
@@ -6335,7 +6335,7 @@
         <v>10</v>
       </c>
       <c r="F92">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G92" t="s">
         <v>11</v>
@@ -6404,7 +6404,7 @@
         <v>10</v>
       </c>
       <c r="F95" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G95" s="3" t="s">
         <v>11</v>
@@ -6427,7 +6427,7 @@
         <v>10</v>
       </c>
       <c r="F96">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G96" t="s">
         <v>11</v>
@@ -6450,7 +6450,7 @@
         <v>10</v>
       </c>
       <c r="F97" s="3">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G97" s="3" t="s">
         <v>11</v>
@@ -6473,7 +6473,7 @@
         <v>10</v>
       </c>
       <c r="F98">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G98" t="s">
         <v>11</v>
@@ -6496,7 +6496,7 @@
         <v>10</v>
       </c>
       <c r="F99" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G99" s="3" t="s">
         <v>11</v>
@@ -6519,7 +6519,7 @@
         <v>10</v>
       </c>
       <c r="F100">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G100" t="s">
         <v>11</v>
@@ -6542,7 +6542,7 @@
         <v>10</v>
       </c>
       <c r="F101" s="3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G101" s="3" t="s">
         <v>11</v>
@@ -6565,7 +6565,7 @@
         <v>10</v>
       </c>
       <c r="F102">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G102" t="s">
         <v>11</v>
@@ -6588,7 +6588,7 @@
         <v>10</v>
       </c>
       <c r="F103" s="3">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G103" s="3" t="s">
         <v>11</v>
@@ -6634,7 +6634,7 @@
         <v>10</v>
       </c>
       <c r="F105" s="3">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G105" s="3" t="s">
         <v>11</v>
@@ -6657,7 +6657,7 @@
         <v>10</v>
       </c>
       <c r="F106">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G106" t="s">
         <v>11</v>
@@ -6680,7 +6680,7 @@
         <v>10</v>
       </c>
       <c r="F107" s="3">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G107" s="3" t="s">
         <v>11</v>
@@ -6703,7 +6703,7 @@
         <v>10</v>
       </c>
       <c r="F108">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G108" t="s">
         <v>11</v>
@@ -6726,7 +6726,7 @@
         <v>10</v>
       </c>
       <c r="F109" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G109" s="3" t="s">
         <v>11</v>
@@ -6749,7 +6749,7 @@
         <v>10</v>
       </c>
       <c r="F110">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G110" t="s">
         <v>11</v>
@@ -6772,7 +6772,7 @@
         <v>10</v>
       </c>
       <c r="F111" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G111" s="3" t="s">
         <v>11</v>
@@ -6795,7 +6795,7 @@
         <v>10</v>
       </c>
       <c r="F112">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G112" t="s">
         <v>11</v>
@@ -6818,7 +6818,7 @@
         <v>10</v>
       </c>
       <c r="F113" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G113" s="3" t="s">
         <v>11</v>
@@ -6841,7 +6841,7 @@
         <v>10</v>
       </c>
       <c r="F114">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G114" t="s">
         <v>11</v>
@@ -6887,7 +6887,7 @@
         <v>10</v>
       </c>
       <c r="F116">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G116" t="s">
         <v>11</v>
@@ -6910,7 +6910,7 @@
         <v>10</v>
       </c>
       <c r="F117" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G117" s="3" t="s">
         <v>11</v>
@@ -6933,7 +6933,7 @@
         <v>10</v>
       </c>
       <c r="F118">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G118" t="s">
         <v>11</v>
@@ -6956,7 +6956,7 @@
         <v>10</v>
       </c>
       <c r="F119" s="3">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G119" s="3" t="s">
         <v>11</v>
@@ -6979,7 +6979,7 @@
         <v>10</v>
       </c>
       <c r="F120">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G120" t="s">
         <v>11</v>
@@ -7002,7 +7002,7 @@
         <v>10</v>
       </c>
       <c r="F121" s="3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G121" s="3" t="s">
         <v>11</v>
@@ -7025,7 +7025,7 @@
         <v>10</v>
       </c>
       <c r="F122">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G122" t="s">
         <v>11</v>
@@ -7048,7 +7048,7 @@
         <v>10</v>
       </c>
       <c r="F123" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G123" s="3" t="s">
         <v>11</v>
@@ -7071,7 +7071,7 @@
         <v>10</v>
       </c>
       <c r="F124">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G124" t="s">
         <v>11</v>
@@ -7094,7 +7094,7 @@
         <v>10</v>
       </c>
       <c r="F125" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G125" s="3" t="s">
         <v>11</v>
@@ -7117,7 +7117,7 @@
         <v>10</v>
       </c>
       <c r="F126">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G126" t="s">
         <v>11</v>
@@ -7163,7 +7163,7 @@
         <v>10</v>
       </c>
       <c r="F128">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G128" t="s">
         <v>11</v>
@@ -7186,7 +7186,7 @@
         <v>10</v>
       </c>
       <c r="F129" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G129" s="3" t="s">
         <v>11</v>
@@ -7209,7 +7209,7 @@
         <v>10</v>
       </c>
       <c r="F130">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G130" t="s">
         <v>11</v>
@@ -7232,7 +7232,7 @@
         <v>10</v>
       </c>
       <c r="F131" s="3">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G131" s="3" t="s">
         <v>11</v>
@@ -7255,7 +7255,7 @@
         <v>10</v>
       </c>
       <c r="F132">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G132" t="s">
         <v>11</v>
@@ -7278,7 +7278,7 @@
         <v>10</v>
       </c>
       <c r="F133" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G133" s="3" t="s">
         <v>11</v>
@@ -7301,7 +7301,7 @@
         <v>10</v>
       </c>
       <c r="F134">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G134" t="s">
         <v>11</v>
@@ -7324,7 +7324,7 @@
         <v>10</v>
       </c>
       <c r="F135" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G135" s="3" t="s">
         <v>11</v>
@@ -7347,7 +7347,7 @@
         <v>10</v>
       </c>
       <c r="F136">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G136" t="s">
         <v>11</v>
@@ -7370,7 +7370,7 @@
         <v>10</v>
       </c>
       <c r="F137" s="3">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G137" s="3" t="s">
         <v>11</v>
@@ -7393,7 +7393,7 @@
         <v>10</v>
       </c>
       <c r="F138">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G138" t="s">
         <v>11</v>
@@ -7416,7 +7416,7 @@
         <v>10</v>
       </c>
       <c r="F139" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G139" s="3" t="s">
         <v>11</v>
@@ -7462,7 +7462,7 @@
         <v>10</v>
       </c>
       <c r="F141" s="3">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G141" s="3" t="s">
         <v>11</v>
@@ -7508,7 +7508,7 @@
         <v>10</v>
       </c>
       <c r="F143" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G143" s="3" t="s">
         <v>11</v>
@@ -7531,7 +7531,7 @@
         <v>10</v>
       </c>
       <c r="F144">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G144" t="s">
         <v>11</v>
@@ -7577,7 +7577,7 @@
         <v>10</v>
       </c>
       <c r="F146">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G146" t="s">
         <v>11</v>
@@ -7623,7 +7623,7 @@
         <v>10</v>
       </c>
       <c r="F148">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G148" t="s">
         <v>11</v>
@@ -7646,7 +7646,7 @@
         <v>10</v>
       </c>
       <c r="F149" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G149" s="3" t="s">
         <v>11</v>
@@ -7669,7 +7669,7 @@
         <v>10</v>
       </c>
       <c r="F150">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G150" t="s">
         <v>11</v>
@@ -7692,7 +7692,7 @@
         <v>10</v>
       </c>
       <c r="F151" s="3">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G151" s="3" t="s">
         <v>11</v>
@@ -7715,7 +7715,7 @@
         <v>10</v>
       </c>
       <c r="F152">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G152" t="s">
         <v>11</v>
@@ -7738,7 +7738,7 @@
         <v>10</v>
       </c>
       <c r="F153" s="3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G153" s="3" t="s">
         <v>11</v>
@@ -7761,7 +7761,7 @@
         <v>10</v>
       </c>
       <c r="F154">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G154" t="s">
         <v>11</v>
@@ -7784,7 +7784,7 @@
         <v>10</v>
       </c>
       <c r="F155" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G155" s="3" t="s">
         <v>11</v>
@@ -7807,7 +7807,7 @@
         <v>10</v>
       </c>
       <c r="F156">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G156" t="s">
         <v>11</v>
@@ -7830,7 +7830,7 @@
         <v>10</v>
       </c>
       <c r="F157" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G157" s="3" t="s">
         <v>11</v>
@@ -7853,7 +7853,7 @@
         <v>10</v>
       </c>
       <c r="F158">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G158" t="s">
         <v>11</v>
@@ -7876,7 +7876,7 @@
         <v>10</v>
       </c>
       <c r="F159" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G159" s="3" t="s">
         <v>11</v>
@@ -7899,7 +7899,7 @@
         <v>10</v>
       </c>
       <c r="F160">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G160" t="s">
         <v>11</v>
@@ -7922,7 +7922,7 @@
         <v>10</v>
       </c>
       <c r="F161" s="3">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G161" s="3" t="s">
         <v>11</v>
@@ -7945,7 +7945,7 @@
         <v>10</v>
       </c>
       <c r="F162">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G162" t="s">
         <v>11</v>
@@ -7968,7 +7968,7 @@
         <v>10</v>
       </c>
       <c r="F163" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G163" s="3" t="s">
         <v>11</v>
@@ -7991,7 +7991,7 @@
         <v>10</v>
       </c>
       <c r="F164">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G164" t="s">
         <v>11</v>
@@ -8014,7 +8014,7 @@
         <v>10</v>
       </c>
       <c r="F165" s="3">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G165" s="3" t="s">
         <v>11</v>
@@ -8037,7 +8037,7 @@
         <v>10</v>
       </c>
       <c r="F166">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G166" t="s">
         <v>11</v>
@@ -8060,7 +8060,7 @@
         <v>10</v>
       </c>
       <c r="F167" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G167" s="3" t="s">
         <v>11</v>
@@ -8106,7 +8106,7 @@
         <v>10</v>
       </c>
       <c r="F169" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G169" s="3" t="s">
         <v>11</v>
@@ -8152,7 +8152,7 @@
         <v>10</v>
       </c>
       <c r="F171" s="3">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G171" s="3" t="s">
         <v>11</v>
@@ -8175,7 +8175,7 @@
         <v>10</v>
       </c>
       <c r="F172">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G172" t="s">
         <v>11</v>
@@ -8221,7 +8221,7 @@
         <v>10</v>
       </c>
       <c r="F174">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G174" t="s">
         <v>11</v>
@@ -8244,7 +8244,7 @@
         <v>10</v>
       </c>
       <c r="F175" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G175" s="3" t="s">
         <v>11</v>
@@ -8267,7 +8267,7 @@
         <v>10</v>
       </c>
       <c r="F176">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G176" t="s">
         <v>11</v>
@@ -8290,7 +8290,7 @@
         <v>10</v>
       </c>
       <c r="F177" s="3">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G177" s="3" t="s">
         <v>11</v>
@@ -8336,7 +8336,7 @@
         <v>10</v>
       </c>
       <c r="F179" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G179" s="3" t="s">
         <v>11</v>
@@ -8359,7 +8359,7 @@
         <v>10</v>
       </c>
       <c r="F180">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G180" t="s">
         <v>11</v>
@@ -8382,7 +8382,7 @@
         <v>10</v>
       </c>
       <c r="F181" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G181" s="3" t="s">
         <v>11</v>
@@ -8405,7 +8405,7 @@
         <v>10</v>
       </c>
       <c r="F182">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G182" t="s">
         <v>11</v>
@@ -8428,7 +8428,7 @@
         <v>10</v>
       </c>
       <c r="F183" s="3">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G183" s="3" t="s">
         <v>11</v>
@@ -8451,7 +8451,7 @@
         <v>10</v>
       </c>
       <c r="F184">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G184" t="s">
         <v>11</v>
@@ -8474,7 +8474,7 @@
         <v>10</v>
       </c>
       <c r="F185" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G185" s="3" t="s">
         <v>11</v>
@@ -8497,7 +8497,7 @@
         <v>10</v>
       </c>
       <c r="F186">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G186" t="s">
         <v>11</v>
@@ -8520,7 +8520,7 @@
         <v>10</v>
       </c>
       <c r="F187" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G187" s="3" t="s">
         <v>11</v>
@@ -8543,7 +8543,7 @@
         <v>10</v>
       </c>
       <c r="F188">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G188" t="s">
         <v>11</v>
@@ -8566,7 +8566,7 @@
         <v>10</v>
       </c>
       <c r="F189" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G189" s="3" t="s">
         <v>11</v>
@@ -8589,7 +8589,7 @@
         <v>10</v>
       </c>
       <c r="F190">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G190" t="s">
         <v>11</v>
@@ -8612,7 +8612,7 @@
         <v>10</v>
       </c>
       <c r="F191" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G191" s="3" t="s">
         <v>11</v>
@@ -8658,7 +8658,7 @@
         <v>10</v>
       </c>
       <c r="F193" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G193" s="3" t="s">
         <v>11</v>
@@ -8681,7 +8681,7 @@
         <v>10</v>
       </c>
       <c r="F194">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G194" t="s">
         <v>11</v>
@@ -8704,7 +8704,7 @@
         <v>10</v>
       </c>
       <c r="F195" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G195" s="3" t="s">
         <v>11</v>
@@ -8727,7 +8727,7 @@
         <v>10</v>
       </c>
       <c r="F196">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G196" t="s">
         <v>11</v>
@@ -8750,7 +8750,7 @@
         <v>10</v>
       </c>
       <c r="F197" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G197" s="3" t="s">
         <v>11</v>
@@ -8773,7 +8773,7 @@
         <v>10</v>
       </c>
       <c r="F198">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G198" t="s">
         <v>11</v>
@@ -8796,7 +8796,7 @@
         <v>10</v>
       </c>
       <c r="F199" s="3">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G199" s="3" t="s">
         <v>11</v>
@@ -8819,7 +8819,7 @@
         <v>10</v>
       </c>
       <c r="F200">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G200" t="s">
         <v>11</v>
@@ -8842,7 +8842,7 @@
         <v>10</v>
       </c>
       <c r="F201" s="3">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G201" s="3" t="s">
         <v>11</v>
@@ -8865,7 +8865,7 @@
         <v>10</v>
       </c>
       <c r="F202">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G202" t="s">
         <v>11</v>
@@ -8888,7 +8888,7 @@
         <v>10</v>
       </c>
       <c r="F203" s="3">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G203" s="3" t="s">
         <v>11</v>
@@ -8934,7 +8934,7 @@
         <v>10</v>
       </c>
       <c r="F205" s="3">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G205" s="3" t="s">
         <v>11</v>
@@ -8980,7 +8980,7 @@
         <v>10</v>
       </c>
       <c r="F207" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G207" s="3" t="s">
         <v>11</v>
@@ -9003,7 +9003,7 @@
         <v>10</v>
       </c>
       <c r="F208">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G208" t="s">
         <v>11</v>
@@ -9026,7 +9026,7 @@
         <v>10</v>
       </c>
       <c r="F209" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G209" s="3" t="s">
         <v>11</v>
@@ -9049,7 +9049,7 @@
         <v>10</v>
       </c>
       <c r="F210">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G210" t="s">
         <v>11</v>
@@ -9072,7 +9072,7 @@
         <v>10</v>
       </c>
       <c r="F211" s="3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G211" s="3" t="s">
         <v>11</v>
@@ -9095,7 +9095,7 @@
         <v>10</v>
       </c>
       <c r="F212">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G212" t="s">
         <v>11</v>
@@ -9118,7 +9118,7 @@
         <v>10</v>
       </c>
       <c r="F213" s="3">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G213" s="3" t="s">
         <v>11</v>
@@ -9141,7 +9141,7 @@
         <v>10</v>
       </c>
       <c r="F214">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G214" t="s">
         <v>11</v>
@@ -9164,7 +9164,7 @@
         <v>10</v>
       </c>
       <c r="F215" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G215" s="3" t="s">
         <v>11</v>
@@ -9187,7 +9187,7 @@
         <v>10</v>
       </c>
       <c r="F216">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G216" t="s">
         <v>11</v>
@@ -9210,7 +9210,7 @@
         <v>10</v>
       </c>
       <c r="F217" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G217" s="3" t="s">
         <v>11</v>
@@ -9279,7 +9279,7 @@
         <v>10</v>
       </c>
       <c r="F220">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G220" t="s">
         <v>11</v>
@@ -9302,7 +9302,7 @@
         <v>10</v>
       </c>
       <c r="F221" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G221" s="3" t="s">
         <v>11</v>
@@ -9325,7 +9325,7 @@
         <v>10</v>
       </c>
       <c r="F222">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G222" t="s">
         <v>11</v>
@@ -9348,7 +9348,7 @@
         <v>10</v>
       </c>
       <c r="F223" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G223" s="3" t="s">
         <v>11</v>
@@ -9371,7 +9371,7 @@
         <v>10</v>
       </c>
       <c r="F224">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G224" t="s">
         <v>11</v>
@@ -9394,7 +9394,7 @@
         <v>10</v>
       </c>
       <c r="F225" s="3">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G225" s="3" t="s">
         <v>11</v>
@@ -9417,7 +9417,7 @@
         <v>10</v>
       </c>
       <c r="F226">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G226" t="s">
         <v>11</v>
@@ -9440,7 +9440,7 @@
         <v>10</v>
       </c>
       <c r="F227" s="3">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G227" s="3" t="s">
         <v>11</v>
@@ -9463,7 +9463,7 @@
         <v>10</v>
       </c>
       <c r="F228">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G228" t="s">
         <v>11</v>
@@ -9486,7 +9486,7 @@
         <v>10</v>
       </c>
       <c r="F229" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G229" s="3" t="s">
         <v>11</v>
@@ -9509,7 +9509,7 @@
         <v>10</v>
       </c>
       <c r="F230">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G230" t="s">
         <v>11</v>
@@ -9532,7 +9532,7 @@
         <v>10</v>
       </c>
       <c r="F231" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G231" s="3" t="s">
         <v>11</v>
@@ -9555,7 +9555,7 @@
         <v>10</v>
       </c>
       <c r="F232">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G232" t="s">
         <v>11</v>
@@ -9578,7 +9578,7 @@
         <v>10</v>
       </c>
       <c r="F233" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G233" s="3" t="s">
         <v>11</v>
@@ -9624,7 +9624,7 @@
         <v>10</v>
       </c>
       <c r="F235" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G235" s="3" t="s">
         <v>11</v>
@@ -9647,7 +9647,7 @@
         <v>10</v>
       </c>
       <c r="F236">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G236" t="s">
         <v>11</v>
@@ -9670,7 +9670,7 @@
         <v>10</v>
       </c>
       <c r="F237" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G237" s="3" t="s">
         <v>11</v>
@@ -9716,7 +9716,7 @@
         <v>10</v>
       </c>
       <c r="F239" s="3">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G239" s="3" t="s">
         <v>11</v>
@@ -9739,7 +9739,7 @@
         <v>10</v>
       </c>
       <c r="F240">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G240" t="s">
         <v>11</v>
@@ -9785,7 +9785,7 @@
         <v>10</v>
       </c>
       <c r="F242">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G242" t="s">
         <v>11</v>
@@ -9831,7 +9831,7 @@
         <v>10</v>
       </c>
       <c r="F244">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G244" t="s">
         <v>11</v>
@@ -9854,7 +9854,7 @@
         <v>10</v>
       </c>
       <c r="F245" s="3">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G245" s="3" t="s">
         <v>11</v>
@@ -9877,7 +9877,7 @@
         <v>10</v>
       </c>
       <c r="F246">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G246" t="s">
         <v>11</v>
@@ -9900,7 +9900,7 @@
         <v>10</v>
       </c>
       <c r="F247" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G247" s="3" t="s">
         <v>11</v>
@@ -9923,7 +9923,7 @@
         <v>10</v>
       </c>
       <c r="F248">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G248" t="s">
         <v>11</v>
@@ -9946,7 +9946,7 @@
         <v>10</v>
       </c>
       <c r="F249" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G249" s="3" t="s">
         <v>11</v>
@@ -9969,7 +9969,7 @@
         <v>10</v>
       </c>
       <c r="F250">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G250" t="s">
         <v>11</v>
@@ -9992,7 +9992,7 @@
         <v>10</v>
       </c>
       <c r="F251" s="3">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G251" s="3" t="s">
         <v>11</v>
@@ -10015,7 +10015,7 @@
         <v>10</v>
       </c>
       <c r="F252">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G252" t="s">
         <v>11</v>
@@ -10038,7 +10038,7 @@
         <v>10</v>
       </c>
       <c r="F253" s="3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G253" s="3" t="s">
         <v>11</v>
@@ -10061,7 +10061,7 @@
         <v>10</v>
       </c>
       <c r="F254">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G254" t="s">
         <v>11</v>
@@ -10084,7 +10084,7 @@
         <v>10</v>
       </c>
       <c r="F255" s="3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G255" s="3" t="s">
         <v>11</v>
@@ -10107,7 +10107,7 @@
         <v>10</v>
       </c>
       <c r="F256">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G256" t="s">
         <v>11</v>
@@ -10130,7 +10130,7 @@
         <v>10</v>
       </c>
       <c r="F257" s="3">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G257" s="3" t="s">
         <v>11</v>
@@ -10153,7 +10153,7 @@
         <v>10</v>
       </c>
       <c r="F258">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G258" t="s">
         <v>11</v>
@@ -10176,7 +10176,7 @@
         <v>10</v>
       </c>
       <c r="F259" s="3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G259" s="3" t="s">
         <v>11</v>
@@ -10222,7 +10222,7 @@
         <v>10</v>
       </c>
       <c r="F261" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G261" s="3" t="s">
         <v>11</v>
@@ -10245,7 +10245,7 @@
         <v>10</v>
       </c>
       <c r="F262">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G262" t="s">
         <v>11</v>
@@ -10268,7 +10268,7 @@
         <v>10</v>
       </c>
       <c r="F263" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G263" s="3" t="s">
         <v>11</v>
@@ -10291,7 +10291,7 @@
         <v>10</v>
       </c>
       <c r="F264">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G264" t="s">
         <v>11</v>
@@ -10314,7 +10314,7 @@
         <v>10</v>
       </c>
       <c r="F265" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G265" s="3" t="s">
         <v>11</v>
@@ -10337,7 +10337,7 @@
         <v>10</v>
       </c>
       <c r="F266">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G266" t="s">
         <v>11</v>
@@ -10360,7 +10360,7 @@
         <v>10</v>
       </c>
       <c r="F267" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G267" s="3" t="s">
         <v>11</v>
@@ -10383,7 +10383,7 @@
         <v>10</v>
       </c>
       <c r="F268">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G268" t="s">
         <v>11</v>
@@ -10406,7 +10406,7 @@
         <v>10</v>
       </c>
       <c r="F269" s="3">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G269" s="3" t="s">
         <v>11</v>
@@ -10452,7 +10452,7 @@
         <v>10</v>
       </c>
       <c r="F271" s="3">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G271" s="3" t="s">
         <v>11</v>
@@ -10475,7 +10475,7 @@
         <v>10</v>
       </c>
       <c r="F272">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G272" t="s">
         <v>11</v>
@@ -10521,7 +10521,7 @@
         <v>10</v>
       </c>
       <c r="F274">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G274" t="s">
         <v>11</v>
@@ -10544,7 +10544,7 @@
         <v>10</v>
       </c>
       <c r="F275" s="3">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G275" s="3" t="s">
         <v>11</v>
@@ -10567,7 +10567,7 @@
         <v>10</v>
       </c>
       <c r="F276">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G276" t="s">
         <v>11</v>
@@ -10590,7 +10590,7 @@
         <v>10</v>
       </c>
       <c r="F277" s="3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G277" s="3" t="s">
         <v>11</v>
@@ -10613,7 +10613,7 @@
         <v>10</v>
       </c>
       <c r="F278">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G278" t="s">
         <v>11</v>
@@ -10636,7 +10636,7 @@
         <v>10</v>
       </c>
       <c r="F279" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G279" s="3" t="s">
         <v>11</v>
@@ -10659,7 +10659,7 @@
         <v>10</v>
       </c>
       <c r="F280">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G280" t="s">
         <v>11</v>
@@ -10682,7 +10682,7 @@
         <v>10</v>
       </c>
       <c r="F281" s="3">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G281" s="3" t="s">
         <v>11</v>
@@ -10705,7 +10705,7 @@
         <v>10</v>
       </c>
       <c r="F282">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G282" t="s">
         <v>11</v>
@@ -10728,7 +10728,7 @@
         <v>10</v>
       </c>
       <c r="F283" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G283" s="3" t="s">
         <v>11</v>
@@ -10751,7 +10751,7 @@
         <v>10</v>
       </c>
       <c r="F284">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G284" t="s">
         <v>11</v>
@@ -10774,7 +10774,7 @@
         <v>10</v>
       </c>
       <c r="F285" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G285" s="3" t="s">
         <v>11</v>
@@ -10797,7 +10797,7 @@
         <v>10</v>
       </c>
       <c r="F286">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G286" t="s">
         <v>11</v>
@@ -10843,7 +10843,7 @@
         <v>10</v>
       </c>
       <c r="F288">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G288" t="s">
         <v>11</v>
@@ -10866,7 +10866,7 @@
         <v>10</v>
       </c>
       <c r="F289" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G289" s="3" t="s">
         <v>11</v>
@@ -10889,7 +10889,7 @@
         <v>10</v>
       </c>
       <c r="F290">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G290" t="s">
         <v>11</v>
@@ -10912,7 +10912,7 @@
         <v>10</v>
       </c>
       <c r="F291" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G291" s="3" t="s">
         <v>11</v>
@@ -10935,7 +10935,7 @@
         <v>10</v>
       </c>
       <c r="F292">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G292" t="s">
         <v>11</v>
@@ -10958,7 +10958,7 @@
         <v>10</v>
       </c>
       <c r="F293" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G293" s="3" t="s">
         <v>11</v>
@@ -10981,7 +10981,7 @@
         <v>10</v>
       </c>
       <c r="F294">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G294" t="s">
         <v>11</v>
@@ -11004,7 +11004,7 @@
         <v>10</v>
       </c>
       <c r="F295" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G295" s="3" t="s">
         <v>11</v>
@@ -11050,7 +11050,7 @@
         <v>10</v>
       </c>
       <c r="F297" s="3">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G297" s="3" t="s">
         <v>11</v>
@@ -11073,7 +11073,7 @@
         <v>10</v>
       </c>
       <c r="F298">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G298" t="s">
         <v>11</v>
@@ -11142,7 +11142,7 @@
         <v>10</v>
       </c>
       <c r="F301" s="3">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G301" s="3" t="s">
         <v>11</v>
@@ -11165,7 +11165,7 @@
         <v>10</v>
       </c>
       <c r="F302">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G302" t="s">
         <v>11</v>
@@ -11188,7 +11188,7 @@
         <v>10</v>
       </c>
       <c r="F303" s="3">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G303" s="3" t="s">
         <v>11</v>
@@ -11211,7 +11211,7 @@
         <v>10</v>
       </c>
       <c r="F304">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G304" t="s">
         <v>11</v>
@@ -11234,7 +11234,7 @@
         <v>10</v>
       </c>
       <c r="F305" s="3">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G305" s="3" t="s">
         <v>11</v>
@@ -11257,7 +11257,7 @@
         <v>10</v>
       </c>
       <c r="F306">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G306" t="s">
         <v>11</v>
@@ -11326,7 +11326,7 @@
         <v>10</v>
       </c>
       <c r="F309" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G309" s="3" t="s">
         <v>11</v>
@@ -11349,7 +11349,7 @@
         <v>10</v>
       </c>
       <c r="F310">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G310" t="s">
         <v>11</v>
@@ -11372,7 +11372,7 @@
         <v>10</v>
       </c>
       <c r="F311" s="3">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G311" s="3" t="s">
         <v>11</v>
@@ -11395,7 +11395,7 @@
         <v>10</v>
       </c>
       <c r="F312">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G312" t="s">
         <v>11</v>
@@ -11418,7 +11418,7 @@
         <v>10</v>
       </c>
       <c r="F313" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G313" s="3" t="s">
         <v>11</v>
@@ -11441,7 +11441,7 @@
         <v>10</v>
       </c>
       <c r="F314">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G314" t="s">
         <v>11</v>
@@ -11464,7 +11464,7 @@
         <v>10</v>
       </c>
       <c r="F315" s="3">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G315" s="3" t="s">
         <v>11</v>
@@ -11487,7 +11487,7 @@
         <v>10</v>
       </c>
       <c r="F316">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G316" t="s">
         <v>11</v>
@@ -11510,7 +11510,7 @@
         <v>10</v>
       </c>
       <c r="F317" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G317" s="3" t="s">
         <v>11</v>
@@ -11533,7 +11533,7 @@
         <v>10</v>
       </c>
       <c r="F318">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G318" t="s">
         <v>11</v>
@@ -11556,7 +11556,7 @@
         <v>10</v>
       </c>
       <c r="F319" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G319" s="3" t="s">
         <v>11</v>
@@ -11579,7 +11579,7 @@
         <v>10</v>
       </c>
       <c r="F320">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G320" t="s">
         <v>11</v>
@@ -11602,7 +11602,7 @@
         <v>10</v>
       </c>
       <c r="F321" s="3">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G321" s="3" t="s">
         <v>11</v>
@@ -11648,7 +11648,7 @@
         <v>10</v>
       </c>
       <c r="F323" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G323" s="3" t="s">
         <v>11</v>
@@ -11694,7 +11694,7 @@
         <v>10</v>
       </c>
       <c r="F325" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G325" s="3" t="s">
         <v>11</v>
@@ -11717,7 +11717,7 @@
         <v>10</v>
       </c>
       <c r="F326">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G326" t="s">
         <v>11</v>
@@ -11740,7 +11740,7 @@
         <v>10</v>
       </c>
       <c r="F327" s="3">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G327" s="3" t="s">
         <v>11</v>
@@ -11763,7 +11763,7 @@
         <v>10</v>
       </c>
       <c r="F328">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G328" t="s">
         <v>11</v>
@@ -11786,7 +11786,7 @@
         <v>10</v>
       </c>
       <c r="F329" s="3">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G329" s="3" t="s">
         <v>11</v>
@@ -11809,7 +11809,7 @@
         <v>10</v>
       </c>
       <c r="F330">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G330" t="s">
         <v>11</v>
@@ -11832,7 +11832,7 @@
         <v>10</v>
       </c>
       <c r="F331" s="3">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G331" s="3" t="s">
         <v>11</v>
@@ -11855,7 +11855,7 @@
         <v>10</v>
       </c>
       <c r="F332">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G332" t="s">
         <v>11</v>
@@ -11878,7 +11878,7 @@
         <v>10</v>
       </c>
       <c r="F333" s="3">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G333" s="3" t="s">
         <v>11</v>
@@ -11901,7 +11901,7 @@
         <v>10</v>
       </c>
       <c r="F334">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G334" t="s">
         <v>11</v>
@@ -11924,7 +11924,7 @@
         <v>10</v>
       </c>
       <c r="F335" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G335" s="3" t="s">
         <v>11</v>
@@ -11970,7 +11970,7 @@
         <v>10</v>
       </c>
       <c r="F337" s="3">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G337" s="3" t="s">
         <v>11</v>
@@ -11993,7 +11993,7 @@
         <v>10</v>
       </c>
       <c r="F338">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G338" t="s">
         <v>11</v>
@@ -12016,7 +12016,7 @@
         <v>10</v>
       </c>
       <c r="F339" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G339" s="3" t="s">
         <v>11</v>
@@ -12062,7 +12062,7 @@
         <v>10</v>
       </c>
       <c r="F341" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G341" s="3" t="s">
         <v>11</v>
@@ -12085,7 +12085,7 @@
         <v>10</v>
       </c>
       <c r="F342">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G342" t="s">
         <v>11</v>
@@ -12108,7 +12108,7 @@
         <v>10</v>
       </c>
       <c r="F343" s="3">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G343" s="3" t="s">
         <v>11</v>
@@ -12131,7 +12131,7 @@
         <v>10</v>
       </c>
       <c r="F344">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G344" t="s">
         <v>11</v>
@@ -12177,7 +12177,7 @@
         <v>10</v>
       </c>
       <c r="F346">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G346" t="s">
         <v>11</v>
@@ -12200,7 +12200,7 @@
         <v>10</v>
       </c>
       <c r="F347" s="3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G347" s="3" t="s">
         <v>11</v>
@@ -12246,7 +12246,7 @@
         <v>10</v>
       </c>
       <c r="F349" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G349" s="3" t="s">
         <v>11</v>
@@ -12269,7 +12269,7 @@
         <v>10</v>
       </c>
       <c r="F350">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G350" t="s">
         <v>11</v>
@@ -12292,7 +12292,7 @@
         <v>10</v>
       </c>
       <c r="F351" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G351" s="3" t="s">
         <v>11</v>
@@ -12315,7 +12315,7 @@
         <v>10</v>
       </c>
       <c r="F352">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G352" t="s">
         <v>11</v>
@@ -12338,7 +12338,7 @@
         <v>10</v>
       </c>
       <c r="F353" s="3">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G353" s="3" t="s">
         <v>11</v>
@@ -12361,7 +12361,7 @@
         <v>10</v>
       </c>
       <c r="F354">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G354" t="s">
         <v>11</v>
@@ -12407,7 +12407,7 @@
         <v>10</v>
       </c>
       <c r="F356">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G356" t="s">
         <v>11</v>
@@ -12430,7 +12430,7 @@
         <v>10</v>
       </c>
       <c r="F357" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G357" s="3" t="s">
         <v>11</v>
@@ -12453,7 +12453,7 @@
         <v>10</v>
       </c>
       <c r="F358">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G358" t="s">
         <v>11</v>
@@ -12476,7 +12476,7 @@
         <v>10</v>
       </c>
       <c r="F359" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G359" s="3" t="s">
         <v>11</v>
@@ -12499,7 +12499,7 @@
         <v>10</v>
       </c>
       <c r="F360">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G360" t="s">
         <v>11</v>
@@ -12522,7 +12522,7 @@
         <v>10</v>
       </c>
       <c r="F361" s="3">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G361" s="3" t="s">
         <v>11</v>
@@ -12568,7 +12568,7 @@
         <v>10</v>
       </c>
       <c r="F363" s="3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G363" s="3" t="s">
         <v>11</v>
@@ -12591,7 +12591,7 @@
         <v>10</v>
       </c>
       <c r="F364">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G364" t="s">
         <v>11</v>
@@ -12614,7 +12614,7 @@
         <v>10</v>
       </c>
       <c r="F365" s="3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G365" s="3" t="s">
         <v>11</v>
@@ -12637,7 +12637,7 @@
         <v>10</v>
       </c>
       <c r="F366">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G366" t="s">
         <v>11</v>
@@ -12660,7 +12660,7 @@
         <v>10</v>
       </c>
       <c r="F367" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G367" s="3" t="s">
         <v>11</v>
@@ -12683,7 +12683,7 @@
         <v>10</v>
       </c>
       <c r="F368">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G368" t="s">
         <v>11</v>
@@ -12706,7 +12706,7 @@
         <v>10</v>
       </c>
       <c r="F369" s="3">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G369" s="3" t="s">
         <v>11</v>
@@ -12729,7 +12729,7 @@
         <v>10</v>
       </c>
       <c r="F370">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G370" t="s">
         <v>11</v>
@@ -12752,7 +12752,7 @@
         <v>10</v>
       </c>
       <c r="F371" s="3">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G371" s="3" t="s">
         <v>11</v>
@@ -12775,7 +12775,7 @@
         <v>10</v>
       </c>
       <c r="F372">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G372" t="s">
         <v>11</v>
@@ -12798,7 +12798,7 @@
         <v>10</v>
       </c>
       <c r="F373" s="3">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G373" s="3" t="s">
         <v>11</v>
@@ -12821,7 +12821,7 @@
         <v>10</v>
       </c>
       <c r="F374">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G374" t="s">
         <v>11</v>
@@ -12844,7 +12844,7 @@
         <v>10</v>
       </c>
       <c r="F375" s="3">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G375" s="3" t="s">
         <v>11</v>
@@ -12867,7 +12867,7 @@
         <v>10</v>
       </c>
       <c r="F376">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G376" t="s">
         <v>11</v>
@@ -12890,7 +12890,7 @@
         <v>10</v>
       </c>
       <c r="F377" s="3">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G377" s="3" t="s">
         <v>11</v>
@@ -12913,7 +12913,7 @@
         <v>10</v>
       </c>
       <c r="F378">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G378" t="s">
         <v>11</v>
@@ -12936,7 +12936,7 @@
         <v>10</v>
       </c>
       <c r="F379" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G379" s="3" t="s">
         <v>11</v>
@@ -12959,7 +12959,7 @@
         <v>10</v>
       </c>
       <c r="F380">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G380" t="s">
         <v>11</v>
@@ -12982,7 +12982,7 @@
         <v>10</v>
       </c>
       <c r="F381" s="3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G381" s="3" t="s">
         <v>11</v>
@@ -13005,7 +13005,7 @@
         <v>10</v>
       </c>
       <c r="F382">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G382" t="s">
         <v>11</v>
@@ -13051,7 +13051,7 @@
         <v>10</v>
       </c>
       <c r="F384">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G384" t="s">
         <v>11</v>
@@ -13074,7 +13074,7 @@
         <v>10</v>
       </c>
       <c r="F385" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G385" s="3" t="s">
         <v>11</v>
@@ -13097,7 +13097,7 @@
         <v>10</v>
       </c>
       <c r="F386">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G386" t="s">
         <v>11</v>
@@ -13120,7 +13120,7 @@
         <v>10</v>
       </c>
       <c r="F387" s="3">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G387" s="3" t="s">
         <v>11</v>
@@ -13143,7 +13143,7 @@
         <v>10</v>
       </c>
       <c r="F388">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G388" t="s">
         <v>11</v>
@@ -13166,7 +13166,7 @@
         <v>10</v>
       </c>
       <c r="F389" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G389" s="3" t="s">
         <v>11</v>
@@ -13189,7 +13189,7 @@
         <v>10</v>
       </c>
       <c r="F390">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G390" t="s">
         <v>11</v>
@@ -13212,7 +13212,7 @@
         <v>10</v>
       </c>
       <c r="F391" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G391" s="3" t="s">
         <v>11</v>
@@ -13235,7 +13235,7 @@
         <v>10</v>
       </c>
       <c r="F392">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G392" t="s">
         <v>11</v>
@@ -13258,7 +13258,7 @@
         <v>10</v>
       </c>
       <c r="F393" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G393" s="3" t="s">
         <v>11</v>
@@ -13281,7 +13281,7 @@
         <v>10</v>
       </c>
       <c r="F394">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G394" t="s">
         <v>11</v>
@@ -13327,7 +13327,7 @@
         <v>10</v>
       </c>
       <c r="F396">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G396" t="s">
         <v>11</v>
@@ -13350,7 +13350,7 @@
         <v>10</v>
       </c>
       <c r="F397" s="3">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G397" s="3" t="s">
         <v>11</v>
@@ -13373,7 +13373,7 @@
         <v>10</v>
       </c>
       <c r="F398">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G398" t="s">
         <v>11</v>
@@ -13396,7 +13396,7 @@
         <v>10</v>
       </c>
       <c r="F399" s="3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G399" s="3" t="s">
         <v>11</v>
@@ -13419,7 +13419,7 @@
         <v>10</v>
       </c>
       <c r="F400">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G400" t="s">
         <v>11</v>
@@ -13442,7 +13442,7 @@
         <v>10</v>
       </c>
       <c r="F401" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G401" s="3" t="s">
         <v>11</v>
@@ -13465,7 +13465,7 @@
         <v>10</v>
       </c>
       <c r="F402">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G402" t="s">
         <v>11</v>
@@ -13488,7 +13488,7 @@
         <v>10</v>
       </c>
       <c r="F403" s="3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G403" s="3" t="s">
         <v>11</v>
@@ -13511,7 +13511,7 @@
         <v>10</v>
       </c>
       <c r="F404">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G404" t="s">
         <v>11</v>
@@ -13534,7 +13534,7 @@
         <v>10</v>
       </c>
       <c r="F405" s="3">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G405" s="3" t="s">
         <v>11</v>
@@ -13557,7 +13557,7 @@
         <v>10</v>
       </c>
       <c r="F406">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G406" t="s">
         <v>11</v>
@@ -13580,7 +13580,7 @@
         <v>10</v>
       </c>
       <c r="F407" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G407" s="3" t="s">
         <v>11</v>
@@ -13603,7 +13603,7 @@
         <v>10</v>
       </c>
       <c r="F408">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G408" t="s">
         <v>11</v>
@@ -13626,7 +13626,7 @@
         <v>10</v>
       </c>
       <c r="F409" s="3">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G409" s="3" t="s">
         <v>11</v>
@@ -13672,7 +13672,7 @@
         <v>10</v>
       </c>
       <c r="F411" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G411" s="3" t="s">
         <v>11</v>
@@ -13695,7 +13695,7 @@
         <v>10</v>
       </c>
       <c r="F412">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G412" t="s">
         <v>11</v>
@@ -13718,7 +13718,7 @@
         <v>10</v>
       </c>
       <c r="F413" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G413" s="3" t="s">
         <v>11</v>
@@ -13741,7 +13741,7 @@
         <v>10</v>
       </c>
       <c r="F414">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G414" t="s">
         <v>11</v>
@@ -13764,7 +13764,7 @@
         <v>10</v>
       </c>
       <c r="F415" s="3">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G415" s="3" t="s">
         <v>11</v>
@@ -13810,7 +13810,7 @@
         <v>10</v>
       </c>
       <c r="F417" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G417" s="3" t="s">
         <v>11</v>
@@ -13833,7 +13833,7 @@
         <v>10</v>
       </c>
       <c r="F418">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G418" t="s">
         <v>11</v>
@@ -13879,7 +13879,7 @@
         <v>10</v>
       </c>
       <c r="F420">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G420" t="s">
         <v>11</v>
@@ -13902,7 +13902,7 @@
         <v>10</v>
       </c>
       <c r="F421" s="3">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G421" s="3" t="s">
         <v>11</v>
@@ -13925,7 +13925,7 @@
         <v>10</v>
       </c>
       <c r="F422">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G422" t="s">
         <v>11</v>
@@ -13948,7 +13948,7 @@
         <v>10</v>
       </c>
       <c r="F423" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G423" s="3" t="s">
         <v>11</v>
@@ -13971,7 +13971,7 @@
         <v>10</v>
       </c>
       <c r="F424">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G424" t="s">
         <v>11</v>
@@ -13994,7 +13994,7 @@
         <v>10</v>
       </c>
       <c r="F425" s="3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G425" s="3" t="s">
         <v>11</v>
@@ -14017,7 +14017,7 @@
         <v>10</v>
       </c>
       <c r="F426">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G426" t="s">
         <v>11</v>
@@ -14040,7 +14040,7 @@
         <v>10</v>
       </c>
       <c r="F427" s="3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G427" s="3" t="s">
         <v>11</v>
@@ -14063,7 +14063,7 @@
         <v>10</v>
       </c>
       <c r="F428">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G428" t="s">
         <v>11</v>
@@ -14086,7 +14086,7 @@
         <v>10</v>
       </c>
       <c r="F429" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G429" s="3" t="s">
         <v>11</v>
@@ -14109,7 +14109,7 @@
         <v>10</v>
       </c>
       <c r="F430">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G430" t="s">
         <v>11</v>
@@ -14132,7 +14132,7 @@
         <v>10</v>
       </c>
       <c r="F431" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G431" s="3" t="s">
         <v>11</v>
@@ -14178,7 +14178,7 @@
         <v>10</v>
       </c>
       <c r="F433" s="3">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G433" s="3" t="s">
         <v>11</v>
@@ -14201,7 +14201,7 @@
         <v>10</v>
       </c>
       <c r="F434">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G434" t="s">
         <v>11</v>
@@ -14224,7 +14224,7 @@
         <v>10</v>
       </c>
       <c r="F435" s="3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G435" s="3" t="s">
         <v>11</v>
@@ -14270,7 +14270,7 @@
         <v>10</v>
       </c>
       <c r="F437" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G437" s="3" t="s">
         <v>11</v>
@@ -14293,7 +14293,7 @@
         <v>10</v>
       </c>
       <c r="F438">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G438" t="s">
         <v>11</v>
@@ -14316,7 +14316,7 @@
         <v>10</v>
       </c>
       <c r="F439" s="3">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G439" s="3" t="s">
         <v>11</v>
@@ -14339,7 +14339,7 @@
         <v>10</v>
       </c>
       <c r="F440">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G440" t="s">
         <v>11</v>
@@ -14362,7 +14362,7 @@
         <v>10</v>
       </c>
       <c r="F441" s="3">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G441" s="3" t="s">
         <v>11</v>
@@ -14385,7 +14385,7 @@
         <v>10</v>
       </c>
       <c r="F442">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G442" t="s">
         <v>11</v>
@@ -14431,7 +14431,7 @@
         <v>10</v>
       </c>
       <c r="F444">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G444" t="s">
         <v>11</v>
@@ -14454,7 +14454,7 @@
         <v>10</v>
       </c>
       <c r="F445" s="3">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G445" s="3" t="s">
         <v>11</v>
@@ -14477,7 +14477,7 @@
         <v>10</v>
       </c>
       <c r="F446">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G446" t="s">
         <v>11</v>
@@ -14546,7 +14546,7 @@
         <v>10</v>
       </c>
       <c r="F449" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G449" s="3" t="s">
         <v>11</v>
@@ -14569,7 +14569,7 @@
         <v>10</v>
       </c>
       <c r="F450">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G450" t="s">
         <v>11</v>
@@ -14592,7 +14592,7 @@
         <v>10</v>
       </c>
       <c r="F451" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G451" s="3" t="s">
         <v>11</v>
@@ -14615,7 +14615,7 @@
         <v>10</v>
       </c>
       <c r="F452">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G452" t="s">
         <v>11</v>
@@ -14638,7 +14638,7 @@
         <v>10</v>
       </c>
       <c r="F453" s="3">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G453" s="3" t="s">
         <v>11</v>
@@ -14684,7 +14684,7 @@
         <v>10</v>
       </c>
       <c r="F455" s="3">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G455" s="3" t="s">
         <v>11</v>
@@ -14730,7 +14730,7 @@
         <v>10</v>
       </c>
       <c r="F457" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G457" s="3" t="s">
         <v>11</v>
@@ -14753,7 +14753,7 @@
         <v>10</v>
       </c>
       <c r="F458">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G458" t="s">
         <v>11</v>
@@ -14776,7 +14776,7 @@
         <v>10</v>
       </c>
       <c r="F459" s="3">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G459" s="3" t="s">
         <v>11</v>
@@ -14799,7 +14799,7 @@
         <v>10</v>
       </c>
       <c r="F460">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G460" t="s">
         <v>11</v>
@@ -14822,7 +14822,7 @@
         <v>10</v>
       </c>
       <c r="F461" s="3">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G461" s="3" t="s">
         <v>11</v>
@@ -14845,7 +14845,7 @@
         <v>10</v>
       </c>
       <c r="F462">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G462" t="s">
         <v>11</v>
@@ -14868,7 +14868,7 @@
         <v>10</v>
       </c>
       <c r="F463" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G463" s="3" t="s">
         <v>11</v>
@@ -14914,7 +14914,7 @@
         <v>10</v>
       </c>
       <c r="F465" s="3">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G465" s="3" t="s">
         <v>11</v>
@@ -14937,7 +14937,7 @@
         <v>10</v>
       </c>
       <c r="F466">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G466" t="s">
         <v>11</v>
@@ -14983,7 +14983,7 @@
         <v>10</v>
       </c>
       <c r="F468">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G468" t="s">
         <v>11</v>
@@ -15006,7 +15006,7 @@
         <v>10</v>
       </c>
       <c r="F469" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G469" s="3" t="s">
         <v>11</v>
@@ -15029,7 +15029,7 @@
         <v>10</v>
       </c>
       <c r="F470">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G470" t="s">
         <v>11</v>
@@ -15052,7 +15052,7 @@
         <v>10</v>
       </c>
       <c r="F471" s="3">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G471" s="3" t="s">
         <v>11</v>
@@ -15075,7 +15075,7 @@
         <v>10</v>
       </c>
       <c r="F472">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G472" t="s">
         <v>11</v>
@@ -15098,7 +15098,7 @@
         <v>10</v>
       </c>
       <c r="F473" s="3">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G473" s="3" t="s">
         <v>11</v>
@@ -15121,7 +15121,7 @@
         <v>10</v>
       </c>
       <c r="F474">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G474" t="s">
         <v>11</v>
@@ -15144,7 +15144,7 @@
         <v>10</v>
       </c>
       <c r="F475" s="3">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G475" s="3" t="s">
         <v>11</v>
@@ -15167,7 +15167,7 @@
         <v>10</v>
       </c>
       <c r="F476">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G476" t="s">
         <v>11</v>
@@ -15213,7 +15213,7 @@
         <v>10</v>
       </c>
       <c r="F478">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G478" t="s">
         <v>11</v>
@@ -15236,7 +15236,7 @@
         <v>10</v>
       </c>
       <c r="F479" s="3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G479" s="3" t="s">
         <v>11</v>
@@ -15259,7 +15259,7 @@
         <v>10</v>
       </c>
       <c r="F480">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G480" t="s">
         <v>11</v>
@@ -15282,7 +15282,7 @@
         <v>10</v>
       </c>
       <c r="F481" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G481" s="3" t="s">
         <v>11</v>
@@ -15305,7 +15305,7 @@
         <v>10</v>
       </c>
       <c r="F482">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G482" t="s">
         <v>11</v>
@@ -15328,7 +15328,7 @@
         <v>10</v>
       </c>
       <c r="F483" s="3">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G483" s="3" t="s">
         <v>11</v>
@@ -15351,7 +15351,7 @@
         <v>10</v>
       </c>
       <c r="F484">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G484" t="s">
         <v>11</v>
@@ -15374,7 +15374,7 @@
         <v>10</v>
       </c>
       <c r="F485" s="3">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G485" s="3" t="s">
         <v>11</v>
@@ -15397,7 +15397,7 @@
         <v>10</v>
       </c>
       <c r="F486">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G486" t="s">
         <v>11</v>
@@ -15420,7 +15420,7 @@
         <v>10</v>
       </c>
       <c r="F487" s="3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G487" s="3" t="s">
         <v>11</v>
@@ -15443,7 +15443,7 @@
         <v>10</v>
       </c>
       <c r="F488">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G488" t="s">
         <v>11</v>
@@ -15466,7 +15466,7 @@
         <v>10</v>
       </c>
       <c r="F489" s="3">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G489" s="3" t="s">
         <v>11</v>
@@ -15489,7 +15489,7 @@
         <v>10</v>
       </c>
       <c r="F490">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G490" t="s">
         <v>11</v>
@@ -15512,7 +15512,7 @@
         <v>10</v>
       </c>
       <c r="F491" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G491" s="3" t="s">
         <v>11</v>
@@ -15535,7 +15535,7 @@
         <v>10</v>
       </c>
       <c r="F492">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G492" t="s">
         <v>11</v>
@@ -15558,7 +15558,7 @@
         <v>10</v>
       </c>
       <c r="F493" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G493" s="3" t="s">
         <v>11</v>
@@ -15581,7 +15581,7 @@
         <v>10</v>
       </c>
       <c r="F494">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G494" t="s">
         <v>11</v>
@@ -15604,7 +15604,7 @@
         <v>10</v>
       </c>
       <c r="F495" s="3">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G495" s="3" t="s">
         <v>11</v>
@@ -15627,7 +15627,7 @@
         <v>10</v>
       </c>
       <c r="F496">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G496" t="s">
         <v>11</v>
@@ -15650,7 +15650,7 @@
         <v>10</v>
       </c>
       <c r="F497" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G497" s="3" t="s">
         <v>11</v>
@@ -15673,7 +15673,7 @@
         <v>10</v>
       </c>
       <c r="F498">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G498" t="s">
         <v>11</v>
@@ -15696,7 +15696,7 @@
         <v>10</v>
       </c>
       <c r="F499" s="3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G499" s="3" t="s">
         <v>11</v>
@@ -15742,7 +15742,7 @@
         <v>10</v>
       </c>
       <c r="F501" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G501" s="3" t="s">
         <v>11</v>
@@ -15765,7 +15765,7 @@
         <v>10</v>
       </c>
       <c r="F502">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G502" t="s">
         <v>11</v>
@@ -15788,7 +15788,7 @@
         <v>10</v>
       </c>
       <c r="F503" s="3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G503" s="3" t="s">
         <v>11</v>
@@ -15811,7 +15811,7 @@
         <v>10</v>
       </c>
       <c r="F504">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G504" t="s">
         <v>11</v>
@@ -15834,7 +15834,7 @@
         <v>10</v>
       </c>
       <c r="F505" s="3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G505" s="3" t="s">
         <v>11</v>
@@ -15857,7 +15857,7 @@
         <v>10</v>
       </c>
       <c r="F506">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G506" t="s">
         <v>11</v>
@@ -15880,7 +15880,7 @@
         <v>10</v>
       </c>
       <c r="F507" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G507" s="3" t="s">
         <v>11</v>
@@ -15903,7 +15903,7 @@
         <v>10</v>
       </c>
       <c r="F508">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G508" t="s">
         <v>11</v>
@@ -15926,7 +15926,7 @@
         <v>10</v>
       </c>
       <c r="F509" s="3">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G509" s="3" t="s">
         <v>11</v>
@@ -15972,7 +15972,7 @@
         <v>10</v>
       </c>
       <c r="F511" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G511" s="3" t="s">
         <v>11</v>
@@ -15995,7 +15995,7 @@
         <v>10</v>
       </c>
       <c r="F512">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G512" t="s">
         <v>11</v>
@@ -16018,7 +16018,7 @@
         <v>10</v>
       </c>
       <c r="F513" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G513" s="3" t="s">
         <v>11</v>
@@ -16041,7 +16041,7 @@
         <v>10</v>
       </c>
       <c r="F514">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G514" t="s">
         <v>11</v>
@@ -16064,7 +16064,7 @@
         <v>10</v>
       </c>
       <c r="F515" s="3">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G515" s="3" t="s">
         <v>11</v>
@@ -16087,7 +16087,7 @@
         <v>10</v>
       </c>
       <c r="F516">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G516" t="s">
         <v>11</v>
@@ -16110,7 +16110,7 @@
         <v>10</v>
       </c>
       <c r="F517" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G517" s="3" t="s">
         <v>11</v>
@@ -16133,7 +16133,7 @@
         <v>10</v>
       </c>
       <c r="F518">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G518" t="s">
         <v>11</v>
@@ -16179,7 +16179,7 @@
         <v>10</v>
       </c>
       <c r="F520">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G520" t="s">
         <v>11</v>
@@ -16202,7 +16202,7 @@
         <v>10</v>
       </c>
       <c r="F521" s="3">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G521" s="3" t="s">
         <v>11</v>
@@ -16225,7 +16225,7 @@
         <v>10</v>
       </c>
       <c r="F522">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G522" t="s">
         <v>11</v>
@@ -16248,7 +16248,7 @@
         <v>10</v>
       </c>
       <c r="F523" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G523" s="3" t="s">
         <v>11</v>
@@ -16271,7 +16271,7 @@
         <v>10</v>
       </c>
       <c r="F524">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G524" t="s">
         <v>11</v>
@@ -16317,7 +16317,7 @@
         <v>10</v>
       </c>
       <c r="F526">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G526" t="s">
         <v>11</v>
@@ -16340,7 +16340,7 @@
         <v>10</v>
       </c>
       <c r="F527" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G527" s="3" t="s">
         <v>11</v>
@@ -16363,7 +16363,7 @@
         <v>10</v>
       </c>
       <c r="F528">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G528" t="s">
         <v>11</v>
@@ -16386,7 +16386,7 @@
         <v>10</v>
       </c>
       <c r="F529" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G529" s="3" t="s">
         <v>11</v>
@@ -16409,7 +16409,7 @@
         <v>10</v>
       </c>
       <c r="F530">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G530" t="s">
         <v>11</v>
@@ -16432,7 +16432,7 @@
         <v>10</v>
       </c>
       <c r="F531" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G531" s="3" t="s">
         <v>11</v>
@@ -16455,7 +16455,7 @@
         <v>10</v>
       </c>
       <c r="F532">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G532" t="s">
         <v>11</v>
@@ -16478,7 +16478,7 @@
         <v>10</v>
       </c>
       <c r="F533" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G533" s="3" t="s">
         <v>11</v>
@@ -16501,7 +16501,7 @@
         <v>10</v>
       </c>
       <c r="F534">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G534" t="s">
         <v>11</v>
@@ -16524,7 +16524,7 @@
         <v>10</v>
       </c>
       <c r="F535" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G535" s="3" t="s">
         <v>11</v>
@@ -16547,7 +16547,7 @@
         <v>10</v>
       </c>
       <c r="F536">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G536" t="s">
         <v>11</v>
@@ -16570,7 +16570,7 @@
         <v>10</v>
       </c>
       <c r="F537" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G537" s="3" t="s">
         <v>11</v>
@@ -16593,7 +16593,7 @@
         <v>10</v>
       </c>
       <c r="F538">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G538" t="s">
         <v>11</v>
@@ -16616,7 +16616,7 @@
         <v>10</v>
       </c>
       <c r="F539" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G539" s="3" t="s">
         <v>11</v>
@@ -16639,7 +16639,7 @@
         <v>10</v>
       </c>
       <c r="F540">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G540" t="s">
         <v>11</v>
@@ -16685,7 +16685,7 @@
         <v>10</v>
       </c>
       <c r="F542">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G542" t="s">
         <v>11</v>
@@ -16731,7 +16731,7 @@
         <v>10</v>
       </c>
       <c r="F544">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G544" t="s">
         <v>11</v>
@@ -16777,7 +16777,7 @@
         <v>10</v>
       </c>
       <c r="F546">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G546" t="s">
         <v>11</v>
@@ -16800,7 +16800,7 @@
         <v>10</v>
       </c>
       <c r="F547" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G547" s="3" t="s">
         <v>11</v>
@@ -16823,7 +16823,7 @@
         <v>10</v>
       </c>
       <c r="F548">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G548" t="s">
         <v>11</v>
@@ -16846,7 +16846,7 @@
         <v>10</v>
       </c>
       <c r="F549" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G549" s="3" t="s">
         <v>11</v>
@@ -16869,7 +16869,7 @@
         <v>10</v>
       </c>
       <c r="F550">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G550" t="s">
         <v>11</v>
@@ -16892,7 +16892,7 @@
         <v>10</v>
       </c>
       <c r="F551" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G551" s="3" t="s">
         <v>11</v>
@@ -16938,7 +16938,7 @@
         <v>10</v>
       </c>
       <c r="F553" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G553" s="3" t="s">
         <v>11</v>
@@ -16961,7 +16961,7 @@
         <v>10</v>
       </c>
       <c r="F554">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G554" t="s">
         <v>11</v>
@@ -16984,7 +16984,7 @@
         <v>10</v>
       </c>
       <c r="F555" s="3">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G555" s="3" t="s">
         <v>11</v>
@@ -17030,7 +17030,7 @@
         <v>10</v>
       </c>
       <c r="F557" s="3">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G557" s="3" t="s">
         <v>11</v>
@@ -17053,7 +17053,7 @@
         <v>10</v>
       </c>
       <c r="F558">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G558" t="s">
         <v>11</v>
@@ -17076,7 +17076,7 @@
         <v>10</v>
       </c>
       <c r="F559" s="3">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G559" s="3" t="s">
         <v>11</v>
@@ -17099,7 +17099,7 @@
         <v>10</v>
       </c>
       <c r="F560">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G560" t="s">
         <v>11</v>
@@ -17122,7 +17122,7 @@
         <v>10</v>
       </c>
       <c r="F561" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G561" s="3" t="s">
         <v>11</v>
@@ -17145,7 +17145,7 @@
         <v>10</v>
       </c>
       <c r="F562">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G562" t="s">
         <v>11</v>
@@ -17168,7 +17168,7 @@
         <v>10</v>
       </c>
       <c r="F563" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G563" s="3" t="s">
         <v>11</v>
@@ -17191,7 +17191,7 @@
         <v>10</v>
       </c>
       <c r="F564">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G564" t="s">
         <v>11</v>
@@ -17214,7 +17214,7 @@
         <v>10</v>
       </c>
       <c r="F565" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G565" s="3" t="s">
         <v>11</v>
@@ -17237,7 +17237,7 @@
         <v>10</v>
       </c>
       <c r="F566">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G566" t="s">
         <v>11</v>
@@ -17260,7 +17260,7 @@
         <v>10</v>
       </c>
       <c r="F567" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G567" s="3" t="s">
         <v>11</v>
@@ -17283,7 +17283,7 @@
         <v>10</v>
       </c>
       <c r="F568">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G568" t="s">
         <v>11</v>
@@ -17306,7 +17306,7 @@
         <v>10</v>
       </c>
       <c r="F569" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G569" s="3" t="s">
         <v>11</v>
@@ -17329,7 +17329,7 @@
         <v>10</v>
       </c>
       <c r="F570">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G570" t="s">
         <v>11</v>
@@ -17352,7 +17352,7 @@
         <v>10</v>
       </c>
       <c r="F571" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G571" s="3" t="s">
         <v>11</v>
@@ -17375,7 +17375,7 @@
         <v>10</v>
       </c>
       <c r="F572">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G572" t="s">
         <v>11</v>
@@ -17398,7 +17398,7 @@
         <v>10</v>
       </c>
       <c r="F573" s="3">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G573" s="3" t="s">
         <v>11</v>
@@ -17421,7 +17421,7 @@
         <v>10</v>
       </c>
       <c r="F574">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G574" t="s">
         <v>11</v>
@@ -17444,7 +17444,7 @@
         <v>10</v>
       </c>
       <c r="F575" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G575" s="3" t="s">
         <v>11</v>
@@ -17467,7 +17467,7 @@
         <v>10</v>
       </c>
       <c r="F576">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G576" t="s">
         <v>11</v>
@@ -17490,7 +17490,7 @@
         <v>10</v>
       </c>
       <c r="F577" s="3">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G577" s="3" t="s">
         <v>11</v>
@@ -17513,7 +17513,7 @@
         <v>10</v>
       </c>
       <c r="F578">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G578" t="s">
         <v>11</v>
@@ -17536,7 +17536,7 @@
         <v>10</v>
       </c>
       <c r="F579" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G579" s="3" t="s">
         <v>11</v>
@@ -17559,7 +17559,7 @@
         <v>10</v>
       </c>
       <c r="F580">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G580" t="s">
         <v>11</v>
@@ -17582,7 +17582,7 @@
         <v>10</v>
       </c>
       <c r="F581" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G581" s="3" t="s">
         <v>11</v>
@@ -17605,7 +17605,7 @@
         <v>10</v>
       </c>
       <c r="F582">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G582" t="s">
         <v>11</v>
@@ -17628,7 +17628,7 @@
         <v>10</v>
       </c>
       <c r="F583" s="3">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G583" s="3" t="s">
         <v>11</v>
@@ -17651,7 +17651,7 @@
         <v>10</v>
       </c>
       <c r="F584">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G584" t="s">
         <v>11</v>
@@ -17674,7 +17674,7 @@
         <v>10</v>
       </c>
       <c r="F585" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G585" s="3" t="s">
         <v>11</v>
@@ -17697,7 +17697,7 @@
         <v>10</v>
       </c>
       <c r="F586">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G586" t="s">
         <v>11</v>
@@ -17720,7 +17720,7 @@
         <v>10</v>
       </c>
       <c r="F587" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G587" s="3" t="s">
         <v>11</v>
@@ -17743,7 +17743,7 @@
         <v>10</v>
       </c>
       <c r="F588">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G588" t="s">
         <v>11</v>
@@ -17766,7 +17766,7 @@
         <v>10</v>
       </c>
       <c r="F589" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G589" s="3" t="s">
         <v>11</v>
@@ -17789,7 +17789,7 @@
         <v>10</v>
       </c>
       <c r="F590">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G590" t="s">
         <v>11</v>
@@ -17812,7 +17812,7 @@
         <v>10</v>
       </c>
       <c r="F591" s="3">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G591" s="3" t="s">
         <v>11</v>
@@ -17835,7 +17835,7 @@
         <v>10</v>
       </c>
       <c r="F592">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G592" t="s">
         <v>11</v>
@@ -17858,7 +17858,7 @@
         <v>10</v>
       </c>
       <c r="F593" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G593" s="3" t="s">
         <v>11</v>
@@ -17881,7 +17881,7 @@
         <v>10</v>
       </c>
       <c r="F594">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G594" t="s">
         <v>11</v>
@@ -17904,7 +17904,7 @@
         <v>10</v>
       </c>
       <c r="F595" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G595" s="3" t="s">
         <v>11</v>
@@ -17927,7 +17927,7 @@
         <v>10</v>
       </c>
       <c r="F596">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G596" t="s">
         <v>11</v>
@@ -17950,7 +17950,7 @@
         <v>10</v>
       </c>
       <c r="F597" s="3">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G597" s="3" t="s">
         <v>11</v>
@@ -17973,7 +17973,7 @@
         <v>10</v>
       </c>
       <c r="F598">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G598" t="s">
         <v>11</v>
@@ -18019,7 +18019,7 @@
         <v>10</v>
       </c>
       <c r="F600">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G600" t="s">
         <v>11</v>
@@ -18042,7 +18042,7 @@
         <v>10</v>
       </c>
       <c r="F601" s="3">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G601" s="3" t="s">
         <v>11</v>
@@ -18065,7 +18065,7 @@
         <v>10</v>
       </c>
       <c r="F602">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G602" t="s">
         <v>11</v>
@@ -18111,7 +18111,7 @@
         <v>10</v>
       </c>
       <c r="F604">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G604" t="s">
         <v>11</v>
@@ -18134,7 +18134,7 @@
         <v>10</v>
       </c>
       <c r="F605" s="3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G605" s="3" t="s">
         <v>11</v>
@@ -18157,7 +18157,7 @@
         <v>10</v>
       </c>
       <c r="F606">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G606" t="s">
         <v>11</v>
@@ -18180,7 +18180,7 @@
         <v>10</v>
       </c>
       <c r="F607" s="3">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G607" s="3" t="s">
         <v>11</v>
@@ -18203,7 +18203,7 @@
         <v>10</v>
       </c>
       <c r="F608">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G608" t="s">
         <v>11</v>
@@ -18226,7 +18226,7 @@
         <v>10</v>
       </c>
       <c r="F609" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G609" s="3" t="s">
         <v>11</v>
@@ -18249,7 +18249,7 @@
         <v>10</v>
       </c>
       <c r="F610">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G610" t="s">
         <v>11</v>
@@ -18272,7 +18272,7 @@
         <v>10</v>
       </c>
       <c r="F611" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G611" s="3" t="s">
         <v>11</v>
@@ -18295,7 +18295,7 @@
         <v>10</v>
       </c>
       <c r="F612">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G612" t="s">
         <v>11</v>
@@ -18318,7 +18318,7 @@
         <v>10</v>
       </c>
       <c r="F613" s="3">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G613" s="3" t="s">
         <v>11</v>
@@ -18341,7 +18341,7 @@
         <v>10</v>
       </c>
       <c r="F614">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G614" t="s">
         <v>11</v>
@@ -18364,7 +18364,7 @@
         <v>10</v>
       </c>
       <c r="F615" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G615" s="3" t="s">
         <v>11</v>
@@ -18387,7 +18387,7 @@
         <v>10</v>
       </c>
       <c r="F616">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G616" t="s">
         <v>11</v>
@@ -18410,7 +18410,7 @@
         <v>10</v>
       </c>
       <c r="F617" s="3">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G617" s="3" t="s">
         <v>11</v>
@@ -18456,7 +18456,7 @@
         <v>10</v>
       </c>
       <c r="F619" s="3">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G619" s="3" t="s">
         <v>11</v>
@@ -18479,7 +18479,7 @@
         <v>10</v>
       </c>
       <c r="F620">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G620" t="s">
         <v>11</v>
@@ -18502,7 +18502,7 @@
         <v>10</v>
       </c>
       <c r="F621" s="3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G621" s="3" t="s">
         <v>11</v>
@@ -18525,7 +18525,7 @@
         <v>10</v>
       </c>
       <c r="F622">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G622" t="s">
         <v>11</v>
@@ -18548,7 +18548,7 @@
         <v>10</v>
       </c>
       <c r="F623" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G623" s="3" t="s">
         <v>11</v>
@@ -18571,7 +18571,7 @@
         <v>10</v>
       </c>
       <c r="F624">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G624" t="s">
         <v>11</v>
@@ -18594,7 +18594,7 @@
         <v>10</v>
       </c>
       <c r="F625" s="3">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G625" s="3" t="s">
         <v>11</v>
@@ -18617,7 +18617,7 @@
         <v>10</v>
       </c>
       <c r="F626">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G626" t="s">
         <v>11</v>
@@ -18640,7 +18640,7 @@
         <v>10</v>
       </c>
       <c r="F627" s="3">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G627" s="3" t="s">
         <v>11</v>
@@ -18663,7 +18663,7 @@
         <v>10</v>
       </c>
       <c r="F628">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G628" t="s">
         <v>11</v>
@@ -18686,7 +18686,7 @@
         <v>10</v>
       </c>
       <c r="F629" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G629" s="3" t="s">
         <v>11</v>
@@ -18709,7 +18709,7 @@
         <v>10</v>
       </c>
       <c r="F630">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G630" t="s">
         <v>11</v>
@@ -18732,7 +18732,7 @@
         <v>10</v>
       </c>
       <c r="F631" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G631" s="3" t="s">
         <v>11</v>
@@ -18755,7 +18755,7 @@
         <v>10</v>
       </c>
       <c r="F632">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G632" t="s">
         <v>11</v>
@@ -18778,7 +18778,7 @@
         <v>10</v>
       </c>
       <c r="F633" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G633" s="3" t="s">
         <v>11</v>
@@ -18801,7 +18801,7 @@
         <v>10</v>
       </c>
       <c r="F634">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G634" t="s">
         <v>11</v>
@@ -18824,7 +18824,7 @@
         <v>10</v>
       </c>
       <c r="F635" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G635" s="3" t="s">
         <v>11</v>
@@ -18847,7 +18847,7 @@
         <v>10</v>
       </c>
       <c r="F636">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G636" t="s">
         <v>11</v>
@@ -18870,7 +18870,7 @@
         <v>10</v>
       </c>
       <c r="F637" s="3">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G637" s="3" t="s">
         <v>11</v>
@@ -18916,7 +18916,7 @@
         <v>10</v>
       </c>
       <c r="F639" s="3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G639" s="3" t="s">
         <v>11</v>
@@ -18939,7 +18939,7 @@
         <v>10</v>
       </c>
       <c r="F640">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G640" t="s">
         <v>11</v>
@@ -18962,7 +18962,7 @@
         <v>10</v>
       </c>
       <c r="F641" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G641" s="3" t="s">
         <v>11</v>
@@ -18985,7 +18985,7 @@
         <v>10</v>
       </c>
       <c r="F642">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G642" t="s">
         <v>11</v>
@@ -19031,7 +19031,7 @@
         <v>10</v>
       </c>
       <c r="F644">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G644" t="s">
         <v>11</v>
@@ -19054,7 +19054,7 @@
         <v>10</v>
       </c>
       <c r="F645" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G645" s="3" t="s">
         <v>11</v>
@@ -19077,7 +19077,7 @@
         <v>10</v>
       </c>
       <c r="F646">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G646" t="s">
         <v>11</v>
@@ -19100,7 +19100,7 @@
         <v>10</v>
       </c>
       <c r="F647" s="3">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G647" s="3" t="s">
         <v>11</v>
@@ -19123,7 +19123,7 @@
         <v>10</v>
       </c>
       <c r="F648">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G648" t="s">
         <v>11</v>
@@ -19192,7 +19192,7 @@
         <v>10</v>
       </c>
       <c r="F651" s="3">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G651" s="3" t="s">
         <v>11</v>
@@ -19215,7 +19215,7 @@
         <v>10</v>
       </c>
       <c r="F652">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G652" t="s">
         <v>11</v>
@@ -19238,7 +19238,7 @@
         <v>10</v>
       </c>
       <c r="F653" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G653" s="3" t="s">
         <v>11</v>
@@ -19261,7 +19261,7 @@
         <v>10</v>
       </c>
       <c r="F654">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G654" t="s">
         <v>11</v>
@@ -19284,7 +19284,7 @@
         <v>10</v>
       </c>
       <c r="F655" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G655" s="3" t="s">
         <v>11</v>
@@ -19307,7 +19307,7 @@
         <v>10</v>
       </c>
       <c r="F656">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G656" t="s">
         <v>11</v>
@@ -19376,7 +19376,7 @@
         <v>10</v>
       </c>
       <c r="F659" s="3">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G659" s="3" t="s">
         <v>11</v>
@@ -19399,7 +19399,7 @@
         <v>10</v>
       </c>
       <c r="F660">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G660" t="s">
         <v>11</v>
@@ -19422,7 +19422,7 @@
         <v>10</v>
       </c>
       <c r="F661" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G661" s="3" t="s">
         <v>11</v>
@@ -19445,7 +19445,7 @@
         <v>10</v>
       </c>
       <c r="F662">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G662" t="s">
         <v>11</v>
@@ -19468,7 +19468,7 @@
         <v>10</v>
       </c>
       <c r="F663" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G663" s="3" t="s">
         <v>11</v>
@@ -19491,7 +19491,7 @@
         <v>10</v>
       </c>
       <c r="F664">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G664" t="s">
         <v>11</v>
@@ -19514,7 +19514,7 @@
         <v>10</v>
       </c>
       <c r="F665" s="3">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G665" s="3" t="s">
         <v>11</v>
@@ -19537,7 +19537,7 @@
         <v>10</v>
       </c>
       <c r="F666">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G666" t="s">
         <v>11</v>
@@ -19560,7 +19560,7 @@
         <v>10</v>
       </c>
       <c r="F667" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G667" s="3" t="s">
         <v>11</v>
@@ -19583,7 +19583,7 @@
         <v>10</v>
       </c>
       <c r="F668">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G668" t="s">
         <v>11</v>
@@ -19606,7 +19606,7 @@
         <v>10</v>
       </c>
       <c r="F669" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G669" s="3" t="s">
         <v>11</v>
@@ -19629,7 +19629,7 @@
         <v>10</v>
       </c>
       <c r="F670">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G670" t="s">
         <v>11</v>
@@ -19652,7 +19652,7 @@
         <v>10</v>
       </c>
       <c r="F671" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G671" s="3" t="s">
         <v>11</v>
@@ -19675,7 +19675,7 @@
         <v>10</v>
       </c>
       <c r="F672">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G672" t="s">
         <v>11</v>
@@ -19698,7 +19698,7 @@
         <v>10</v>
       </c>
       <c r="F673" s="3">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G673" s="3" t="s">
         <v>11</v>
@@ -19721,7 +19721,7 @@
         <v>10</v>
       </c>
       <c r="F674">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G674" t="s">
         <v>11</v>
@@ -19744,7 +19744,7 @@
         <v>10</v>
       </c>
       <c r="F675" s="3">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G675" s="3" t="s">
         <v>11</v>
@@ -19767,7 +19767,7 @@
         <v>10</v>
       </c>
       <c r="F676">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G676" t="s">
         <v>11</v>
@@ -19790,7 +19790,7 @@
         <v>10</v>
       </c>
       <c r="F677" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G677" s="3" t="s">
         <v>11</v>
@@ -19813,7 +19813,7 @@
         <v>10</v>
       </c>
       <c r="F678">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G678" t="s">
         <v>11</v>
@@ -19836,7 +19836,7 @@
         <v>10</v>
       </c>
       <c r="F679" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G679" s="3" t="s">
         <v>11</v>
@@ -19859,7 +19859,7 @@
         <v>10</v>
       </c>
       <c r="F680">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G680" t="s">
         <v>11</v>
@@ -19882,7 +19882,7 @@
         <v>10</v>
       </c>
       <c r="F681" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G681" s="3" t="s">
         <v>11</v>
@@ -19905,7 +19905,7 @@
         <v>10</v>
       </c>
       <c r="F682">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G682" t="s">
         <v>11</v>
@@ -19928,7 +19928,7 @@
         <v>10</v>
       </c>
       <c r="F683" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G683" s="3" t="s">
         <v>11</v>
@@ -19951,7 +19951,7 @@
         <v>10</v>
       </c>
       <c r="F684">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G684" t="s">
         <v>11</v>
@@ -19974,7 +19974,7 @@
         <v>10</v>
       </c>
       <c r="F685" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G685" s="3" t="s">
         <v>11</v>
@@ -19997,7 +19997,7 @@
         <v>10</v>
       </c>
       <c r="F686">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G686" t="s">
         <v>11</v>
@@ -20020,7 +20020,7 @@
         <v>10</v>
       </c>
       <c r="F687" s="3">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G687" s="3" t="s">
         <v>11</v>
@@ -20066,7 +20066,7 @@
         <v>10</v>
       </c>
       <c r="F689" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G689" s="3" t="s">
         <v>11</v>
@@ -20089,7 +20089,7 @@
         <v>10</v>
       </c>
       <c r="F690">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G690" t="s">
         <v>11</v>
@@ -20112,7 +20112,7 @@
         <v>10</v>
       </c>
       <c r="F691" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G691" s="3" t="s">
         <v>11</v>
@@ -20135,7 +20135,7 @@
         <v>10</v>
       </c>
       <c r="F692">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G692" t="s">
         <v>11</v>
@@ -20158,7 +20158,7 @@
         <v>10</v>
       </c>
       <c r="F693" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G693" s="3" t="s">
         <v>11</v>
@@ -20181,7 +20181,7 @@
         <v>10</v>
       </c>
       <c r="F694">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G694" t="s">
         <v>11</v>
@@ -20204,7 +20204,7 @@
         <v>10</v>
       </c>
       <c r="F695" s="3">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G695" s="3" t="s">
         <v>11</v>
@@ -20227,7 +20227,7 @@
         <v>10</v>
       </c>
       <c r="F696">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G696" t="s">
         <v>11</v>
@@ -20250,7 +20250,7 @@
         <v>10</v>
       </c>
       <c r="F697" s="3">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G697" s="3" t="s">
         <v>11</v>
@@ -20273,7 +20273,7 @@
         <v>10</v>
       </c>
       <c r="F698">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G698" t="s">
         <v>11</v>
@@ -20296,7 +20296,7 @@
         <v>10</v>
       </c>
       <c r="F699" s="3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G699" s="3" t="s">
         <v>11</v>
@@ -20319,7 +20319,7 @@
         <v>10</v>
       </c>
       <c r="F700">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G700" t="s">
         <v>11</v>
@@ -20342,7 +20342,7 @@
         <v>10</v>
       </c>
       <c r="F701" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G701" s="3" t="s">
         <v>11</v>
@@ -20365,7 +20365,7 @@
         <v>10</v>
       </c>
       <c r="F702">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G702" t="s">
         <v>11</v>
@@ -20388,7 +20388,7 @@
         <v>10</v>
       </c>
       <c r="F703" s="3">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G703" s="3" t="s">
         <v>11</v>
@@ -20411,7 +20411,7 @@
         <v>10</v>
       </c>
       <c r="F704">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G704" t="s">
         <v>11</v>
@@ -20434,7 +20434,7 @@
         <v>10</v>
       </c>
       <c r="F705" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G705" s="3" t="s">
         <v>11</v>
@@ -20457,7 +20457,7 @@
         <v>10</v>
       </c>
       <c r="F706">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G706" t="s">
         <v>11</v>
@@ -20480,7 +20480,7 @@
         <v>10</v>
       </c>
       <c r="F707" s="3">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G707" s="3" t="s">
         <v>11</v>
@@ -20503,7 +20503,7 @@
         <v>10</v>
       </c>
       <c r="F708">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G708" t="s">
         <v>11</v>
@@ -20526,7 +20526,7 @@
         <v>10</v>
       </c>
       <c r="F709" s="3">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G709" s="3" t="s">
         <v>11</v>
@@ -20549,7 +20549,7 @@
         <v>10</v>
       </c>
       <c r="F710">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G710" t="s">
         <v>11</v>
@@ -20572,7 +20572,7 @@
         <v>10</v>
       </c>
       <c r="F711" s="3">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G711" s="3" t="s">
         <v>11</v>
@@ -20595,7 +20595,7 @@
         <v>10</v>
       </c>
       <c r="F712">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G712" t="s">
         <v>11</v>
@@ -20618,7 +20618,7 @@
         <v>10</v>
       </c>
       <c r="F713" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G713" s="3" t="s">
         <v>11</v>
@@ -20641,7 +20641,7 @@
         <v>10</v>
       </c>
       <c r="F714">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G714" t="s">
         <v>11</v>
@@ -20664,7 +20664,7 @@
         <v>10</v>
       </c>
       <c r="F715" s="3">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G715" s="3" t="s">
         <v>11</v>
@@ -20687,7 +20687,7 @@
         <v>10</v>
       </c>
       <c r="F716">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G716" t="s">
         <v>11</v>
@@ -20710,7 +20710,7 @@
         <v>10</v>
       </c>
       <c r="F717" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G717" s="3" t="s">
         <v>11</v>
@@ -20733,7 +20733,7 @@
         <v>10</v>
       </c>
       <c r="F718">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G718" t="s">
         <v>11</v>
@@ -20756,7 +20756,7 @@
         <v>10</v>
       </c>
       <c r="F719" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G719" s="3" t="s">
         <v>11</v>
@@ -20779,7 +20779,7 @@
         <v>10</v>
       </c>
       <c r="F720">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G720" t="s">
         <v>11</v>
@@ -20802,7 +20802,7 @@
         <v>10</v>
       </c>
       <c r="F721" s="3">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G721" s="3" t="s">
         <v>11</v>
@@ -20825,7 +20825,7 @@
         <v>10</v>
       </c>
       <c r="F722">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G722" t="s">
         <v>11</v>
@@ -20871,7 +20871,7 @@
         <v>10</v>
       </c>
       <c r="F724">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G724" t="s">
         <v>11</v>
@@ -20894,7 +20894,7 @@
         <v>10</v>
       </c>
       <c r="F725" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G725" s="3" t="s">
         <v>11</v>
@@ -20917,7 +20917,7 @@
         <v>10</v>
       </c>
       <c r="F726">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G726" t="s">
         <v>11</v>
@@ -20940,7 +20940,7 @@
         <v>10</v>
       </c>
       <c r="F727" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G727" s="3" t="s">
         <v>11</v>
@@ -20986,7 +20986,7 @@
         <v>10</v>
       </c>
       <c r="F729" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G729" s="3" t="s">
         <v>11</v>
@@ -21009,7 +21009,7 @@
         <v>10</v>
       </c>
       <c r="F730">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G730" t="s">
         <v>11</v>
@@ -21032,7 +21032,7 @@
         <v>10</v>
       </c>
       <c r="F731" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G731" s="3" t="s">
         <v>11</v>
@@ -21055,7 +21055,7 @@
         <v>10</v>
       </c>
       <c r="F732">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G732" t="s">
         <v>11</v>
@@ -21078,7 +21078,7 @@
         <v>10</v>
       </c>
       <c r="F733" s="3">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G733" s="3" t="s">
         <v>11</v>
@@ -21101,7 +21101,7 @@
         <v>10</v>
       </c>
       <c r="F734">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G734" t="s">
         <v>11</v>
@@ -21124,7 +21124,7 @@
         <v>10</v>
       </c>
       <c r="F735" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G735" s="3" t="s">
         <v>11</v>
@@ -21147,7 +21147,7 @@
         <v>10</v>
       </c>
       <c r="F736">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G736" t="s">
         <v>11</v>
@@ -21170,7 +21170,7 @@
         <v>10</v>
       </c>
       <c r="F737" s="3">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G737" s="3" t="s">
         <v>11</v>
@@ -21193,7 +21193,7 @@
         <v>10</v>
       </c>
       <c r="F738">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G738" t="s">
         <v>11</v>
@@ -21239,7 +21239,7 @@
         <v>10</v>
       </c>
       <c r="F740">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G740" t="s">
         <v>11</v>
@@ -21262,7 +21262,7 @@
         <v>10</v>
       </c>
       <c r="F741" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G741" s="3" t="s">
         <v>11</v>
@@ -21285,7 +21285,7 @@
         <v>10</v>
       </c>
       <c r="F742">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G742" t="s">
         <v>11</v>
@@ -21308,7 +21308,7 @@
         <v>10</v>
       </c>
       <c r="F743" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G743" s="3" t="s">
         <v>11</v>
@@ -21331,7 +21331,7 @@
         <v>10</v>
       </c>
       <c r="F744">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G744" t="s">
         <v>11</v>
@@ -21354,7 +21354,7 @@
         <v>10</v>
       </c>
       <c r="F745" s="3">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G745" s="3" t="s">
         <v>11</v>
@@ -21377,7 +21377,7 @@
         <v>10</v>
       </c>
       <c r="F746">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G746" t="s">
         <v>11</v>
@@ -21400,7 +21400,7 @@
         <v>10</v>
       </c>
       <c r="F747" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G747" s="3" t="s">
         <v>11</v>
@@ -21423,7 +21423,7 @@
         <v>10</v>
       </c>
       <c r="F748">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G748" t="s">
         <v>11</v>
@@ -21446,7 +21446,7 @@
         <v>10</v>
       </c>
       <c r="F749" s="3">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G749" s="3" t="s">
         <v>11</v>
@@ -21469,7 +21469,7 @@
         <v>10</v>
       </c>
       <c r="F750">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G750" t="s">
         <v>11</v>
@@ -21492,7 +21492,7 @@
         <v>10</v>
       </c>
       <c r="F751" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G751" s="3" t="s">
         <v>11</v>
@@ -21515,7 +21515,7 @@
         <v>10</v>
       </c>
       <c r="F752">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G752" t="s">
         <v>11</v>
@@ -21538,7 +21538,7 @@
         <v>10</v>
       </c>
       <c r="F753" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G753" s="3" t="s">
         <v>11</v>
@@ -21561,7 +21561,7 @@
         <v>10</v>
       </c>
       <c r="F754">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G754" t="s">
         <v>11</v>
@@ -21584,7 +21584,7 @@
         <v>10</v>
       </c>
       <c r="F755" s="3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G755" s="3" t="s">
         <v>11</v>
@@ -21607,7 +21607,7 @@
         <v>10</v>
       </c>
       <c r="F756">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G756" t="s">
         <v>11</v>
@@ -21630,7 +21630,7 @@
         <v>10</v>
       </c>
       <c r="F757" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G757" s="3" t="s">
         <v>11</v>
@@ -21653,7 +21653,7 @@
         <v>10</v>
       </c>
       <c r="F758">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G758" t="s">
         <v>11</v>
@@ -21676,7 +21676,7 @@
         <v>10</v>
       </c>
       <c r="F759" s="3">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G759" s="3" t="s">
         <v>11</v>
@@ -21722,7 +21722,7 @@
         <v>10</v>
       </c>
       <c r="F761" s="3">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G761" s="3" t="s">
         <v>11</v>
@@ -21745,7 +21745,7 @@
         <v>10</v>
       </c>
       <c r="F762">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G762" t="s">
         <v>11</v>
@@ -21768,7 +21768,7 @@
         <v>10</v>
       </c>
       <c r="F763" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G763" s="3" t="s">
         <v>11</v>
@@ -21791,7 +21791,7 @@
         <v>10</v>
       </c>
       <c r="F764">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G764" t="s">
         <v>11</v>
@@ -21814,7 +21814,7 @@
         <v>10</v>
       </c>
       <c r="F765" s="3">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G765" s="3" t="s">
         <v>11</v>
@@ -21837,7 +21837,7 @@
         <v>10</v>
       </c>
       <c r="F766">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G766" t="s">
         <v>11</v>
@@ -21860,7 +21860,7 @@
         <v>10</v>
       </c>
       <c r="F767" s="3">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G767" s="3" t="s">
         <v>11</v>
@@ -21883,7 +21883,7 @@
         <v>10</v>
       </c>
       <c r="F768">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G768" t="s">
         <v>11</v>
@@ -21929,7 +21929,7 @@
         <v>10</v>
       </c>
       <c r="F770">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G770" t="s">
         <v>11</v>
@@ -21952,7 +21952,7 @@
         <v>10</v>
       </c>
       <c r="F771" s="3">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G771" s="3" t="s">
         <v>11</v>
@@ -21975,7 +21975,7 @@
         <v>10</v>
       </c>
       <c r="F772">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G772" t="s">
         <v>11</v>
@@ -22021,7 +22021,7 @@
         <v>10</v>
       </c>
       <c r="F774">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G774" t="s">
         <v>11</v>
@@ -22044,7 +22044,7 @@
         <v>10</v>
       </c>
       <c r="F775" s="3">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G775" s="3" t="s">
         <v>11</v>
@@ -22067,7 +22067,7 @@
         <v>10</v>
       </c>
       <c r="F776">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G776" t="s">
         <v>11</v>
@@ -22090,7 +22090,7 @@
         <v>10</v>
       </c>
       <c r="F777" s="3">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G777" s="3" t="s">
         <v>11</v>
@@ -22136,7 +22136,7 @@
         <v>10</v>
       </c>
       <c r="F779" s="3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G779" s="3" t="s">
         <v>11</v>
@@ -22159,7 +22159,7 @@
         <v>10</v>
       </c>
       <c r="F780">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G780" t="s">
         <v>11</v>
@@ -22182,7 +22182,7 @@
         <v>10</v>
       </c>
       <c r="F781" s="3">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G781" s="3" t="s">
         <v>11</v>
@@ -22205,7 +22205,7 @@
         <v>10</v>
       </c>
       <c r="F782">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G782" t="s">
         <v>11</v>
@@ -22228,7 +22228,7 @@
         <v>10</v>
       </c>
       <c r="F783" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G783" s="3" t="s">
         <v>11</v>
@@ -22251,7 +22251,7 @@
         <v>10</v>
       </c>
       <c r="F784">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G784" t="s">
         <v>11</v>
@@ -22274,7 +22274,7 @@
         <v>10</v>
       </c>
       <c r="F785" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G785" s="3" t="s">
         <v>11</v>
@@ -22297,7 +22297,7 @@
         <v>10</v>
       </c>
       <c r="F786">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G786" t="s">
         <v>11</v>
@@ -22320,7 +22320,7 @@
         <v>10</v>
       </c>
       <c r="F787" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G787" s="3" t="s">
         <v>11</v>
@@ -22343,7 +22343,7 @@
         <v>10</v>
       </c>
       <c r="F788">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G788" t="s">
         <v>11</v>
@@ -22366,7 +22366,7 @@
         <v>10</v>
       </c>
       <c r="F789" s="3">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G789" s="3" t="s">
         <v>11</v>
@@ -22389,7 +22389,7 @@
         <v>10</v>
       </c>
       <c r="F790">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G790" t="s">
         <v>11</v>
@@ -22412,7 +22412,7 @@
         <v>10</v>
       </c>
       <c r="F791" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G791" s="3" t="s">
         <v>11</v>
@@ -22435,7 +22435,7 @@
         <v>10</v>
       </c>
       <c r="F792">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G792" t="s">
         <v>11</v>
@@ -22458,7 +22458,7 @@
         <v>10</v>
       </c>
       <c r="F793" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G793" s="3" t="s">
         <v>11</v>
@@ -22481,7 +22481,7 @@
         <v>10</v>
       </c>
       <c r="F794">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G794" t="s">
         <v>11</v>
@@ -22504,7 +22504,7 @@
         <v>10</v>
       </c>
       <c r="F795" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G795" s="3" t="s">
         <v>11</v>
@@ -22527,7 +22527,7 @@
         <v>10</v>
       </c>
       <c r="F796">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G796" t="s">
         <v>11</v>
@@ -22550,7 +22550,7 @@
         <v>10</v>
       </c>
       <c r="F797" s="3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G797" s="3" t="s">
         <v>11</v>
@@ -22573,7 +22573,7 @@
         <v>10</v>
       </c>
       <c r="F798">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G798" t="s">
         <v>11</v>
@@ -22596,7 +22596,7 @@
         <v>10</v>
       </c>
       <c r="F799" s="3">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G799" s="3" t="s">
         <v>11</v>
@@ -22619,7 +22619,7 @@
         <v>10</v>
       </c>
       <c r="F800">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G800" t="s">
         <v>11</v>
@@ -22642,7 +22642,7 @@
         <v>10</v>
       </c>
       <c r="F801" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G801" s="3" t="s">
         <v>11</v>
@@ -22665,7 +22665,7 @@
         <v>10</v>
       </c>
       <c r="F802">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G802" t="s">
         <v>11</v>
@@ -22711,7 +22711,7 @@
         <v>10</v>
       </c>
       <c r="F804">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G804" t="s">
         <v>11</v>
@@ -22734,7 +22734,7 @@
         <v>10</v>
       </c>
       <c r="F805" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G805" s="3" t="s">
         <v>11</v>
@@ -22757,7 +22757,7 @@
         <v>10</v>
       </c>
       <c r="F806">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G806" t="s">
         <v>11</v>
@@ -22780,7 +22780,7 @@
         <v>10</v>
       </c>
       <c r="F807" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G807" s="3" t="s">
         <v>11</v>
@@ -22826,7 +22826,7 @@
         <v>10</v>
       </c>
       <c r="F809" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G809" s="3" t="s">
         <v>11</v>
@@ -22849,7 +22849,7 @@
         <v>10</v>
       </c>
       <c r="F810">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G810" t="s">
         <v>11</v>
@@ -22872,7 +22872,7 @@
         <v>10</v>
       </c>
       <c r="F811" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G811" s="3" t="s">
         <v>11</v>
@@ -22895,7 +22895,7 @@
         <v>10</v>
       </c>
       <c r="F812">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G812" t="s">
         <v>11</v>
@@ -22964,7 +22964,7 @@
         <v>10</v>
       </c>
       <c r="F815" s="3">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G815" s="3" t="s">
         <v>11</v>
@@ -22987,7 +22987,7 @@
         <v>10</v>
       </c>
       <c r="F816">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G816" t="s">
         <v>11</v>
@@ -23010,7 +23010,7 @@
         <v>10</v>
       </c>
       <c r="F817" s="3">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G817" s="3" t="s">
         <v>11</v>
@@ -23033,7 +23033,7 @@
         <v>10</v>
       </c>
       <c r="F818">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G818" t="s">
         <v>11</v>
@@ -23056,7 +23056,7 @@
         <v>10</v>
       </c>
       <c r="F819" s="3">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G819" s="3" t="s">
         <v>11</v>
@@ -23079,7 +23079,7 @@
         <v>10</v>
       </c>
       <c r="F820">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G820" t="s">
         <v>11</v>
@@ -23102,7 +23102,7 @@
         <v>10</v>
       </c>
       <c r="F821" s="3">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G821" s="3" t="s">
         <v>11</v>
@@ -23125,7 +23125,7 @@
         <v>10</v>
       </c>
       <c r="F822">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G822" t="s">
         <v>11</v>
@@ -23148,7 +23148,7 @@
         <v>10</v>
       </c>
       <c r="F823" s="3">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G823" s="3" t="s">
         <v>11</v>
@@ -23171,7 +23171,7 @@
         <v>10</v>
       </c>
       <c r="F824">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G824" t="s">
         <v>11</v>
@@ -23194,7 +23194,7 @@
         <v>10</v>
       </c>
       <c r="F825" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G825" s="3" t="s">
         <v>11</v>
@@ -23217,7 +23217,7 @@
         <v>10</v>
       </c>
       <c r="F826">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G826" t="s">
         <v>11</v>
@@ -23240,7 +23240,7 @@
         <v>10</v>
       </c>
       <c r="F827" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G827" s="3" t="s">
         <v>11</v>
@@ -23263,7 +23263,7 @@
         <v>10</v>
       </c>
       <c r="F828">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G828" t="s">
         <v>11</v>
@@ -23286,7 +23286,7 @@
         <v>10</v>
       </c>
       <c r="F829" s="3">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G829" s="3" t="s">
         <v>11</v>
@@ -23309,7 +23309,7 @@
         <v>10</v>
       </c>
       <c r="F830">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G830" t="s">
         <v>11</v>
@@ -23332,7 +23332,7 @@
         <v>10</v>
       </c>
       <c r="F831" s="3">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G831" s="3" t="s">
         <v>11</v>
@@ -23355,7 +23355,7 @@
         <v>10</v>
       </c>
       <c r="F832">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G832" t="s">
         <v>11</v>
@@ -23378,7 +23378,7 @@
         <v>10</v>
       </c>
       <c r="F833" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G833" s="3" t="s">
         <v>11</v>
@@ -23401,7 +23401,7 @@
         <v>10</v>
       </c>
       <c r="F834">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G834" t="s">
         <v>11</v>
@@ -23424,7 +23424,7 @@
         <v>10</v>
       </c>
       <c r="F835" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G835" s="3" t="s">
         <v>11</v>
@@ -23447,7 +23447,7 @@
         <v>10</v>
       </c>
       <c r="F836">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G836" t="s">
         <v>11</v>
@@ -23470,7 +23470,7 @@
         <v>10</v>
       </c>
       <c r="F837" s="3">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G837" s="3" t="s">
         <v>11</v>
@@ -23539,7 +23539,7 @@
         <v>10</v>
       </c>
       <c r="F840">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G840" t="s">
         <v>11</v>
@@ -23562,7 +23562,7 @@
         <v>10</v>
       </c>
       <c r="F841" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G841" s="3" t="s">
         <v>11</v>
@@ -23585,7 +23585,7 @@
         <v>10</v>
       </c>
       <c r="F842">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G842" t="s">
         <v>11</v>
@@ -23608,7 +23608,7 @@
         <v>10</v>
       </c>
       <c r="F843" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G843" s="3" t="s">
         <v>11</v>
@@ -23631,7 +23631,7 @@
         <v>10</v>
       </c>
       <c r="F844">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G844" t="s">
         <v>11</v>
@@ -23654,7 +23654,7 @@
         <v>10</v>
       </c>
       <c r="F845" s="3">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G845" s="3" t="s">
         <v>11</v>
@@ -23700,7 +23700,7 @@
         <v>10</v>
       </c>
       <c r="F847" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G847" s="3" t="s">
         <v>11</v>
@@ -23723,7 +23723,7 @@
         <v>10</v>
       </c>
       <c r="F848">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G848" t="s">
         <v>11</v>
@@ -23746,7 +23746,7 @@
         <v>10</v>
       </c>
       <c r="F849" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G849" s="3" t="s">
         <v>11</v>
@@ -23792,7 +23792,7 @@
         <v>10</v>
       </c>
       <c r="F851" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G851" s="3" t="s">
         <v>11</v>
@@ -23815,7 +23815,7 @@
         <v>10</v>
       </c>
       <c r="F852">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G852" t="s">
         <v>11</v>
@@ -23838,7 +23838,7 @@
         <v>10</v>
       </c>
       <c r="F853" s="3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G853" s="3" t="s">
         <v>11</v>
@@ -23861,7 +23861,7 @@
         <v>10</v>
       </c>
       <c r="F854">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G854" t="s">
         <v>11</v>
@@ -23884,7 +23884,7 @@
         <v>10</v>
       </c>
       <c r="F855" s="3">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G855" s="3" t="s">
         <v>11</v>
@@ -23907,7 +23907,7 @@
         <v>10</v>
       </c>
       <c r="F856">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G856" t="s">
         <v>11</v>
@@ -23930,7 +23930,7 @@
         <v>10</v>
       </c>
       <c r="F857" s="3">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G857" s="3" t="s">
         <v>11</v>
@@ -23953,7 +23953,7 @@
         <v>10</v>
       </c>
       <c r="F858">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G858" t="s">
         <v>11</v>
@@ -23976,7 +23976,7 @@
         <v>10</v>
       </c>
       <c r="F859" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G859" s="3" t="s">
         <v>11</v>
@@ -23999,7 +23999,7 @@
         <v>10</v>
       </c>
       <c r="F860">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G860" t="s">
         <v>11</v>
@@ -24022,7 +24022,7 @@
         <v>10</v>
       </c>
       <c r="F861" s="3">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G861" s="3" t="s">
         <v>11</v>
@@ -24045,7 +24045,7 @@
         <v>10</v>
       </c>
       <c r="F862">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G862" t="s">
         <v>11</v>
@@ -24068,7 +24068,7 @@
         <v>10</v>
       </c>
       <c r="F863" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G863" s="3" t="s">
         <v>11</v>
@@ -24091,7 +24091,7 @@
         <v>10</v>
       </c>
       <c r="F864">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G864" t="s">
         <v>11</v>
@@ -24114,7 +24114,7 @@
         <v>10</v>
       </c>
       <c r="F865" s="3">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G865" s="3" t="s">
         <v>11</v>
@@ -24137,7 +24137,7 @@
         <v>10</v>
       </c>
       <c r="F866">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G866" t="s">
         <v>11</v>
@@ -24160,7 +24160,7 @@
         <v>10</v>
       </c>
       <c r="F867" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G867" s="3" t="s">
         <v>11</v>
@@ -24183,7 +24183,7 @@
         <v>10</v>
       </c>
       <c r="F868">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G868" t="s">
         <v>11</v>
@@ -24206,7 +24206,7 @@
         <v>10</v>
       </c>
       <c r="F869" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G869" s="3" t="s">
         <v>11</v>
@@ -24229,7 +24229,7 @@
         <v>10</v>
       </c>
       <c r="F870">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G870" t="s">
         <v>11</v>
@@ -24252,7 +24252,7 @@
         <v>10</v>
       </c>
       <c r="F871" s="3">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G871" s="3" t="s">
         <v>11</v>
@@ -24275,7 +24275,7 @@
         <v>10</v>
       </c>
       <c r="F872">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G872" t="s">
         <v>11</v>
@@ -24298,7 +24298,7 @@
         <v>10</v>
       </c>
       <c r="F873" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G873" s="3" t="s">
         <v>11</v>
@@ -24321,7 +24321,7 @@
         <v>10</v>
       </c>
       <c r="F874">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G874" t="s">
         <v>11</v>
@@ -24344,7 +24344,7 @@
         <v>10</v>
       </c>
       <c r="F875" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G875" s="3" t="s">
         <v>11</v>
@@ -24367,7 +24367,7 @@
         <v>10</v>
       </c>
       <c r="F876">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G876" t="s">
         <v>11</v>
@@ -24390,7 +24390,7 @@
         <v>10</v>
       </c>
       <c r="F877" s="3">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G877" s="3" t="s">
         <v>11</v>
@@ -24413,7 +24413,7 @@
         <v>10</v>
       </c>
       <c r="F878">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G878" t="s">
         <v>11</v>
@@ -24436,7 +24436,7 @@
         <v>10</v>
       </c>
       <c r="F879" s="3">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G879" s="3" t="s">
         <v>11</v>
@@ -24459,7 +24459,7 @@
         <v>10</v>
       </c>
       <c r="F880">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G880" t="s">
         <v>11</v>
@@ -24505,7 +24505,7 @@
         <v>10</v>
       </c>
       <c r="F882">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G882" t="s">
         <v>11</v>
@@ -24528,7 +24528,7 @@
         <v>10</v>
       </c>
       <c r="F883" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G883" s="3" t="s">
         <v>11</v>
@@ -24551,7 +24551,7 @@
         <v>10</v>
       </c>
       <c r="F884">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G884" t="s">
         <v>11</v>
@@ -24574,7 +24574,7 @@
         <v>10</v>
       </c>
       <c r="F885" s="3">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G885" s="3" t="s">
         <v>11</v>
@@ -24597,7 +24597,7 @@
         <v>10</v>
       </c>
       <c r="F886">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G886" t="s">
         <v>11</v>
@@ -24620,7 +24620,7 @@
         <v>10</v>
       </c>
       <c r="F887" s="3">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G887" s="3" t="s">
         <v>11</v>
@@ -24643,7 +24643,7 @@
         <v>10</v>
       </c>
       <c r="F888">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G888" t="s">
         <v>11</v>
@@ -24666,7 +24666,7 @@
         <v>10</v>
       </c>
       <c r="F889" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G889" s="3" t="s">
         <v>11</v>
@@ -24689,7 +24689,7 @@
         <v>10</v>
       </c>
       <c r="F890">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G890" t="s">
         <v>11</v>
@@ -24712,7 +24712,7 @@
         <v>10</v>
       </c>
       <c r="F891" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G891" s="3" t="s">
         <v>11</v>
@@ -24735,7 +24735,7 @@
         <v>10</v>
       </c>
       <c r="F892">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G892" t="s">
         <v>11</v>
@@ -24758,7 +24758,7 @@
         <v>10</v>
       </c>
       <c r="F893" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G893" s="3" t="s">
         <v>11</v>
@@ -24781,7 +24781,7 @@
         <v>10</v>
       </c>
       <c r="F894">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G894" t="s">
         <v>11</v>
@@ -24804,7 +24804,7 @@
         <v>10</v>
       </c>
       <c r="F895" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G895" s="3" t="s">
         <v>11</v>
@@ -24827,7 +24827,7 @@
         <v>10</v>
       </c>
       <c r="F896">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G896" t="s">
         <v>11</v>
@@ -24850,7 +24850,7 @@
         <v>10</v>
       </c>
       <c r="F897" s="3">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G897" s="3" t="s">
         <v>11</v>
@@ -24896,7 +24896,7 @@
         <v>10</v>
       </c>
       <c r="F899" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G899" s="3" t="s">
         <v>11</v>
@@ -24919,7 +24919,7 @@
         <v>10</v>
       </c>
       <c r="F900">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G900" t="s">
         <v>11</v>
@@ -24942,7 +24942,7 @@
         <v>10</v>
       </c>
       <c r="F901" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G901" s="3" t="s">
         <v>11</v>
@@ -24965,7 +24965,7 @@
         <v>10</v>
       </c>
       <c r="F902">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G902" t="s">
         <v>11</v>
@@ -24988,7 +24988,7 @@
         <v>10</v>
       </c>
       <c r="F903" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G903" s="3" t="s">
         <v>11</v>
@@ -25011,7 +25011,7 @@
         <v>10</v>
       </c>
       <c r="F904">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G904" t="s">
         <v>11</v>
@@ -25034,7 +25034,7 @@
         <v>10</v>
       </c>
       <c r="F905" s="3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G905" s="3" t="s">
         <v>11</v>
@@ -25057,7 +25057,7 @@
         <v>10</v>
       </c>
       <c r="F906">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G906" t="s">
         <v>11</v>
@@ -25080,7 +25080,7 @@
         <v>10</v>
       </c>
       <c r="F907" s="3">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G907" s="3" t="s">
         <v>11</v>
@@ -25103,7 +25103,7 @@
         <v>10</v>
       </c>
       <c r="F908">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G908" t="s">
         <v>11</v>
@@ -25126,7 +25126,7 @@
         <v>10</v>
       </c>
       <c r="F909" s="3">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G909" s="3" t="s">
         <v>11</v>
@@ -25149,7 +25149,7 @@
         <v>10</v>
       </c>
       <c r="F910">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G910" t="s">
         <v>11</v>
@@ -25172,7 +25172,7 @@
         <v>10</v>
       </c>
       <c r="F911" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G911" s="3" t="s">
         <v>11</v>
@@ -25195,7 +25195,7 @@
         <v>10</v>
       </c>
       <c r="F912">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G912" t="s">
         <v>11</v>
@@ -25218,7 +25218,7 @@
         <v>10</v>
       </c>
       <c r="F913" s="3">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G913" s="3" t="s">
         <v>11</v>
@@ -25241,7 +25241,7 @@
         <v>10</v>
       </c>
       <c r="F914">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G914" t="s">
         <v>11</v>
@@ -25264,7 +25264,7 @@
         <v>10</v>
       </c>
       <c r="F915" s="3">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G915" s="3" t="s">
         <v>11</v>
@@ -25287,7 +25287,7 @@
         <v>10</v>
       </c>
       <c r="F916">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G916" t="s">
         <v>11</v>
@@ -25310,7 +25310,7 @@
         <v>10</v>
       </c>
       <c r="F917" s="3">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G917" s="3" t="s">
         <v>11</v>
@@ -25333,7 +25333,7 @@
         <v>10</v>
       </c>
       <c r="F918">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G918" t="s">
         <v>11</v>
@@ -25356,7 +25356,7 @@
         <v>10</v>
       </c>
       <c r="F919" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G919" s="3" t="s">
         <v>11</v>
@@ -25379,7 +25379,7 @@
         <v>10</v>
       </c>
       <c r="F920">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G920" t="s">
         <v>11</v>
@@ -25402,7 +25402,7 @@
         <v>10</v>
       </c>
       <c r="F921" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G921" s="3" t="s">
         <v>11</v>
@@ -25425,7 +25425,7 @@
         <v>10</v>
       </c>
       <c r="F922">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G922" t="s">
         <v>11</v>
@@ -25471,7 +25471,7 @@
         <v>10</v>
       </c>
       <c r="F924">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G924" t="s">
         <v>11</v>
@@ -25494,7 +25494,7 @@
         <v>10</v>
       </c>
       <c r="F925" s="3">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G925" s="3" t="s">
         <v>11</v>
@@ -25540,7 +25540,7 @@
         <v>10</v>
       </c>
       <c r="F927" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G927" s="3" t="s">
         <v>11</v>
@@ -25563,7 +25563,7 @@
         <v>10</v>
       </c>
       <c r="F928">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G928" t="s">
         <v>11</v>
@@ -25586,7 +25586,7 @@
         <v>10</v>
       </c>
       <c r="F929" s="3">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G929" s="3" t="s">
         <v>11</v>
@@ -25609,7 +25609,7 @@
         <v>10</v>
       </c>
       <c r="F930">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G930" t="s">
         <v>11</v>
@@ -25632,7 +25632,7 @@
         <v>10</v>
       </c>
       <c r="F931" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G931" s="3" t="s">
         <v>11</v>
@@ -25678,7 +25678,7 @@
         <v>10</v>
       </c>
       <c r="F933" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G933" s="3" t="s">
         <v>11</v>
@@ -25701,7 +25701,7 @@
         <v>10</v>
       </c>
       <c r="F934">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G934" t="s">
         <v>11</v>
@@ -25724,7 +25724,7 @@
         <v>10</v>
       </c>
       <c r="F935" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G935" s="3" t="s">
         <v>11</v>
@@ -25747,7 +25747,7 @@
         <v>10</v>
       </c>
       <c r="F936">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G936" t="s">
         <v>11</v>
@@ -25770,7 +25770,7 @@
         <v>10</v>
       </c>
       <c r="F937" s="3">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G937" s="3" t="s">
         <v>11</v>
@@ -25793,7 +25793,7 @@
         <v>10</v>
       </c>
       <c r="F938">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G938" t="s">
         <v>11</v>
@@ -25816,7 +25816,7 @@
         <v>10</v>
       </c>
       <c r="F939" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G939" s="3" t="s">
         <v>11</v>
@@ -25862,7 +25862,7 @@
         <v>10</v>
       </c>
       <c r="F941" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G941" s="3" t="s">
         <v>11</v>
@@ -25885,7 +25885,7 @@
         <v>10</v>
       </c>
       <c r="F942">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G942" t="s">
         <v>11</v>
@@ -25908,7 +25908,7 @@
         <v>10</v>
       </c>
       <c r="F943" s="3">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G943" s="3" t="s">
         <v>11</v>
@@ -25931,7 +25931,7 @@
         <v>10</v>
       </c>
       <c r="F944">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G944" t="s">
         <v>11</v>
@@ -25954,7 +25954,7 @@
         <v>10</v>
       </c>
       <c r="F945" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G945" s="3" t="s">
         <v>11</v>
@@ -25977,7 +25977,7 @@
         <v>10</v>
       </c>
       <c r="F946">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G946" t="s">
         <v>11</v>
@@ -26000,7 +26000,7 @@
         <v>10</v>
       </c>
       <c r="F947" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G947" s="3" t="s">
         <v>11</v>
@@ -26023,7 +26023,7 @@
         <v>10</v>
       </c>
       <c r="F948">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G948" t="s">
         <v>11</v>
@@ -26046,7 +26046,7 @@
         <v>10</v>
       </c>
       <c r="F949" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G949" s="3" t="s">
         <v>11</v>
@@ -26069,7 +26069,7 @@
         <v>10</v>
       </c>
       <c r="F950">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G950" t="s">
         <v>11</v>
@@ -26092,7 +26092,7 @@
         <v>10</v>
       </c>
       <c r="F951" s="3">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G951" s="3" t="s">
         <v>11</v>
@@ -26115,7 +26115,7 @@
         <v>10</v>
       </c>
       <c r="F952">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G952" t="s">
         <v>11</v>
@@ -26138,7 +26138,7 @@
         <v>10</v>
       </c>
       <c r="F953" s="3">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G953" s="3" t="s">
         <v>11</v>
@@ -26161,7 +26161,7 @@
         <v>10</v>
       </c>
       <c r="F954">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G954" t="s">
         <v>11</v>
@@ -26184,7 +26184,7 @@
         <v>10</v>
       </c>
       <c r="F955" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G955" s="3" t="s">
         <v>11</v>
@@ -26207,7 +26207,7 @@
         <v>10</v>
       </c>
       <c r="F956">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G956" t="s">
         <v>11</v>
@@ -26230,7 +26230,7 @@
         <v>10</v>
       </c>
       <c r="F957" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G957" s="3" t="s">
         <v>11</v>
@@ -26253,7 +26253,7 @@
         <v>10</v>
       </c>
       <c r="F958">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G958" t="s">
         <v>11</v>
@@ -26276,7 +26276,7 @@
         <v>10</v>
       </c>
       <c r="F959" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G959" s="3" t="s">
         <v>11</v>
@@ -26299,7 +26299,7 @@
         <v>10</v>
       </c>
       <c r="F960">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G960" t="s">
         <v>11</v>
@@ -26322,7 +26322,7 @@
         <v>10</v>
       </c>
       <c r="F961" s="3">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G961" s="3" t="s">
         <v>11</v>
@@ -26345,7 +26345,7 @@
         <v>10</v>
       </c>
       <c r="F962">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G962" t="s">
         <v>11</v>
@@ -26368,7 +26368,7 @@
         <v>10</v>
       </c>
       <c r="F963" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G963" s="3" t="s">
         <v>11</v>
@@ -26391,7 +26391,7 @@
         <v>10</v>
       </c>
       <c r="F964">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G964" t="s">
         <v>11</v>
@@ -26437,7 +26437,7 @@
         <v>10</v>
       </c>
       <c r="F966">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G966" t="s">
         <v>11</v>
@@ -26460,7 +26460,7 @@
         <v>10</v>
       </c>
       <c r="F967" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G967" s="3" t="s">
         <v>11</v>
@@ -26483,7 +26483,7 @@
         <v>10</v>
       </c>
       <c r="F968">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G968" t="s">
         <v>11</v>
@@ -26506,7 +26506,7 @@
         <v>10</v>
       </c>
       <c r="F969" s="3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G969" s="3" t="s">
         <v>11</v>
@@ -26552,7 +26552,7 @@
         <v>10</v>
       </c>
       <c r="F971" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G971" s="3" t="s">
         <v>11</v>
@@ -26575,7 +26575,7 @@
         <v>10</v>
       </c>
       <c r="F972">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G972" t="s">
         <v>11</v>
@@ -26598,7 +26598,7 @@
         <v>10</v>
       </c>
       <c r="F973" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G973" s="3" t="s">
         <v>11</v>
@@ -26644,7 +26644,7 @@
         <v>10</v>
       </c>
       <c r="F975" s="3">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G975" s="3" t="s">
         <v>11</v>
@@ -26713,7 +26713,7 @@
         <v>10</v>
       </c>
       <c r="F978">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G978" t="s">
         <v>11</v>
@@ -26736,7 +26736,7 @@
         <v>10</v>
       </c>
       <c r="F979" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G979" s="3" t="s">
         <v>11</v>
@@ -26759,7 +26759,7 @@
         <v>10</v>
       </c>
       <c r="F980">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G980" t="s">
         <v>11</v>
@@ -26782,7 +26782,7 @@
         <v>10</v>
       </c>
       <c r="F981" s="3">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G981" s="3" t="s">
         <v>11</v>
@@ -26874,7 +26874,7 @@
         <v>10</v>
       </c>
       <c r="F985" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G985" s="3" t="s">
         <v>11</v>
@@ -26897,7 +26897,7 @@
         <v>10</v>
       </c>
       <c r="F986">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G986" t="s">
         <v>11</v>
@@ -26920,7 +26920,7 @@
         <v>10</v>
       </c>
       <c r="F987" s="3">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G987" s="3" t="s">
         <v>11</v>
@@ -26966,7 +26966,7 @@
         <v>10</v>
       </c>
       <c r="F989" s="3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G989" s="3" t="s">
         <v>11</v>
@@ -26989,7 +26989,7 @@
         <v>10</v>
       </c>
       <c r="F990">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G990" t="s">
         <v>11</v>
@@ -27012,7 +27012,7 @@
         <v>10</v>
       </c>
       <c r="F991" s="3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G991" s="3" t="s">
         <v>11</v>
@@ -27035,7 +27035,7 @@
         <v>10</v>
       </c>
       <c r="F992">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G992" t="s">
         <v>11</v>
@@ -27058,7 +27058,7 @@
         <v>10</v>
       </c>
       <c r="F993" s="3">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G993" s="3" t="s">
         <v>11</v>
@@ -27104,7 +27104,7 @@
         <v>10</v>
       </c>
       <c r="F995" s="3">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G995" s="3" t="s">
         <v>11</v>
@@ -27127,7 +27127,7 @@
         <v>10</v>
       </c>
       <c r="F996">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G996" t="s">
         <v>11</v>
@@ -27150,7 +27150,7 @@
         <v>10</v>
       </c>
       <c r="F997" s="3">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G997" s="3" t="s">
         <v>11</v>
@@ -27173,7 +27173,7 @@
         <v>10</v>
       </c>
       <c r="F998">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G998" t="s">
         <v>11</v>
@@ -27196,7 +27196,7 @@
         <v>10</v>
       </c>
       <c r="F999" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G999" s="3" t="s">
         <v>11</v>
@@ -27219,7 +27219,7 @@
         <v>10</v>
       </c>
       <c r="F1000">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G1000" t="s">
         <v>11</v>
@@ -27242,7 +27242,7 @@
         <v>10</v>
       </c>
       <c r="F1001" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G1001" s="3" t="s">
         <v>11</v>
@@ -27265,7 +27265,7 @@
         <v>10</v>
       </c>
       <c r="F1002">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G1002" t="s">
         <v>11</v>
@@ -27288,7 +27288,7 @@
         <v>10</v>
       </c>
       <c r="F1003" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G1003" s="3" t="s">
         <v>11</v>
@@ -27311,7 +27311,7 @@
         <v>10</v>
       </c>
       <c r="F1004">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G1004" t="s">
         <v>11</v>
@@ -27334,7 +27334,7 @@
         <v>10</v>
       </c>
       <c r="F1005" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G1005" s="3" t="s">
         <v>11</v>
@@ -27357,7 +27357,7 @@
         <v>10</v>
       </c>
       <c r="F1006">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G1006" t="s">
         <v>11</v>
@@ -27380,7 +27380,7 @@
         <v>10</v>
       </c>
       <c r="F1007" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1007" s="3" t="s">
         <v>11</v>
@@ -27403,7 +27403,7 @@
         <v>10</v>
       </c>
       <c r="F1008">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G1008" t="s">
         <v>11</v>
@@ -27449,7 +27449,7 @@
         <v>10</v>
       </c>
       <c r="F1010">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G1010" t="s">
         <v>11</v>
@@ -27472,7 +27472,7 @@
         <v>10</v>
       </c>
       <c r="F1011" s="3">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G1011" s="3" t="s">
         <v>11</v>
@@ -27495,7 +27495,7 @@
         <v>10</v>
       </c>
       <c r="F1012">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G1012" t="s">
         <v>11</v>
@@ -27518,7 +27518,7 @@
         <v>10</v>
       </c>
       <c r="F1013" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G1013" s="3" t="s">
         <v>11</v>
@@ -27541,7 +27541,7 @@
         <v>10</v>
       </c>
       <c r="F1014">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G1014" t="s">
         <v>11</v>
@@ -27564,7 +27564,7 @@
         <v>10</v>
       </c>
       <c r="F1015" s="3">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G1015" s="3" t="s">
         <v>11</v>
@@ -27587,7 +27587,7 @@
         <v>10</v>
       </c>
       <c r="F1016">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G1016" t="s">
         <v>11</v>
@@ -27656,7 +27656,7 @@
         <v>10</v>
       </c>
       <c r="F1019" s="3">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G1019" s="3" t="s">
         <v>11</v>
@@ -27679,7 +27679,7 @@
         <v>10</v>
       </c>
       <c r="F1020">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G1020" t="s">
         <v>11</v>
@@ -27702,7 +27702,7 @@
         <v>10</v>
       </c>
       <c r="F1021" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G1021" s="3" t="s">
         <v>11</v>
@@ -27725,7 +27725,7 @@
         <v>10</v>
       </c>
       <c r="F1022">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G1022" t="s">
         <v>11</v>
@@ -27748,7 +27748,7 @@
         <v>10</v>
       </c>
       <c r="F1023" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G1023" s="3" t="s">
         <v>11</v>
@@ -27771,7 +27771,7 @@
         <v>10</v>
       </c>
       <c r="F1024">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G1024" t="s">
         <v>11</v>
@@ -27794,7 +27794,7 @@
         <v>10</v>
       </c>
       <c r="F1025" s="3">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G1025" s="3" t="s">
         <v>11</v>
@@ -27817,7 +27817,7 @@
         <v>10</v>
       </c>
       <c r="F1026">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G1026" t="s">
         <v>11</v>
@@ -27840,7 +27840,7 @@
         <v>10</v>
       </c>
       <c r="F1027" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G1027" s="3" t="s">
         <v>11</v>
@@ -27863,7 +27863,7 @@
         <v>10</v>
       </c>
       <c r="F1028">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G1028" t="s">
         <v>11</v>
@@ -27886,7 +27886,7 @@
         <v>10</v>
       </c>
       <c r="F1029" s="3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G1029" s="3" t="s">
         <v>11</v>
@@ -27909,7 +27909,7 @@
         <v>10</v>
       </c>
       <c r="F1030">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G1030" t="s">
         <v>11</v>
@@ -27932,7 +27932,7 @@
         <v>10</v>
       </c>
       <c r="F1031" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G1031" s="3" t="s">
         <v>11</v>
@@ -27955,7 +27955,7 @@
         <v>10</v>
       </c>
       <c r="F1032">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G1032" t="s">
         <v>11</v>
@@ -27978,7 +27978,7 @@
         <v>10</v>
       </c>
       <c r="F1033" s="3">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G1033" s="3" t="s">
         <v>11</v>
@@ -28001,7 +28001,7 @@
         <v>10</v>
       </c>
       <c r="F1034">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G1034" t="s">
         <v>11</v>
@@ -28024,7 +28024,7 @@
         <v>10</v>
       </c>
       <c r="F1035" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G1035" s="3" t="s">
         <v>11</v>
@@ -28047,7 +28047,7 @@
         <v>10</v>
       </c>
       <c r="F1036">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G1036" t="s">
         <v>11</v>
@@ -28070,7 +28070,7 @@
         <v>10</v>
       </c>
       <c r="F1037" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G1037" s="3" t="s">
         <v>11</v>
@@ -28093,7 +28093,7 @@
         <v>10</v>
       </c>
       <c r="F1038">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G1038" t="s">
         <v>11</v>
@@ -28116,7 +28116,7 @@
         <v>10</v>
       </c>
       <c r="F1039" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G1039" s="3" t="s">
         <v>11</v>
@@ -28139,7 +28139,7 @@
         <v>10</v>
       </c>
       <c r="F1040">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1040" t="s">
         <v>11</v>
@@ -28185,7 +28185,7 @@
         <v>10</v>
       </c>
       <c r="F1042">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G1042" t="s">
         <v>11</v>
@@ -28208,7 +28208,7 @@
         <v>10</v>
       </c>
       <c r="F1043" s="3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G1043" s="3" t="s">
         <v>11</v>
@@ -28231,7 +28231,7 @@
         <v>10</v>
       </c>
       <c r="F1044">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G1044" t="s">
         <v>11</v>
@@ -28254,7 +28254,7 @@
         <v>10</v>
       </c>
       <c r="F1045" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G1045" s="3" t="s">
         <v>11</v>
@@ -28277,7 +28277,7 @@
         <v>10</v>
       </c>
       <c r="F1046">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G1046" t="s">
         <v>11</v>
@@ -28300,7 +28300,7 @@
         <v>10</v>
       </c>
       <c r="F1047" s="3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G1047" s="3" t="s">
         <v>11</v>
@@ -28323,7 +28323,7 @@
         <v>10</v>
       </c>
       <c r="F1048">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G1048" t="s">
         <v>11</v>
@@ -28346,7 +28346,7 @@
         <v>10</v>
       </c>
       <c r="F1049" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G1049" s="3" t="s">
         <v>11</v>
@@ -28369,7 +28369,7 @@
         <v>10</v>
       </c>
       <c r="F1050">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G1050" t="s">
         <v>11</v>
@@ -28392,7 +28392,7 @@
         <v>10</v>
       </c>
       <c r="F1051" s="3">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G1051" s="3" t="s">
         <v>11</v>
@@ -28415,7 +28415,7 @@
         <v>10</v>
       </c>
       <c r="F1052">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G1052" t="s">
         <v>11</v>
@@ -28438,7 +28438,7 @@
         <v>10</v>
       </c>
       <c r="F1053" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G1053" s="3" t="s">
         <v>11</v>
@@ -28461,7 +28461,7 @@
         <v>10</v>
       </c>
       <c r="F1054">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G1054" t="s">
         <v>11</v>
@@ -28484,7 +28484,7 @@
         <v>10</v>
       </c>
       <c r="F1055" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G1055" s="3" t="s">
         <v>11</v>
@@ -28507,7 +28507,7 @@
         <v>10</v>
       </c>
       <c r="F1056">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G1056" t="s">
         <v>11</v>
@@ -28530,7 +28530,7 @@
         <v>10</v>
       </c>
       <c r="F1057" s="3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G1057" s="3" t="s">
         <v>11</v>
@@ -28576,7 +28576,7 @@
         <v>10</v>
       </c>
       <c r="F1059" s="3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G1059" s="3" t="s">
         <v>11</v>
@@ -28599,7 +28599,7 @@
         <v>10</v>
       </c>
       <c r="F1060">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G1060" t="s">
         <v>11</v>
@@ -28622,7 +28622,7 @@
         <v>10</v>
       </c>
       <c r="F1061" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G1061" s="3" t="s">
         <v>11</v>
@@ -28645,7 +28645,7 @@
         <v>10</v>
       </c>
       <c r="F1062">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G1062" t="s">
         <v>11</v>
@@ -28668,7 +28668,7 @@
         <v>10</v>
       </c>
       <c r="F1063" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G1063" s="3" t="s">
         <v>11</v>
@@ -28691,7 +28691,7 @@
         <v>10</v>
       </c>
       <c r="F1064">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G1064" t="s">
         <v>11</v>
@@ -28714,7 +28714,7 @@
         <v>10</v>
       </c>
       <c r="F1065" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G1065" s="3" t="s">
         <v>11</v>
@@ -28737,7 +28737,7 @@
         <v>10</v>
       </c>
       <c r="F1066">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G1066" t="s">
         <v>11</v>
@@ -28760,7 +28760,7 @@
         <v>10</v>
       </c>
       <c r="F1067" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G1067" s="3" t="s">
         <v>11</v>
@@ -28806,7 +28806,7 @@
         <v>10</v>
       </c>
       <c r="F1069" s="3">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G1069" s="3" t="s">
         <v>11</v>
@@ -28829,7 +28829,7 @@
         <v>10</v>
       </c>
       <c r="F1070">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G1070" t="s">
         <v>11</v>
@@ -28852,7 +28852,7 @@
         <v>10</v>
       </c>
       <c r="F1071" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G1071" s="3" t="s">
         <v>11</v>
@@ -28875,7 +28875,7 @@
         <v>10</v>
       </c>
       <c r="F1072">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G1072" t="s">
         <v>11</v>
@@ -28898,7 +28898,7 @@
         <v>10</v>
       </c>
       <c r="F1073" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1073" s="3" t="s">
         <v>11</v>
@@ -28921,7 +28921,7 @@
         <v>10</v>
       </c>
       <c r="F1074">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1074" t="s">
         <v>11</v>
@@ -28944,7 +28944,7 @@
         <v>10</v>
       </c>
       <c r="F1075" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G1075" s="3" t="s">
         <v>11</v>
@@ -28990,7 +28990,7 @@
         <v>10</v>
       </c>
       <c r="F1077" s="3">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G1077" s="3" t="s">
         <v>11</v>
@@ -29013,7 +29013,7 @@
         <v>10</v>
       </c>
       <c r="F1078">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G1078" t="s">
         <v>11</v>
@@ -29036,7 +29036,7 @@
         <v>10</v>
       </c>
       <c r="F1079" s="3">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G1079" s="3" t="s">
         <v>11</v>
@@ -29059,7 +29059,7 @@
         <v>10</v>
       </c>
       <c r="F1080">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G1080" t="s">
         <v>11</v>
@@ -29082,7 +29082,7 @@
         <v>10</v>
       </c>
       <c r="F1081" s="3">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G1081" s="3" t="s">
         <v>11</v>
@@ -29105,7 +29105,7 @@
         <v>10</v>
       </c>
       <c r="F1082">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G1082" t="s">
         <v>11</v>
@@ -29128,7 +29128,7 @@
         <v>10</v>
       </c>
       <c r="F1083" s="3">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G1083" s="3" t="s">
         <v>11</v>
@@ -29151,7 +29151,7 @@
         <v>10</v>
       </c>
       <c r="F1084">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G1084" t="s">
         <v>11</v>
@@ -29197,7 +29197,7 @@
         <v>10</v>
       </c>
       <c r="F1086">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G1086" t="s">
         <v>11</v>
@@ -29220,7 +29220,7 @@
         <v>10</v>
       </c>
       <c r="F1087" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G1087" s="3" t="s">
         <v>11</v>
@@ -29243,7 +29243,7 @@
         <v>10</v>
       </c>
       <c r="F1088">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G1088" t="s">
         <v>11</v>
@@ -29266,7 +29266,7 @@
         <v>10</v>
       </c>
       <c r="F1089" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1089" s="3" t="s">
         <v>11</v>
@@ -29289,7 +29289,7 @@
         <v>10</v>
       </c>
       <c r="F1090">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G1090" t="s">
         <v>11</v>
@@ -29312,7 +29312,7 @@
         <v>10</v>
       </c>
       <c r="F1091" s="3">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G1091" s="3" t="s">
         <v>11</v>
@@ -29335,7 +29335,7 @@
         <v>10</v>
       </c>
       <c r="F1092">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1092" t="s">
         <v>11</v>
@@ -29358,7 +29358,7 @@
         <v>10</v>
       </c>
       <c r="F1093" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G1093" s="3" t="s">
         <v>11</v>
@@ -29381,7 +29381,7 @@
         <v>10</v>
       </c>
       <c r="F1094">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G1094" t="s">
         <v>11</v>
@@ -29404,7 +29404,7 @@
         <v>10</v>
       </c>
       <c r="F1095" s="3">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G1095" s="3" t="s">
         <v>11</v>
@@ -29427,7 +29427,7 @@
         <v>10</v>
       </c>
       <c r="F1096">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G1096" t="s">
         <v>11</v>
@@ -29450,7 +29450,7 @@
         <v>10</v>
       </c>
       <c r="F1097" s="3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G1097" s="3" t="s">
         <v>11</v>
@@ -29496,7 +29496,7 @@
         <v>10</v>
       </c>
       <c r="F1099" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G1099" s="3" t="s">
         <v>11</v>
@@ -29519,7 +29519,7 @@
         <v>10</v>
       </c>
       <c r="F1100">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G1100" t="s">
         <v>11</v>
@@ -29542,7 +29542,7 @@
         <v>10</v>
       </c>
       <c r="F1101" s="3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G1101" s="3" t="s">
         <v>11</v>

--- a/Test_Results/Excel/selenium-report.xlsx
+++ b/Test_Results/Excel/selenium-report.xlsx
@@ -4265,7 +4265,7 @@
         <v>10</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G2" t="s">
         <v>11</v>
@@ -4288,7 +4288,7 @@
         <v>10</v>
       </c>
       <c r="F3" s="3">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>11</v>
@@ -4311,7 +4311,7 @@
         <v>10</v>
       </c>
       <c r="F4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G4" t="s">
         <v>11</v>
@@ -4357,7 +4357,7 @@
         <v>10</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G6" t="s">
         <v>11</v>
@@ -4380,7 +4380,7 @@
         <v>10</v>
       </c>
       <c r="F7" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>11</v>
@@ -4403,7 +4403,7 @@
         <v>10</v>
       </c>
       <c r="F8">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G8" t="s">
         <v>11</v>
@@ -4426,7 +4426,7 @@
         <v>10</v>
       </c>
       <c r="F9" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>11</v>
@@ -4449,7 +4449,7 @@
         <v>10</v>
       </c>
       <c r="F10">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G10" t="s">
         <v>11</v>
@@ -4472,7 +4472,7 @@
         <v>10</v>
       </c>
       <c r="F11" s="3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>11</v>
@@ -4495,7 +4495,7 @@
         <v>10</v>
       </c>
       <c r="F12">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G12" t="s">
         <v>11</v>
@@ -4518,7 +4518,7 @@
         <v>10</v>
       </c>
       <c r="F13" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>11</v>
@@ -4541,7 +4541,7 @@
         <v>10</v>
       </c>
       <c r="F14">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G14" t="s">
         <v>11</v>
@@ -4564,7 +4564,7 @@
         <v>10</v>
       </c>
       <c r="F15" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>11</v>
@@ -4610,7 +4610,7 @@
         <v>10</v>
       </c>
       <c r="F17" s="3">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>11</v>
@@ -4633,7 +4633,7 @@
         <v>10</v>
       </c>
       <c r="F18">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G18" t="s">
         <v>11</v>
@@ -4656,7 +4656,7 @@
         <v>10</v>
       </c>
       <c r="F19" s="3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>11</v>
@@ -4702,7 +4702,7 @@
         <v>10</v>
       </c>
       <c r="F21" s="3">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>11</v>
@@ -4725,7 +4725,7 @@
         <v>10</v>
       </c>
       <c r="F22">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G22" t="s">
         <v>11</v>
@@ -4748,7 +4748,7 @@
         <v>10</v>
       </c>
       <c r="F23" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>11</v>
@@ -4771,7 +4771,7 @@
         <v>10</v>
       </c>
       <c r="F24">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G24" t="s">
         <v>11</v>
@@ -4794,7 +4794,7 @@
         <v>10</v>
       </c>
       <c r="F25" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>11</v>
@@ -4817,7 +4817,7 @@
         <v>10</v>
       </c>
       <c r="F26">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G26" t="s">
         <v>11</v>
@@ -4863,7 +4863,7 @@
         <v>10</v>
       </c>
       <c r="F28">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G28" t="s">
         <v>11</v>
@@ -4886,7 +4886,7 @@
         <v>10</v>
       </c>
       <c r="F29" s="3">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>11</v>
@@ -4909,7 +4909,7 @@
         <v>10</v>
       </c>
       <c r="F30">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G30" t="s">
         <v>11</v>
@@ -4932,7 +4932,7 @@
         <v>10</v>
       </c>
       <c r="F31" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>11</v>
@@ -4955,7 +4955,7 @@
         <v>10</v>
       </c>
       <c r="F32">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G32" t="s">
         <v>11</v>
@@ -4978,7 +4978,7 @@
         <v>10</v>
       </c>
       <c r="F33" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>11</v>
@@ -5001,7 +5001,7 @@
         <v>10</v>
       </c>
       <c r="F34">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G34" t="s">
         <v>11</v>
@@ -5024,7 +5024,7 @@
         <v>10</v>
       </c>
       <c r="F35" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>11</v>
@@ -5070,7 +5070,7 @@
         <v>10</v>
       </c>
       <c r="F37" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>11</v>
@@ -5093,7 +5093,7 @@
         <v>10</v>
       </c>
       <c r="F38">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G38" t="s">
         <v>11</v>
@@ -5116,7 +5116,7 @@
         <v>10</v>
       </c>
       <c r="F39" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G39" s="3" t="s">
         <v>11</v>
@@ -5139,7 +5139,7 @@
         <v>10</v>
       </c>
       <c r="F40">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G40" t="s">
         <v>11</v>
@@ -5162,7 +5162,7 @@
         <v>10</v>
       </c>
       <c r="F41" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>11</v>
@@ -5185,7 +5185,7 @@
         <v>10</v>
       </c>
       <c r="F42">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G42" t="s">
         <v>11</v>
@@ -5208,7 +5208,7 @@
         <v>10</v>
       </c>
       <c r="F43" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>11</v>
@@ -5231,7 +5231,7 @@
         <v>10</v>
       </c>
       <c r="F44">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G44" t="s">
         <v>11</v>
@@ -5254,7 +5254,7 @@
         <v>10</v>
       </c>
       <c r="F45" s="3">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>11</v>
@@ -5277,7 +5277,7 @@
         <v>10</v>
       </c>
       <c r="F46">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G46" t="s">
         <v>11</v>
@@ -5300,7 +5300,7 @@
         <v>10</v>
       </c>
       <c r="F47" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>11</v>
@@ -5323,7 +5323,7 @@
         <v>10</v>
       </c>
       <c r="F48">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G48" t="s">
         <v>11</v>
@@ -5346,7 +5346,7 @@
         <v>10</v>
       </c>
       <c r="F49" s="3">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>11</v>
@@ -5369,7 +5369,7 @@
         <v>10</v>
       </c>
       <c r="F50">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G50" t="s">
         <v>11</v>
@@ -5392,7 +5392,7 @@
         <v>10</v>
       </c>
       <c r="F51" s="3">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>11</v>
@@ -5415,7 +5415,7 @@
         <v>10</v>
       </c>
       <c r="F52">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G52" t="s">
         <v>11</v>
@@ -5438,7 +5438,7 @@
         <v>10</v>
       </c>
       <c r="F53" s="3">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G53" s="3" t="s">
         <v>11</v>
@@ -5461,7 +5461,7 @@
         <v>10</v>
       </c>
       <c r="F54">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G54" t="s">
         <v>11</v>
@@ -5484,7 +5484,7 @@
         <v>10</v>
       </c>
       <c r="F55" s="3">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G55" s="3" t="s">
         <v>11</v>
@@ -5530,7 +5530,7 @@
         <v>10</v>
       </c>
       <c r="F57" s="3">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G57" s="3" t="s">
         <v>11</v>
@@ -5553,7 +5553,7 @@
         <v>10</v>
       </c>
       <c r="F58">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G58" t="s">
         <v>11</v>
@@ -5576,7 +5576,7 @@
         <v>10</v>
       </c>
       <c r="F59" s="3">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G59" s="3" t="s">
         <v>11</v>
@@ -5599,7 +5599,7 @@
         <v>10</v>
       </c>
       <c r="F60">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G60" t="s">
         <v>11</v>
@@ -5622,7 +5622,7 @@
         <v>10</v>
       </c>
       <c r="F61" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G61" s="3" t="s">
         <v>11</v>
@@ -5645,7 +5645,7 @@
         <v>10</v>
       </c>
       <c r="F62">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G62" t="s">
         <v>11</v>
@@ -5668,7 +5668,7 @@
         <v>10</v>
       </c>
       <c r="F63" s="3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G63" s="3" t="s">
         <v>11</v>
@@ -5691,7 +5691,7 @@
         <v>10</v>
       </c>
       <c r="F64">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G64" t="s">
         <v>11</v>
@@ -5714,7 +5714,7 @@
         <v>10</v>
       </c>
       <c r="F65" s="3">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G65" s="3" t="s">
         <v>11</v>
@@ -5737,7 +5737,7 @@
         <v>10</v>
       </c>
       <c r="F66">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G66" t="s">
         <v>11</v>
@@ -5760,7 +5760,7 @@
         <v>10</v>
       </c>
       <c r="F67" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G67" s="3" t="s">
         <v>11</v>
@@ -5783,7 +5783,7 @@
         <v>10</v>
       </c>
       <c r="F68">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G68" t="s">
         <v>11</v>
@@ -5806,7 +5806,7 @@
         <v>10</v>
       </c>
       <c r="F69" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G69" s="3" t="s">
         <v>11</v>
@@ -5829,7 +5829,7 @@
         <v>10</v>
       </c>
       <c r="F70">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G70" t="s">
         <v>11</v>
@@ -5852,7 +5852,7 @@
         <v>10</v>
       </c>
       <c r="F71" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G71" s="3" t="s">
         <v>11</v>
@@ -5875,7 +5875,7 @@
         <v>10</v>
       </c>
       <c r="F72">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G72" t="s">
         <v>11</v>
@@ -5898,7 +5898,7 @@
         <v>10</v>
       </c>
       <c r="F73" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G73" s="3" t="s">
         <v>11</v>
@@ -5921,7 +5921,7 @@
         <v>10</v>
       </c>
       <c r="F74">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G74" t="s">
         <v>11</v>
@@ -5944,7 +5944,7 @@
         <v>10</v>
       </c>
       <c r="F75" s="3">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G75" s="3" t="s">
         <v>11</v>
@@ -5967,7 +5967,7 @@
         <v>10</v>
       </c>
       <c r="F76">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G76" t="s">
         <v>11</v>
@@ -5990,7 +5990,7 @@
         <v>10</v>
       </c>
       <c r="F77" s="3">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G77" s="3" t="s">
         <v>11</v>
@@ -6013,7 +6013,7 @@
         <v>10</v>
       </c>
       <c r="F78">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G78" t="s">
         <v>11</v>
@@ -6036,7 +6036,7 @@
         <v>10</v>
       </c>
       <c r="F79" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G79" s="3" t="s">
         <v>11</v>
@@ -6059,7 +6059,7 @@
         <v>10</v>
       </c>
       <c r="F80">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G80" t="s">
         <v>11</v>
@@ -6082,7 +6082,7 @@
         <v>10</v>
       </c>
       <c r="F81" s="3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G81" s="3" t="s">
         <v>11</v>
@@ -6105,7 +6105,7 @@
         <v>10</v>
       </c>
       <c r="F82">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G82" t="s">
         <v>11</v>
@@ -6128,7 +6128,7 @@
         <v>10</v>
       </c>
       <c r="F83" s="3">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G83" s="3" t="s">
         <v>11</v>
@@ -6151,7 +6151,7 @@
         <v>10</v>
       </c>
       <c r="F84">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G84" t="s">
         <v>11</v>
@@ -6174,7 +6174,7 @@
         <v>10</v>
       </c>
       <c r="F85" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G85" s="3" t="s">
         <v>11</v>
@@ -6197,7 +6197,7 @@
         <v>10</v>
       </c>
       <c r="F86">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G86" t="s">
         <v>11</v>
@@ -6220,7 +6220,7 @@
         <v>10</v>
       </c>
       <c r="F87" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G87" s="3" t="s">
         <v>11</v>
@@ -6243,7 +6243,7 @@
         <v>10</v>
       </c>
       <c r="F88">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G88" t="s">
         <v>11</v>
@@ -6266,7 +6266,7 @@
         <v>10</v>
       </c>
       <c r="F89" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G89" s="3" t="s">
         <v>11</v>
@@ -6289,7 +6289,7 @@
         <v>10</v>
       </c>
       <c r="F90">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G90" t="s">
         <v>11</v>
@@ -6312,7 +6312,7 @@
         <v>10</v>
       </c>
       <c r="F91" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G91" s="3" t="s">
         <v>11</v>
@@ -6335,7 +6335,7 @@
         <v>10</v>
       </c>
       <c r="F92">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G92" t="s">
         <v>11</v>
@@ -6358,7 +6358,7 @@
         <v>10</v>
       </c>
       <c r="F93" s="3">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G93" s="3" t="s">
         <v>11</v>
@@ -6404,7 +6404,7 @@
         <v>10</v>
       </c>
       <c r="F95" s="3">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G95" s="3" t="s">
         <v>11</v>
@@ -6427,7 +6427,7 @@
         <v>10</v>
       </c>
       <c r="F96">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G96" t="s">
         <v>11</v>
@@ -6450,7 +6450,7 @@
         <v>10</v>
       </c>
       <c r="F97" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G97" s="3" t="s">
         <v>11</v>
@@ -6473,7 +6473,7 @@
         <v>10</v>
       </c>
       <c r="F98">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G98" t="s">
         <v>11</v>
@@ -6496,7 +6496,7 @@
         <v>10</v>
       </c>
       <c r="F99" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G99" s="3" t="s">
         <v>11</v>
@@ -6519,7 +6519,7 @@
         <v>10</v>
       </c>
       <c r="F100">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G100" t="s">
         <v>11</v>
@@ -6542,7 +6542,7 @@
         <v>10</v>
       </c>
       <c r="F101" s="3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G101" s="3" t="s">
         <v>11</v>
@@ -6565,7 +6565,7 @@
         <v>10</v>
       </c>
       <c r="F102">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G102" t="s">
         <v>11</v>
@@ -6588,7 +6588,7 @@
         <v>10</v>
       </c>
       <c r="F103" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G103" s="3" t="s">
         <v>11</v>
@@ -6634,7 +6634,7 @@
         <v>10</v>
       </c>
       <c r="F105" s="3">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G105" s="3" t="s">
         <v>11</v>
@@ -6657,7 +6657,7 @@
         <v>10</v>
       </c>
       <c r="F106">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G106" t="s">
         <v>11</v>
@@ -6680,7 +6680,7 @@
         <v>10</v>
       </c>
       <c r="F107" s="3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G107" s="3" t="s">
         <v>11</v>
@@ -6703,7 +6703,7 @@
         <v>10</v>
       </c>
       <c r="F108">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G108" t="s">
         <v>11</v>
@@ -6726,7 +6726,7 @@
         <v>10</v>
       </c>
       <c r="F109" s="3">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G109" s="3" t="s">
         <v>11</v>
@@ -6749,7 +6749,7 @@
         <v>10</v>
       </c>
       <c r="F110">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G110" t="s">
         <v>11</v>
@@ -6772,7 +6772,7 @@
         <v>10</v>
       </c>
       <c r="F111" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G111" s="3" t="s">
         <v>11</v>
@@ -6795,7 +6795,7 @@
         <v>10</v>
       </c>
       <c r="F112">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G112" t="s">
         <v>11</v>
@@ -6818,7 +6818,7 @@
         <v>10</v>
       </c>
       <c r="F113" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G113" s="3" t="s">
         <v>11</v>
@@ -6841,7 +6841,7 @@
         <v>10</v>
       </c>
       <c r="F114">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G114" t="s">
         <v>11</v>
@@ -6864,7 +6864,7 @@
         <v>10</v>
       </c>
       <c r="F115" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G115" s="3" t="s">
         <v>11</v>
@@ -6887,7 +6887,7 @@
         <v>10</v>
       </c>
       <c r="F116">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G116" t="s">
         <v>11</v>
@@ -6910,7 +6910,7 @@
         <v>10</v>
       </c>
       <c r="F117" s="3">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G117" s="3" t="s">
         <v>11</v>
@@ -6956,7 +6956,7 @@
         <v>10</v>
       </c>
       <c r="F119" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G119" s="3" t="s">
         <v>11</v>
@@ -7002,7 +7002,7 @@
         <v>10</v>
       </c>
       <c r="F121" s="3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G121" s="3" t="s">
         <v>11</v>
@@ -7025,7 +7025,7 @@
         <v>10</v>
       </c>
       <c r="F122">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G122" t="s">
         <v>11</v>
@@ -7094,7 +7094,7 @@
         <v>10</v>
       </c>
       <c r="F125" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G125" s="3" t="s">
         <v>11</v>
@@ -7117,7 +7117,7 @@
         <v>10</v>
       </c>
       <c r="F126">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G126" t="s">
         <v>11</v>
@@ -7140,7 +7140,7 @@
         <v>10</v>
       </c>
       <c r="F127" s="3">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G127" s="3" t="s">
         <v>11</v>
@@ -7186,7 +7186,7 @@
         <v>10</v>
       </c>
       <c r="F129" s="3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G129" s="3" t="s">
         <v>11</v>
@@ -7209,7 +7209,7 @@
         <v>10</v>
       </c>
       <c r="F130">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G130" t="s">
         <v>11</v>
@@ -7232,7 +7232,7 @@
         <v>10</v>
       </c>
       <c r="F131" s="3">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G131" s="3" t="s">
         <v>11</v>
@@ -7255,7 +7255,7 @@
         <v>10</v>
       </c>
       <c r="F132">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G132" t="s">
         <v>11</v>
@@ -7278,7 +7278,7 @@
         <v>10</v>
       </c>
       <c r="F133" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G133" s="3" t="s">
         <v>11</v>
@@ -7301,7 +7301,7 @@
         <v>10</v>
       </c>
       <c r="F134">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G134" t="s">
         <v>11</v>
@@ -7324,7 +7324,7 @@
         <v>10</v>
       </c>
       <c r="F135" s="3">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G135" s="3" t="s">
         <v>11</v>
@@ -7347,7 +7347,7 @@
         <v>10</v>
       </c>
       <c r="F136">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G136" t="s">
         <v>11</v>
@@ -7370,7 +7370,7 @@
         <v>10</v>
       </c>
       <c r="F137" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G137" s="3" t="s">
         <v>11</v>
@@ -7393,7 +7393,7 @@
         <v>10</v>
       </c>
       <c r="F138">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G138" t="s">
         <v>11</v>
@@ -7439,7 +7439,7 @@
         <v>10</v>
       </c>
       <c r="F140">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G140" t="s">
         <v>11</v>
@@ -7462,7 +7462,7 @@
         <v>10</v>
       </c>
       <c r="F141" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G141" s="3" t="s">
         <v>11</v>
@@ -7485,7 +7485,7 @@
         <v>10</v>
       </c>
       <c r="F142">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G142" t="s">
         <v>11</v>
@@ -7508,7 +7508,7 @@
         <v>10</v>
       </c>
       <c r="F143" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G143" s="3" t="s">
         <v>11</v>
@@ -7531,7 +7531,7 @@
         <v>10</v>
       </c>
       <c r="F144">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G144" t="s">
         <v>11</v>
@@ -7554,7 +7554,7 @@
         <v>10</v>
       </c>
       <c r="F145" s="3">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G145" s="3" t="s">
         <v>11</v>
@@ -7600,7 +7600,7 @@
         <v>10</v>
       </c>
       <c r="F147" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G147" s="3" t="s">
         <v>11</v>
@@ -7623,7 +7623,7 @@
         <v>10</v>
       </c>
       <c r="F148">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G148" t="s">
         <v>11</v>
@@ -7669,7 +7669,7 @@
         <v>10</v>
       </c>
       <c r="F150">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G150" t="s">
         <v>11</v>
@@ -7692,7 +7692,7 @@
         <v>10</v>
       </c>
       <c r="F151" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G151" s="3" t="s">
         <v>11</v>
@@ -7738,7 +7738,7 @@
         <v>10</v>
       </c>
       <c r="F153" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G153" s="3" t="s">
         <v>11</v>
@@ -7761,7 +7761,7 @@
         <v>10</v>
       </c>
       <c r="F154">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G154" t="s">
         <v>11</v>
@@ -7784,7 +7784,7 @@
         <v>10</v>
       </c>
       <c r="F155" s="3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G155" s="3" t="s">
         <v>11</v>
@@ -7807,7 +7807,7 @@
         <v>10</v>
       </c>
       <c r="F156">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G156" t="s">
         <v>11</v>
@@ -7830,7 +7830,7 @@
         <v>10</v>
       </c>
       <c r="F157" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G157" s="3" t="s">
         <v>11</v>
@@ -7853,7 +7853,7 @@
         <v>10</v>
       </c>
       <c r="F158">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G158" t="s">
         <v>11</v>
@@ -7876,7 +7876,7 @@
         <v>10</v>
       </c>
       <c r="F159" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G159" s="3" t="s">
         <v>11</v>
@@ -7899,7 +7899,7 @@
         <v>10</v>
       </c>
       <c r="F160">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G160" t="s">
         <v>11</v>
@@ -7922,7 +7922,7 @@
         <v>10</v>
       </c>
       <c r="F161" s="3">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G161" s="3" t="s">
         <v>11</v>
@@ -7945,7 +7945,7 @@
         <v>10</v>
       </c>
       <c r="F162">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G162" t="s">
         <v>11</v>
@@ -7968,7 +7968,7 @@
         <v>10</v>
       </c>
       <c r="F163" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G163" s="3" t="s">
         <v>11</v>
@@ -7991,7 +7991,7 @@
         <v>10</v>
       </c>
       <c r="F164">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G164" t="s">
         <v>11</v>
@@ -8014,7 +8014,7 @@
         <v>10</v>
       </c>
       <c r="F165" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G165" s="3" t="s">
         <v>11</v>
@@ -8037,7 +8037,7 @@
         <v>10</v>
       </c>
       <c r="F166">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G166" t="s">
         <v>11</v>
@@ -8060,7 +8060,7 @@
         <v>10</v>
       </c>
       <c r="F167" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G167" s="3" t="s">
         <v>11</v>
@@ -8083,7 +8083,7 @@
         <v>10</v>
       </c>
       <c r="F168">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G168" t="s">
         <v>11</v>
@@ -8129,7 +8129,7 @@
         <v>10</v>
       </c>
       <c r="F170">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G170" t="s">
         <v>11</v>
@@ -8152,7 +8152,7 @@
         <v>10</v>
       </c>
       <c r="F171" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G171" s="3" t="s">
         <v>11</v>
@@ -8175,7 +8175,7 @@
         <v>10</v>
       </c>
       <c r="F172">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G172" t="s">
         <v>11</v>
@@ -8198,7 +8198,7 @@
         <v>10</v>
       </c>
       <c r="F173" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G173" s="3" t="s">
         <v>11</v>
@@ -8221,7 +8221,7 @@
         <v>10</v>
       </c>
       <c r="F174">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G174" t="s">
         <v>11</v>
@@ -8244,7 +8244,7 @@
         <v>10</v>
       </c>
       <c r="F175" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G175" s="3" t="s">
         <v>11</v>
@@ -8267,7 +8267,7 @@
         <v>10</v>
       </c>
       <c r="F176">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G176" t="s">
         <v>11</v>
@@ -8290,7 +8290,7 @@
         <v>10</v>
       </c>
       <c r="F177" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G177" s="3" t="s">
         <v>11</v>
@@ -8313,7 +8313,7 @@
         <v>10</v>
       </c>
       <c r="F178">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G178" t="s">
         <v>11</v>
@@ -8359,7 +8359,7 @@
         <v>10</v>
       </c>
       <c r="F180">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G180" t="s">
         <v>11</v>
@@ -8382,7 +8382,7 @@
         <v>10</v>
       </c>
       <c r="F181" s="3">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G181" s="3" t="s">
         <v>11</v>
@@ -8428,7 +8428,7 @@
         <v>10</v>
       </c>
       <c r="F183" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G183" s="3" t="s">
         <v>11</v>
@@ -8451,7 +8451,7 @@
         <v>10</v>
       </c>
       <c r="F184">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G184" t="s">
         <v>11</v>
@@ -8497,7 +8497,7 @@
         <v>10</v>
       </c>
       <c r="F186">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G186" t="s">
         <v>11</v>
@@ -8520,7 +8520,7 @@
         <v>10</v>
       </c>
       <c r="F187" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G187" s="3" t="s">
         <v>11</v>
@@ -8566,7 +8566,7 @@
         <v>10</v>
       </c>
       <c r="F189" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G189" s="3" t="s">
         <v>11</v>
@@ -8589,7 +8589,7 @@
         <v>10</v>
       </c>
       <c r="F190">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G190" t="s">
         <v>11</v>
@@ -8612,7 +8612,7 @@
         <v>10</v>
       </c>
       <c r="F191" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G191" s="3" t="s">
         <v>11</v>
@@ -8635,7 +8635,7 @@
         <v>10</v>
       </c>
       <c r="F192">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G192" t="s">
         <v>11</v>
@@ -8658,7 +8658,7 @@
         <v>10</v>
       </c>
       <c r="F193" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G193" s="3" t="s">
         <v>11</v>
@@ -8681,7 +8681,7 @@
         <v>10</v>
       </c>
       <c r="F194">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G194" t="s">
         <v>11</v>
@@ -8704,7 +8704,7 @@
         <v>10</v>
       </c>
       <c r="F195" s="3">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G195" s="3" t="s">
         <v>11</v>
@@ -8727,7 +8727,7 @@
         <v>10</v>
       </c>
       <c r="F196">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G196" t="s">
         <v>11</v>
@@ -8750,7 +8750,7 @@
         <v>10</v>
       </c>
       <c r="F197" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G197" s="3" t="s">
         <v>11</v>
@@ -8796,7 +8796,7 @@
         <v>10</v>
       </c>
       <c r="F199" s="3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G199" s="3" t="s">
         <v>11</v>
@@ -8819,7 +8819,7 @@
         <v>10</v>
       </c>
       <c r="F200">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G200" t="s">
         <v>11</v>
@@ -8842,7 +8842,7 @@
         <v>10</v>
       </c>
       <c r="F201" s="3">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G201" s="3" t="s">
         <v>11</v>
@@ -8865,7 +8865,7 @@
         <v>10</v>
       </c>
       <c r="F202">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G202" t="s">
         <v>11</v>
@@ -8888,7 +8888,7 @@
         <v>10</v>
       </c>
       <c r="F203" s="3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G203" s="3" t="s">
         <v>11</v>
@@ -8911,7 +8911,7 @@
         <v>10</v>
       </c>
       <c r="F204">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G204" t="s">
         <v>11</v>
@@ -8934,7 +8934,7 @@
         <v>10</v>
       </c>
       <c r="F205" s="3">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G205" s="3" t="s">
         <v>11</v>
@@ -8957,7 +8957,7 @@
         <v>10</v>
       </c>
       <c r="F206">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G206" t="s">
         <v>11</v>
@@ -8980,7 +8980,7 @@
         <v>10</v>
       </c>
       <c r="F207" s="3">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G207" s="3" t="s">
         <v>11</v>
@@ -9003,7 +9003,7 @@
         <v>10</v>
       </c>
       <c r="F208">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G208" t="s">
         <v>11</v>
@@ -9026,7 +9026,7 @@
         <v>10</v>
       </c>
       <c r="F209" s="3">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G209" s="3" t="s">
         <v>11</v>
@@ -9049,7 +9049,7 @@
         <v>10</v>
       </c>
       <c r="F210">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G210" t="s">
         <v>11</v>
@@ -9072,7 +9072,7 @@
         <v>10</v>
       </c>
       <c r="F211" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G211" s="3" t="s">
         <v>11</v>
@@ -9095,7 +9095,7 @@
         <v>10</v>
       </c>
       <c r="F212">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G212" t="s">
         <v>11</v>
@@ -9118,7 +9118,7 @@
         <v>10</v>
       </c>
       <c r="F213" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G213" s="3" t="s">
         <v>11</v>
@@ -9141,7 +9141,7 @@
         <v>10</v>
       </c>
       <c r="F214">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G214" t="s">
         <v>11</v>
@@ -9164,7 +9164,7 @@
         <v>10</v>
       </c>
       <c r="F215" s="3">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G215" s="3" t="s">
         <v>11</v>
@@ -9187,7 +9187,7 @@
         <v>10</v>
       </c>
       <c r="F216">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G216" t="s">
         <v>11</v>
@@ -9210,7 +9210,7 @@
         <v>10</v>
       </c>
       <c r="F217" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G217" s="3" t="s">
         <v>11</v>
@@ -9233,7 +9233,7 @@
         <v>10</v>
       </c>
       <c r="F218">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G218" t="s">
         <v>11</v>
@@ -9279,7 +9279,7 @@
         <v>10</v>
       </c>
       <c r="F220">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G220" t="s">
         <v>11</v>
@@ -9302,7 +9302,7 @@
         <v>10</v>
       </c>
       <c r="F221" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G221" s="3" t="s">
         <v>11</v>
@@ -9325,7 +9325,7 @@
         <v>10</v>
       </c>
       <c r="F222">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G222" t="s">
         <v>11</v>
@@ -9348,7 +9348,7 @@
         <v>10</v>
       </c>
       <c r="F223" s="3">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G223" s="3" t="s">
         <v>11</v>
@@ -9394,7 +9394,7 @@
         <v>10</v>
       </c>
       <c r="F225" s="3">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G225" s="3" t="s">
         <v>11</v>
@@ -9417,7 +9417,7 @@
         <v>10</v>
       </c>
       <c r="F226">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G226" t="s">
         <v>11</v>
@@ -9440,7 +9440,7 @@
         <v>10</v>
       </c>
       <c r="F227" s="3">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G227" s="3" t="s">
         <v>11</v>
@@ -9463,7 +9463,7 @@
         <v>10</v>
       </c>
       <c r="F228">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G228" t="s">
         <v>11</v>
@@ -9486,7 +9486,7 @@
         <v>10</v>
       </c>
       <c r="F229" s="3">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G229" s="3" t="s">
         <v>11</v>
@@ -9509,7 +9509,7 @@
         <v>10</v>
       </c>
       <c r="F230">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G230" t="s">
         <v>11</v>
@@ -9532,7 +9532,7 @@
         <v>10</v>
       </c>
       <c r="F231" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G231" s="3" t="s">
         <v>11</v>
@@ -9555,7 +9555,7 @@
         <v>10</v>
       </c>
       <c r="F232">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G232" t="s">
         <v>11</v>
@@ -9578,7 +9578,7 @@
         <v>10</v>
       </c>
       <c r="F233" s="3">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G233" s="3" t="s">
         <v>11</v>
@@ -9601,7 +9601,7 @@
         <v>10</v>
       </c>
       <c r="F234">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G234" t="s">
         <v>11</v>
@@ -9624,7 +9624,7 @@
         <v>10</v>
       </c>
       <c r="F235" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G235" s="3" t="s">
         <v>11</v>
@@ -9647,7 +9647,7 @@
         <v>10</v>
       </c>
       <c r="F236">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G236" t="s">
         <v>11</v>
@@ -9670,7 +9670,7 @@
         <v>10</v>
       </c>
       <c r="F237" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G237" s="3" t="s">
         <v>11</v>
@@ -9716,7 +9716,7 @@
         <v>10</v>
       </c>
       <c r="F239" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G239" s="3" t="s">
         <v>11</v>
@@ -9739,7 +9739,7 @@
         <v>10</v>
       </c>
       <c r="F240">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G240" t="s">
         <v>11</v>
@@ -9762,7 +9762,7 @@
         <v>10</v>
       </c>
       <c r="F241" s="3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G241" s="3" t="s">
         <v>11</v>
@@ -9831,7 +9831,7 @@
         <v>10</v>
       </c>
       <c r="F244">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G244" t="s">
         <v>11</v>
@@ -9854,7 +9854,7 @@
         <v>10</v>
       </c>
       <c r="F245" s="3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G245" s="3" t="s">
         <v>11</v>
@@ -9877,7 +9877,7 @@
         <v>10</v>
       </c>
       <c r="F246">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G246" t="s">
         <v>11</v>
@@ -9900,7 +9900,7 @@
         <v>10</v>
       </c>
       <c r="F247" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G247" s="3" t="s">
         <v>11</v>
@@ -9923,7 +9923,7 @@
         <v>10</v>
       </c>
       <c r="F248">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G248" t="s">
         <v>11</v>
@@ -9946,7 +9946,7 @@
         <v>10</v>
       </c>
       <c r="F249" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G249" s="3" t="s">
         <v>11</v>
@@ -9969,7 +9969,7 @@
         <v>10</v>
       </c>
       <c r="F250">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G250" t="s">
         <v>11</v>
@@ -9992,7 +9992,7 @@
         <v>10</v>
       </c>
       <c r="F251" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G251" s="3" t="s">
         <v>11</v>
@@ -10015,7 +10015,7 @@
         <v>10</v>
       </c>
       <c r="F252">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G252" t="s">
         <v>11</v>
@@ -10038,7 +10038,7 @@
         <v>10</v>
       </c>
       <c r="F253" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G253" s="3" t="s">
         <v>11</v>
@@ -10084,7 +10084,7 @@
         <v>10</v>
       </c>
       <c r="F255" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G255" s="3" t="s">
         <v>11</v>
@@ -10107,7 +10107,7 @@
         <v>10</v>
       </c>
       <c r="F256">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G256" t="s">
         <v>11</v>
@@ -10130,7 +10130,7 @@
         <v>10</v>
       </c>
       <c r="F257" s="3">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G257" s="3" t="s">
         <v>11</v>
@@ -10153,7 +10153,7 @@
         <v>10</v>
       </c>
       <c r="F258">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G258" t="s">
         <v>11</v>
@@ -10176,7 +10176,7 @@
         <v>10</v>
       </c>
       <c r="F259" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G259" s="3" t="s">
         <v>11</v>
@@ -10222,7 +10222,7 @@
         <v>10</v>
       </c>
       <c r="F261" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G261" s="3" t="s">
         <v>11</v>
@@ -10245,7 +10245,7 @@
         <v>10</v>
       </c>
       <c r="F262">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G262" t="s">
         <v>11</v>
@@ -10291,7 +10291,7 @@
         <v>10</v>
       </c>
       <c r="F264">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G264" t="s">
         <v>11</v>
@@ -10314,7 +10314,7 @@
         <v>10</v>
       </c>
       <c r="F265" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G265" s="3" t="s">
         <v>11</v>
@@ -10337,7 +10337,7 @@
         <v>10</v>
       </c>
       <c r="F266">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G266" t="s">
         <v>11</v>
@@ -10360,7 +10360,7 @@
         <v>10</v>
       </c>
       <c r="F267" s="3">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G267" s="3" t="s">
         <v>11</v>
@@ -10383,7 +10383,7 @@
         <v>10</v>
       </c>
       <c r="F268">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G268" t="s">
         <v>11</v>
@@ -10406,7 +10406,7 @@
         <v>10</v>
       </c>
       <c r="F269" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G269" s="3" t="s">
         <v>11</v>
@@ -10429,7 +10429,7 @@
         <v>10</v>
       </c>
       <c r="F270">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G270" t="s">
         <v>11</v>
@@ -10475,7 +10475,7 @@
         <v>10</v>
       </c>
       <c r="F272">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G272" t="s">
         <v>11</v>
@@ -10498,7 +10498,7 @@
         <v>10</v>
       </c>
       <c r="F273" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G273" s="3" t="s">
         <v>11</v>
@@ -10521,7 +10521,7 @@
         <v>10</v>
       </c>
       <c r="F274">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G274" t="s">
         <v>11</v>
@@ -10544,7 +10544,7 @@
         <v>10</v>
       </c>
       <c r="F275" s="3">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G275" s="3" t="s">
         <v>11</v>
@@ -10567,7 +10567,7 @@
         <v>10</v>
       </c>
       <c r="F276">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G276" t="s">
         <v>11</v>
@@ -10613,7 +10613,7 @@
         <v>10</v>
       </c>
       <c r="F278">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G278" t="s">
         <v>11</v>
@@ -10636,7 +10636,7 @@
         <v>10</v>
       </c>
       <c r="F279" s="3">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G279" s="3" t="s">
         <v>11</v>
@@ -10659,7 +10659,7 @@
         <v>10</v>
       </c>
       <c r="F280">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G280" t="s">
         <v>11</v>
@@ -10682,7 +10682,7 @@
         <v>10</v>
       </c>
       <c r="F281" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G281" s="3" t="s">
         <v>11</v>
@@ -10705,7 +10705,7 @@
         <v>10</v>
       </c>
       <c r="F282">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G282" t="s">
         <v>11</v>
@@ -10728,7 +10728,7 @@
         <v>10</v>
       </c>
       <c r="F283" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G283" s="3" t="s">
         <v>11</v>
@@ -10751,7 +10751,7 @@
         <v>10</v>
       </c>
       <c r="F284">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G284" t="s">
         <v>11</v>
@@ -10774,7 +10774,7 @@
         <v>10</v>
       </c>
       <c r="F285" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G285" s="3" t="s">
         <v>11</v>
@@ -10797,7 +10797,7 @@
         <v>10</v>
       </c>
       <c r="F286">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G286" t="s">
         <v>11</v>
@@ -10843,7 +10843,7 @@
         <v>10</v>
       </c>
       <c r="F288">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G288" t="s">
         <v>11</v>
@@ -10935,7 +10935,7 @@
         <v>10</v>
       </c>
       <c r="F292">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G292" t="s">
         <v>11</v>
@@ -10958,7 +10958,7 @@
         <v>10</v>
       </c>
       <c r="F293" s="3">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G293" s="3" t="s">
         <v>11</v>
@@ -10981,7 +10981,7 @@
         <v>10</v>
       </c>
       <c r="F294">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G294" t="s">
         <v>11</v>
@@ -11004,7 +11004,7 @@
         <v>10</v>
       </c>
       <c r="F295" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G295" s="3" t="s">
         <v>11</v>
@@ -11027,7 +11027,7 @@
         <v>10</v>
       </c>
       <c r="F296">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G296" t="s">
         <v>11</v>
@@ -11050,7 +11050,7 @@
         <v>10</v>
       </c>
       <c r="F297" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G297" s="3" t="s">
         <v>11</v>
@@ -11073,7 +11073,7 @@
         <v>10</v>
       </c>
       <c r="F298">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G298" t="s">
         <v>11</v>
@@ -11142,7 +11142,7 @@
         <v>10</v>
       </c>
       <c r="F301" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G301" s="3" t="s">
         <v>11</v>
@@ -11165,7 +11165,7 @@
         <v>10</v>
       </c>
       <c r="F302">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G302" t="s">
         <v>11</v>
@@ -11211,7 +11211,7 @@
         <v>10</v>
       </c>
       <c r="F304">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G304" t="s">
         <v>11</v>
@@ -11234,7 +11234,7 @@
         <v>10</v>
       </c>
       <c r="F305" s="3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G305" s="3" t="s">
         <v>11</v>
@@ -11280,7 +11280,7 @@
         <v>10</v>
       </c>
       <c r="F307" s="3">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G307" s="3" t="s">
         <v>11</v>
@@ -11303,7 +11303,7 @@
         <v>10</v>
       </c>
       <c r="F308">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G308" t="s">
         <v>11</v>
@@ -11326,7 +11326,7 @@
         <v>10</v>
       </c>
       <c r="F309" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G309" s="3" t="s">
         <v>11</v>
@@ -11349,7 +11349,7 @@
         <v>10</v>
       </c>
       <c r="F310">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G310" t="s">
         <v>11</v>
@@ -11372,7 +11372,7 @@
         <v>10</v>
       </c>
       <c r="F311" s="3">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G311" s="3" t="s">
         <v>11</v>
@@ -11395,7 +11395,7 @@
         <v>10</v>
       </c>
       <c r="F312">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G312" t="s">
         <v>11</v>
@@ -11418,7 +11418,7 @@
         <v>10</v>
       </c>
       <c r="F313" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G313" s="3" t="s">
         <v>11</v>
@@ -11464,7 +11464,7 @@
         <v>10</v>
       </c>
       <c r="F315" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G315" s="3" t="s">
         <v>11</v>
@@ -11487,7 +11487,7 @@
         <v>10</v>
       </c>
       <c r="F316">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G316" t="s">
         <v>11</v>
@@ -11510,7 +11510,7 @@
         <v>10</v>
       </c>
       <c r="F317" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G317" s="3" t="s">
         <v>11</v>
@@ -11556,7 +11556,7 @@
         <v>10</v>
       </c>
       <c r="F319" s="3">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G319" s="3" t="s">
         <v>11</v>
@@ -11579,7 +11579,7 @@
         <v>10</v>
       </c>
       <c r="F320">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G320" t="s">
         <v>11</v>
@@ -11602,7 +11602,7 @@
         <v>10</v>
       </c>
       <c r="F321" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G321" s="3" t="s">
         <v>11</v>
@@ -11625,7 +11625,7 @@
         <v>10</v>
       </c>
       <c r="F322">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G322" t="s">
         <v>11</v>
@@ -11648,7 +11648,7 @@
         <v>10</v>
       </c>
       <c r="F323" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G323" s="3" t="s">
         <v>11</v>
@@ -11671,7 +11671,7 @@
         <v>10</v>
       </c>
       <c r="F324">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G324" t="s">
         <v>11</v>
@@ -11694,7 +11694,7 @@
         <v>10</v>
       </c>
       <c r="F325" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G325" s="3" t="s">
         <v>11</v>
@@ -11717,7 +11717,7 @@
         <v>10</v>
       </c>
       <c r="F326">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G326" t="s">
         <v>11</v>
@@ -11740,7 +11740,7 @@
         <v>10</v>
       </c>
       <c r="F327" s="3">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G327" s="3" t="s">
         <v>11</v>
@@ -11763,7 +11763,7 @@
         <v>10</v>
       </c>
       <c r="F328">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G328" t="s">
         <v>11</v>
@@ -11786,7 +11786,7 @@
         <v>10</v>
       </c>
       <c r="F329" s="3">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G329" s="3" t="s">
         <v>11</v>
@@ -11809,7 +11809,7 @@
         <v>10</v>
       </c>
       <c r="F330">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G330" t="s">
         <v>11</v>
@@ -11901,7 +11901,7 @@
         <v>10</v>
       </c>
       <c r="F334">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G334" t="s">
         <v>11</v>
@@ -11924,7 +11924,7 @@
         <v>10</v>
       </c>
       <c r="F335" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G335" s="3" t="s">
         <v>11</v>
@@ -11947,7 +11947,7 @@
         <v>10</v>
       </c>
       <c r="F336">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G336" t="s">
         <v>11</v>
@@ -11970,7 +11970,7 @@
         <v>10</v>
       </c>
       <c r="F337" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G337" s="3" t="s">
         <v>11</v>
@@ -11993,7 +11993,7 @@
         <v>10</v>
       </c>
       <c r="F338">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G338" t="s">
         <v>11</v>
@@ -12016,7 +12016,7 @@
         <v>10</v>
       </c>
       <c r="F339" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G339" s="3" t="s">
         <v>11</v>
@@ -12039,7 +12039,7 @@
         <v>10</v>
       </c>
       <c r="F340">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G340" t="s">
         <v>11</v>
@@ -12062,7 +12062,7 @@
         <v>10</v>
       </c>
       <c r="F341" s="3">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G341" s="3" t="s">
         <v>11</v>
@@ -12085,7 +12085,7 @@
         <v>10</v>
       </c>
       <c r="F342">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G342" t="s">
         <v>11</v>
@@ -12108,7 +12108,7 @@
         <v>10</v>
       </c>
       <c r="F343" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G343" s="3" t="s">
         <v>11</v>
@@ -12131,7 +12131,7 @@
         <v>10</v>
       </c>
       <c r="F344">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G344" t="s">
         <v>11</v>
@@ -12154,7 +12154,7 @@
         <v>10</v>
       </c>
       <c r="F345" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G345" s="3" t="s">
         <v>11</v>
@@ -12177,7 +12177,7 @@
         <v>10</v>
       </c>
       <c r="F346">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G346" t="s">
         <v>11</v>
@@ -12200,7 +12200,7 @@
         <v>10</v>
       </c>
       <c r="F347" s="3">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G347" s="3" t="s">
         <v>11</v>
@@ -12223,7 +12223,7 @@
         <v>10</v>
       </c>
       <c r="F348">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G348" t="s">
         <v>11</v>
@@ -12246,7 +12246,7 @@
         <v>10</v>
       </c>
       <c r="F349" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G349" s="3" t="s">
         <v>11</v>
@@ -12269,7 +12269,7 @@
         <v>10</v>
       </c>
       <c r="F350">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G350" t="s">
         <v>11</v>
@@ -12315,7 +12315,7 @@
         <v>10</v>
       </c>
       <c r="F352">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G352" t="s">
         <v>11</v>
@@ -12338,7 +12338,7 @@
         <v>10</v>
       </c>
       <c r="F353" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G353" s="3" t="s">
         <v>11</v>
@@ -12361,7 +12361,7 @@
         <v>10</v>
       </c>
       <c r="F354">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G354" t="s">
         <v>11</v>
@@ -12384,7 +12384,7 @@
         <v>10</v>
       </c>
       <c r="F355" s="3">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G355" s="3" t="s">
         <v>11</v>
@@ -12407,7 +12407,7 @@
         <v>10</v>
       </c>
       <c r="F356">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G356" t="s">
         <v>11</v>
@@ -12430,7 +12430,7 @@
         <v>10</v>
       </c>
       <c r="F357" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G357" s="3" t="s">
         <v>11</v>
@@ -12453,7 +12453,7 @@
         <v>10</v>
       </c>
       <c r="F358">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G358" t="s">
         <v>11</v>
@@ -12476,7 +12476,7 @@
         <v>10</v>
       </c>
       <c r="F359" s="3">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G359" s="3" t="s">
         <v>11</v>
@@ -12499,7 +12499,7 @@
         <v>10</v>
       </c>
       <c r="F360">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G360" t="s">
         <v>11</v>
@@ -12522,7 +12522,7 @@
         <v>10</v>
       </c>
       <c r="F361" s="3">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G361" s="3" t="s">
         <v>11</v>
@@ -12545,7 +12545,7 @@
         <v>10</v>
       </c>
       <c r="F362">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G362" t="s">
         <v>11</v>
@@ -12568,7 +12568,7 @@
         <v>10</v>
       </c>
       <c r="F363" s="3">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G363" s="3" t="s">
         <v>11</v>
@@ -12591,7 +12591,7 @@
         <v>10</v>
       </c>
       <c r="F364">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G364" t="s">
         <v>11</v>
@@ -12614,7 +12614,7 @@
         <v>10</v>
       </c>
       <c r="F365" s="3">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G365" s="3" t="s">
         <v>11</v>
@@ -12637,7 +12637,7 @@
         <v>10</v>
       </c>
       <c r="F366">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G366" t="s">
         <v>11</v>
@@ -12660,7 +12660,7 @@
         <v>10</v>
       </c>
       <c r="F367" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G367" s="3" t="s">
         <v>11</v>
@@ -12683,7 +12683,7 @@
         <v>10</v>
       </c>
       <c r="F368">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G368" t="s">
         <v>11</v>
@@ -12706,7 +12706,7 @@
         <v>10</v>
       </c>
       <c r="F369" s="3">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G369" s="3" t="s">
         <v>11</v>
@@ -12729,7 +12729,7 @@
         <v>10</v>
       </c>
       <c r="F370">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G370" t="s">
         <v>11</v>
@@ -12752,7 +12752,7 @@
         <v>10</v>
       </c>
       <c r="F371" s="3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G371" s="3" t="s">
         <v>11</v>
@@ -12775,7 +12775,7 @@
         <v>10</v>
       </c>
       <c r="F372">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G372" t="s">
         <v>11</v>
@@ -12798,7 +12798,7 @@
         <v>10</v>
       </c>
       <c r="F373" s="3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G373" s="3" t="s">
         <v>11</v>
@@ -12821,7 +12821,7 @@
         <v>10</v>
       </c>
       <c r="F374">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G374" t="s">
         <v>11</v>
@@ -12844,7 +12844,7 @@
         <v>10</v>
       </c>
       <c r="F375" s="3">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G375" s="3" t="s">
         <v>11</v>
@@ -12867,7 +12867,7 @@
         <v>10</v>
       </c>
       <c r="F376">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G376" t="s">
         <v>11</v>
@@ -12890,7 +12890,7 @@
         <v>10</v>
       </c>
       <c r="F377" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G377" s="3" t="s">
         <v>11</v>
@@ -12913,7 +12913,7 @@
         <v>10</v>
       </c>
       <c r="F378">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G378" t="s">
         <v>11</v>
@@ -12936,7 +12936,7 @@
         <v>10</v>
       </c>
       <c r="F379" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G379" s="3" t="s">
         <v>11</v>
@@ -12959,7 +12959,7 @@
         <v>10</v>
       </c>
       <c r="F380">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G380" t="s">
         <v>11</v>
@@ -12982,7 +12982,7 @@
         <v>10</v>
       </c>
       <c r="F381" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G381" s="3" t="s">
         <v>11</v>
@@ -13005,7 +13005,7 @@
         <v>10</v>
       </c>
       <c r="F382">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G382" t="s">
         <v>11</v>
@@ -13028,7 +13028,7 @@
         <v>10</v>
       </c>
       <c r="F383" s="3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G383" s="3" t="s">
         <v>11</v>
@@ -13051,7 +13051,7 @@
         <v>10</v>
       </c>
       <c r="F384">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G384" t="s">
         <v>11</v>
@@ -13074,7 +13074,7 @@
         <v>10</v>
       </c>
       <c r="F385" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G385" s="3" t="s">
         <v>11</v>
@@ -13097,7 +13097,7 @@
         <v>10</v>
       </c>
       <c r="F386">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G386" t="s">
         <v>11</v>
@@ -13120,7 +13120,7 @@
         <v>10</v>
       </c>
       <c r="F387" s="3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G387" s="3" t="s">
         <v>11</v>
@@ -13143,7 +13143,7 @@
         <v>10</v>
       </c>
       <c r="F388">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G388" t="s">
         <v>11</v>
@@ -13166,7 +13166,7 @@
         <v>10</v>
       </c>
       <c r="F389" s="3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G389" s="3" t="s">
         <v>11</v>
@@ -13212,7 +13212,7 @@
         <v>10</v>
       </c>
       <c r="F391" s="3">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G391" s="3" t="s">
         <v>11</v>
@@ -13235,7 +13235,7 @@
         <v>10</v>
       </c>
       <c r="F392">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G392" t="s">
         <v>11</v>
@@ -13258,7 +13258,7 @@
         <v>10</v>
       </c>
       <c r="F393" s="3">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G393" s="3" t="s">
         <v>11</v>
@@ -13281,7 +13281,7 @@
         <v>10</v>
       </c>
       <c r="F394">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G394" t="s">
         <v>11</v>
@@ -13304,7 +13304,7 @@
         <v>10</v>
       </c>
       <c r="F395" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G395" s="3" t="s">
         <v>11</v>
@@ -13327,7 +13327,7 @@
         <v>10</v>
       </c>
       <c r="F396">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G396" t="s">
         <v>11</v>
@@ -13350,7 +13350,7 @@
         <v>10</v>
       </c>
       <c r="F397" s="3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G397" s="3" t="s">
         <v>11</v>
@@ -13396,7 +13396,7 @@
         <v>10</v>
       </c>
       <c r="F399" s="3">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G399" s="3" t="s">
         <v>11</v>
@@ -13419,7 +13419,7 @@
         <v>10</v>
       </c>
       <c r="F400">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G400" t="s">
         <v>11</v>
@@ -13442,7 +13442,7 @@
         <v>10</v>
       </c>
       <c r="F401" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G401" s="3" t="s">
         <v>11</v>
@@ -13465,7 +13465,7 @@
         <v>10</v>
       </c>
       <c r="F402">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G402" t="s">
         <v>11</v>
@@ -13488,7 +13488,7 @@
         <v>10</v>
       </c>
       <c r="F403" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G403" s="3" t="s">
         <v>11</v>
@@ -13534,7 +13534,7 @@
         <v>10</v>
       </c>
       <c r="F405" s="3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G405" s="3" t="s">
         <v>11</v>
@@ -13557,7 +13557,7 @@
         <v>10</v>
       </c>
       <c r="F406">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G406" t="s">
         <v>11</v>
@@ -13580,7 +13580,7 @@
         <v>10</v>
       </c>
       <c r="F407" s="3">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G407" s="3" t="s">
         <v>11</v>
@@ -13603,7 +13603,7 @@
         <v>10</v>
       </c>
       <c r="F408">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G408" t="s">
         <v>11</v>
@@ -13626,7 +13626,7 @@
         <v>10</v>
       </c>
       <c r="F409" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G409" s="3" t="s">
         <v>11</v>
@@ -13672,7 +13672,7 @@
         <v>10</v>
       </c>
       <c r="F411" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G411" s="3" t="s">
         <v>11</v>
@@ -13695,7 +13695,7 @@
         <v>10</v>
       </c>
       <c r="F412">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G412" t="s">
         <v>11</v>
@@ -13718,7 +13718,7 @@
         <v>10</v>
       </c>
       <c r="F413" s="3">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G413" s="3" t="s">
         <v>11</v>
@@ -13741,7 +13741,7 @@
         <v>10</v>
       </c>
       <c r="F414">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G414" t="s">
         <v>11</v>
@@ -13764,7 +13764,7 @@
         <v>10</v>
       </c>
       <c r="F415" s="3">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G415" s="3" t="s">
         <v>11</v>
@@ -13787,7 +13787,7 @@
         <v>10</v>
       </c>
       <c r="F416">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G416" t="s">
         <v>11</v>
@@ -13833,7 +13833,7 @@
         <v>10</v>
       </c>
       <c r="F418">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G418" t="s">
         <v>11</v>
@@ -13856,7 +13856,7 @@
         <v>10</v>
       </c>
       <c r="F419" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G419" s="3" t="s">
         <v>11</v>
@@ -13879,7 +13879,7 @@
         <v>10</v>
       </c>
       <c r="F420">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G420" t="s">
         <v>11</v>
@@ -13902,7 +13902,7 @@
         <v>10</v>
       </c>
       <c r="F421" s="3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G421" s="3" t="s">
         <v>11</v>
@@ -13925,7 +13925,7 @@
         <v>10</v>
       </c>
       <c r="F422">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G422" t="s">
         <v>11</v>
@@ -13948,7 +13948,7 @@
         <v>10</v>
       </c>
       <c r="F423" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G423" s="3" t="s">
         <v>11</v>
@@ -13971,7 +13971,7 @@
         <v>10</v>
       </c>
       <c r="F424">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G424" t="s">
         <v>11</v>
@@ -13994,7 +13994,7 @@
         <v>10</v>
       </c>
       <c r="F425" s="3">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G425" s="3" t="s">
         <v>11</v>
@@ -14017,7 +14017,7 @@
         <v>10</v>
       </c>
       <c r="F426">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G426" t="s">
         <v>11</v>
@@ -14040,7 +14040,7 @@
         <v>10</v>
       </c>
       <c r="F427" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G427" s="3" t="s">
         <v>11</v>
@@ -14063,7 +14063,7 @@
         <v>10</v>
       </c>
       <c r="F428">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G428" t="s">
         <v>11</v>
@@ -14086,7 +14086,7 @@
         <v>10</v>
       </c>
       <c r="F429" s="3">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G429" s="3" t="s">
         <v>11</v>
@@ -14109,7 +14109,7 @@
         <v>10</v>
       </c>
       <c r="F430">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G430" t="s">
         <v>11</v>
@@ -14132,7 +14132,7 @@
         <v>10</v>
       </c>
       <c r="F431" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G431" s="3" t="s">
         <v>11</v>
@@ -14155,7 +14155,7 @@
         <v>10</v>
       </c>
       <c r="F432">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G432" t="s">
         <v>11</v>
@@ -14178,7 +14178,7 @@
         <v>10</v>
       </c>
       <c r="F433" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G433" s="3" t="s">
         <v>11</v>
@@ -14224,7 +14224,7 @@
         <v>10</v>
       </c>
       <c r="F435" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G435" s="3" t="s">
         <v>11</v>
@@ -14270,7 +14270,7 @@
         <v>10</v>
       </c>
       <c r="F437" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G437" s="3" t="s">
         <v>11</v>
@@ -14293,7 +14293,7 @@
         <v>10</v>
       </c>
       <c r="F438">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G438" t="s">
         <v>11</v>
@@ -14316,7 +14316,7 @@
         <v>10</v>
       </c>
       <c r="F439" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G439" s="3" t="s">
         <v>11</v>
@@ -14339,7 +14339,7 @@
         <v>10</v>
       </c>
       <c r="F440">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G440" t="s">
         <v>11</v>
@@ -14362,7 +14362,7 @@
         <v>10</v>
       </c>
       <c r="F441" s="3">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G441" s="3" t="s">
         <v>11</v>
@@ -14385,7 +14385,7 @@
         <v>10</v>
       </c>
       <c r="F442">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G442" t="s">
         <v>11</v>
@@ -14408,7 +14408,7 @@
         <v>10</v>
       </c>
       <c r="F443" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G443" s="3" t="s">
         <v>11</v>
@@ -14454,7 +14454,7 @@
         <v>10</v>
       </c>
       <c r="F445" s="3">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G445" s="3" t="s">
         <v>11</v>
@@ -14477,7 +14477,7 @@
         <v>10</v>
       </c>
       <c r="F446">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G446" t="s">
         <v>11</v>
@@ -14500,7 +14500,7 @@
         <v>10</v>
       </c>
       <c r="F447" s="3">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G447" s="3" t="s">
         <v>11</v>
@@ -14523,7 +14523,7 @@
         <v>10</v>
       </c>
       <c r="F448">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G448" t="s">
         <v>11</v>
@@ -14546,7 +14546,7 @@
         <v>10</v>
       </c>
       <c r="F449" s="3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G449" s="3" t="s">
         <v>11</v>
@@ -14569,7 +14569,7 @@
         <v>10</v>
       </c>
       <c r="F450">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G450" t="s">
         <v>11</v>
@@ -14592,7 +14592,7 @@
         <v>10</v>
       </c>
       <c r="F451" s="3">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G451" s="3" t="s">
         <v>11</v>
@@ -14638,7 +14638,7 @@
         <v>10</v>
       </c>
       <c r="F453" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G453" s="3" t="s">
         <v>11</v>
@@ -14661,7 +14661,7 @@
         <v>10</v>
       </c>
       <c r="F454">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G454" t="s">
         <v>11</v>
@@ -14684,7 +14684,7 @@
         <v>10</v>
       </c>
       <c r="F455" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G455" s="3" t="s">
         <v>11</v>
@@ -14707,7 +14707,7 @@
         <v>10</v>
       </c>
       <c r="F456">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G456" t="s">
         <v>11</v>
@@ -14753,7 +14753,7 @@
         <v>10</v>
       </c>
       <c r="F458">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G458" t="s">
         <v>11</v>
@@ -14776,7 +14776,7 @@
         <v>10</v>
       </c>
       <c r="F459" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G459" s="3" t="s">
         <v>11</v>
@@ -14799,7 +14799,7 @@
         <v>10</v>
       </c>
       <c r="F460">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G460" t="s">
         <v>11</v>
@@ -14822,7 +14822,7 @@
         <v>10</v>
       </c>
       <c r="F461" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G461" s="3" t="s">
         <v>11</v>
@@ -14868,7 +14868,7 @@
         <v>10</v>
       </c>
       <c r="F463" s="3">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G463" s="3" t="s">
         <v>11</v>
@@ -14914,7 +14914,7 @@
         <v>10</v>
       </c>
       <c r="F465" s="3">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G465" s="3" t="s">
         <v>11</v>
@@ -14960,7 +14960,7 @@
         <v>10</v>
       </c>
       <c r="F467" s="3">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G467" s="3" t="s">
         <v>11</v>
@@ -14983,7 +14983,7 @@
         <v>10</v>
       </c>
       <c r="F468">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G468" t="s">
         <v>11</v>
@@ -15006,7 +15006,7 @@
         <v>10</v>
       </c>
       <c r="F469" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G469" s="3" t="s">
         <v>11</v>
@@ -15029,7 +15029,7 @@
         <v>10</v>
       </c>
       <c r="F470">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G470" t="s">
         <v>11</v>
@@ -15052,7 +15052,7 @@
         <v>10</v>
       </c>
       <c r="F471" s="3">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G471" s="3" t="s">
         <v>11</v>
@@ -15098,7 +15098,7 @@
         <v>10</v>
       </c>
       <c r="F473" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G473" s="3" t="s">
         <v>11</v>
@@ -15121,7 +15121,7 @@
         <v>10</v>
       </c>
       <c r="F474">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G474" t="s">
         <v>11</v>
@@ -15144,7 +15144,7 @@
         <v>10</v>
       </c>
       <c r="F475" s="3">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G475" s="3" t="s">
         <v>11</v>
@@ -15167,7 +15167,7 @@
         <v>10</v>
       </c>
       <c r="F476">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G476" t="s">
         <v>11</v>
@@ -15190,7 +15190,7 @@
         <v>10</v>
       </c>
       <c r="F477" s="3">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G477" s="3" t="s">
         <v>11</v>
@@ -15213,7 +15213,7 @@
         <v>10</v>
       </c>
       <c r="F478">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G478" t="s">
         <v>11</v>
@@ -15236,7 +15236,7 @@
         <v>10</v>
       </c>
       <c r="F479" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G479" s="3" t="s">
         <v>11</v>
@@ -15282,7 +15282,7 @@
         <v>10</v>
       </c>
       <c r="F481" s="3">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G481" s="3" t="s">
         <v>11</v>
@@ -15305,7 +15305,7 @@
         <v>10</v>
       </c>
       <c r="F482">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G482" t="s">
         <v>11</v>
@@ -15328,7 +15328,7 @@
         <v>10</v>
       </c>
       <c r="F483" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G483" s="3" t="s">
         <v>11</v>
@@ -15351,7 +15351,7 @@
         <v>10</v>
       </c>
       <c r="F484">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G484" t="s">
         <v>11</v>
@@ -15374,7 +15374,7 @@
         <v>10</v>
       </c>
       <c r="F485" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G485" s="3" t="s">
         <v>11</v>
@@ -15397,7 +15397,7 @@
         <v>10</v>
       </c>
       <c r="F486">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G486" t="s">
         <v>11</v>
@@ -15420,7 +15420,7 @@
         <v>10</v>
       </c>
       <c r="F487" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G487" s="3" t="s">
         <v>11</v>
@@ -15443,7 +15443,7 @@
         <v>10</v>
       </c>
       <c r="F488">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G488" t="s">
         <v>11</v>
@@ -15466,7 +15466,7 @@
         <v>10</v>
       </c>
       <c r="F489" s="3">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G489" s="3" t="s">
         <v>11</v>
@@ -15489,7 +15489,7 @@
         <v>10</v>
       </c>
       <c r="F490">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G490" t="s">
         <v>11</v>
@@ -15512,7 +15512,7 @@
         <v>10</v>
       </c>
       <c r="F491" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G491" s="3" t="s">
         <v>11</v>
@@ -15535,7 +15535,7 @@
         <v>10</v>
       </c>
       <c r="F492">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G492" t="s">
         <v>11</v>
@@ -15558,7 +15558,7 @@
         <v>10</v>
       </c>
       <c r="F493" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G493" s="3" t="s">
         <v>11</v>
@@ -15604,7 +15604,7 @@
         <v>10</v>
       </c>
       <c r="F495" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G495" s="3" t="s">
         <v>11</v>
@@ -15627,7 +15627,7 @@
         <v>10</v>
       </c>
       <c r="F496">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G496" t="s">
         <v>11</v>
@@ -15650,7 +15650,7 @@
         <v>10</v>
       </c>
       <c r="F497" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G497" s="3" t="s">
         <v>11</v>
@@ -15673,7 +15673,7 @@
         <v>10</v>
       </c>
       <c r="F498">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G498" t="s">
         <v>11</v>
@@ -15719,7 +15719,7 @@
         <v>10</v>
       </c>
       <c r="F500">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G500" t="s">
         <v>11</v>
@@ -15742,7 +15742,7 @@
         <v>10</v>
       </c>
       <c r="F501" s="3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G501" s="3" t="s">
         <v>11</v>
@@ -15765,7 +15765,7 @@
         <v>10</v>
       </c>
       <c r="F502">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G502" t="s">
         <v>11</v>
@@ -15788,7 +15788,7 @@
         <v>10</v>
       </c>
       <c r="F503" s="3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G503" s="3" t="s">
         <v>11</v>
@@ -15811,7 +15811,7 @@
         <v>10</v>
       </c>
       <c r="F504">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G504" t="s">
         <v>11</v>
@@ -15834,7 +15834,7 @@
         <v>10</v>
       </c>
       <c r="F505" s="3">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G505" s="3" t="s">
         <v>11</v>
@@ -15857,7 +15857,7 @@
         <v>10</v>
       </c>
       <c r="F506">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G506" t="s">
         <v>11</v>
@@ -15880,7 +15880,7 @@
         <v>10</v>
       </c>
       <c r="F507" s="3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G507" s="3" t="s">
         <v>11</v>
@@ -15903,7 +15903,7 @@
         <v>10</v>
       </c>
       <c r="F508">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G508" t="s">
         <v>11</v>
@@ -15926,7 +15926,7 @@
         <v>10</v>
       </c>
       <c r="F509" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G509" s="3" t="s">
         <v>11</v>
@@ -15949,7 +15949,7 @@
         <v>10</v>
       </c>
       <c r="F510">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G510" t="s">
         <v>11</v>
@@ -15972,7 +15972,7 @@
         <v>10</v>
       </c>
       <c r="F511" s="3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G511" s="3" t="s">
         <v>11</v>
@@ -15995,7 +15995,7 @@
         <v>10</v>
       </c>
       <c r="F512">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G512" t="s">
         <v>11</v>
@@ -16018,7 +16018,7 @@
         <v>10</v>
       </c>
       <c r="F513" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G513" s="3" t="s">
         <v>11</v>
@@ -16041,7 +16041,7 @@
         <v>10</v>
       </c>
       <c r="F514">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G514" t="s">
         <v>11</v>
@@ -16064,7 +16064,7 @@
         <v>10</v>
       </c>
       <c r="F515" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G515" s="3" t="s">
         <v>11</v>
@@ -16110,7 +16110,7 @@
         <v>10</v>
       </c>
       <c r="F517" s="3">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G517" s="3" t="s">
         <v>11</v>
@@ -16133,7 +16133,7 @@
         <v>10</v>
       </c>
       <c r="F518">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G518" t="s">
         <v>11</v>
@@ -16156,7 +16156,7 @@
         <v>10</v>
       </c>
       <c r="F519" s="3">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G519" s="3" t="s">
         <v>11</v>
@@ -16179,7 +16179,7 @@
         <v>10</v>
       </c>
       <c r="F520">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G520" t="s">
         <v>11</v>
@@ -16202,7 +16202,7 @@
         <v>10</v>
       </c>
       <c r="F521" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G521" s="3" t="s">
         <v>11</v>
@@ -16225,7 +16225,7 @@
         <v>10</v>
       </c>
       <c r="F522">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G522" t="s">
         <v>11</v>
@@ -16248,7 +16248,7 @@
         <v>10</v>
       </c>
       <c r="F523" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G523" s="3" t="s">
         <v>11</v>
@@ -16271,7 +16271,7 @@
         <v>10</v>
       </c>
       <c r="F524">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G524" t="s">
         <v>11</v>
@@ -16294,7 +16294,7 @@
         <v>10</v>
       </c>
       <c r="F525" s="3">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G525" s="3" t="s">
         <v>11</v>
@@ -16340,7 +16340,7 @@
         <v>10</v>
       </c>
       <c r="F527" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G527" s="3" t="s">
         <v>11</v>
@@ -16363,7 +16363,7 @@
         <v>10</v>
       </c>
       <c r="F528">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G528" t="s">
         <v>11</v>
@@ -16386,7 +16386,7 @@
         <v>10</v>
       </c>
       <c r="F529" s="3">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G529" s="3" t="s">
         <v>11</v>
@@ -16409,7 +16409,7 @@
         <v>10</v>
       </c>
       <c r="F530">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G530" t="s">
         <v>11</v>
@@ -16432,7 +16432,7 @@
         <v>10</v>
       </c>
       <c r="F531" s="3">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G531" s="3" t="s">
         <v>11</v>
@@ -16455,7 +16455,7 @@
         <v>10</v>
       </c>
       <c r="F532">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G532" t="s">
         <v>11</v>
@@ -16478,7 +16478,7 @@
         <v>10</v>
       </c>
       <c r="F533" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G533" s="3" t="s">
         <v>11</v>
@@ -16501,7 +16501,7 @@
         <v>10</v>
       </c>
       <c r="F534">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G534" t="s">
         <v>11</v>
@@ -16524,7 +16524,7 @@
         <v>10</v>
       </c>
       <c r="F535" s="3">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G535" s="3" t="s">
         <v>11</v>
@@ -16547,7 +16547,7 @@
         <v>10</v>
       </c>
       <c r="F536">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G536" t="s">
         <v>11</v>
@@ -16570,7 +16570,7 @@
         <v>10</v>
       </c>
       <c r="F537" s="3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G537" s="3" t="s">
         <v>11</v>
@@ -16616,7 +16616,7 @@
         <v>10</v>
       </c>
       <c r="F539" s="3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G539" s="3" t="s">
         <v>11</v>
@@ -16639,7 +16639,7 @@
         <v>10</v>
       </c>
       <c r="F540">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G540" t="s">
         <v>11</v>
@@ -16662,7 +16662,7 @@
         <v>10</v>
       </c>
       <c r="F541" s="3">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G541" s="3" t="s">
         <v>11</v>
@@ -16685,7 +16685,7 @@
         <v>10</v>
       </c>
       <c r="F542">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G542" t="s">
         <v>11</v>
@@ -16708,7 +16708,7 @@
         <v>10</v>
       </c>
       <c r="F543" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G543" s="3" t="s">
         <v>11</v>
@@ -16731,7 +16731,7 @@
         <v>10</v>
       </c>
       <c r="F544">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G544" t="s">
         <v>11</v>
@@ -16777,7 +16777,7 @@
         <v>10</v>
       </c>
       <c r="F546">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G546" t="s">
         <v>11</v>
@@ -16800,7 +16800,7 @@
         <v>10</v>
       </c>
       <c r="F547" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G547" s="3" t="s">
         <v>11</v>
@@ -16869,7 +16869,7 @@
         <v>10</v>
       </c>
       <c r="F550">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G550" t="s">
         <v>11</v>
@@ -16892,7 +16892,7 @@
         <v>10</v>
       </c>
       <c r="F551" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G551" s="3" t="s">
         <v>11</v>
@@ -16915,7 +16915,7 @@
         <v>10</v>
       </c>
       <c r="F552">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G552" t="s">
         <v>11</v>
@@ -16938,7 +16938,7 @@
         <v>10</v>
       </c>
       <c r="F553" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G553" s="3" t="s">
         <v>11</v>
@@ -16961,7 +16961,7 @@
         <v>10</v>
       </c>
       <c r="F554">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G554" t="s">
         <v>11</v>
@@ -16984,7 +16984,7 @@
         <v>10</v>
       </c>
       <c r="F555" s="3">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G555" s="3" t="s">
         <v>11</v>
@@ -17007,7 +17007,7 @@
         <v>10</v>
       </c>
       <c r="F556">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G556" t="s">
         <v>11</v>
@@ -17030,7 +17030,7 @@
         <v>10</v>
       </c>
       <c r="F557" s="3">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G557" s="3" t="s">
         <v>11</v>
@@ -17076,7 +17076,7 @@
         <v>10</v>
       </c>
       <c r="F559" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G559" s="3" t="s">
         <v>11</v>
@@ -17099,7 +17099,7 @@
         <v>10</v>
       </c>
       <c r="F560">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G560" t="s">
         <v>11</v>
@@ -17145,7 +17145,7 @@
         <v>10</v>
       </c>
       <c r="F562">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G562" t="s">
         <v>11</v>
@@ -17168,7 +17168,7 @@
         <v>10</v>
       </c>
       <c r="F563" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G563" s="3" t="s">
         <v>11</v>
@@ -17191,7 +17191,7 @@
         <v>10</v>
       </c>
       <c r="F564">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G564" t="s">
         <v>11</v>
@@ -17214,7 +17214,7 @@
         <v>10</v>
       </c>
       <c r="F565" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G565" s="3" t="s">
         <v>11</v>
@@ -17237,7 +17237,7 @@
         <v>10</v>
       </c>
       <c r="F566">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G566" t="s">
         <v>11</v>
@@ -17260,7 +17260,7 @@
         <v>10</v>
       </c>
       <c r="F567" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G567" s="3" t="s">
         <v>11</v>
@@ -17283,7 +17283,7 @@
         <v>10</v>
       </c>
       <c r="F568">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G568" t="s">
         <v>11</v>
@@ -17306,7 +17306,7 @@
         <v>10</v>
       </c>
       <c r="F569" s="3">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G569" s="3" t="s">
         <v>11</v>
@@ -17329,7 +17329,7 @@
         <v>10</v>
       </c>
       <c r="F570">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G570" t="s">
         <v>11</v>
@@ -17352,7 +17352,7 @@
         <v>10</v>
       </c>
       <c r="F571" s="3">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G571" s="3" t="s">
         <v>11</v>
@@ -17375,7 +17375,7 @@
         <v>10</v>
       </c>
       <c r="F572">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G572" t="s">
         <v>11</v>
@@ -17398,7 +17398,7 @@
         <v>10</v>
       </c>
       <c r="F573" s="3">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G573" s="3" t="s">
         <v>11</v>
@@ -17421,7 +17421,7 @@
         <v>10</v>
       </c>
       <c r="F574">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G574" t="s">
         <v>11</v>
@@ -17444,7 +17444,7 @@
         <v>10</v>
       </c>
       <c r="F575" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G575" s="3" t="s">
         <v>11</v>
@@ -17467,7 +17467,7 @@
         <v>10</v>
       </c>
       <c r="F576">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G576" t="s">
         <v>11</v>
@@ -17490,7 +17490,7 @@
         <v>10</v>
       </c>
       <c r="F577" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G577" s="3" t="s">
         <v>11</v>
@@ -17513,7 +17513,7 @@
         <v>10</v>
       </c>
       <c r="F578">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G578" t="s">
         <v>11</v>
@@ -17536,7 +17536,7 @@
         <v>10</v>
       </c>
       <c r="F579" s="3">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G579" s="3" t="s">
         <v>11</v>
@@ -17559,7 +17559,7 @@
         <v>10</v>
       </c>
       <c r="F580">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G580" t="s">
         <v>11</v>
@@ -17582,7 +17582,7 @@
         <v>10</v>
       </c>
       <c r="F581" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G581" s="3" t="s">
         <v>11</v>
@@ -17605,7 +17605,7 @@
         <v>10</v>
       </c>
       <c r="F582">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G582" t="s">
         <v>11</v>
@@ -17628,7 +17628,7 @@
         <v>10</v>
       </c>
       <c r="F583" s="3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G583" s="3" t="s">
         <v>11</v>
@@ -17651,7 +17651,7 @@
         <v>10</v>
       </c>
       <c r="F584">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G584" t="s">
         <v>11</v>
@@ -17674,7 +17674,7 @@
         <v>10</v>
       </c>
       <c r="F585" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G585" s="3" t="s">
         <v>11</v>
@@ -17697,7 +17697,7 @@
         <v>10</v>
       </c>
       <c r="F586">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G586" t="s">
         <v>11</v>
@@ -17720,7 +17720,7 @@
         <v>10</v>
       </c>
       <c r="F587" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G587" s="3" t="s">
         <v>11</v>
@@ -17743,7 +17743,7 @@
         <v>10</v>
       </c>
       <c r="F588">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G588" t="s">
         <v>11</v>
@@ -17766,7 +17766,7 @@
         <v>10</v>
       </c>
       <c r="F589" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G589" s="3" t="s">
         <v>11</v>
@@ -17812,7 +17812,7 @@
         <v>10</v>
       </c>
       <c r="F591" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G591" s="3" t="s">
         <v>11</v>
@@ -17835,7 +17835,7 @@
         <v>10</v>
       </c>
       <c r="F592">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G592" t="s">
         <v>11</v>
@@ -17858,7 +17858,7 @@
         <v>10</v>
       </c>
       <c r="F593" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G593" s="3" t="s">
         <v>11</v>
@@ -17881,7 +17881,7 @@
         <v>10</v>
       </c>
       <c r="F594">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G594" t="s">
         <v>11</v>
@@ -17904,7 +17904,7 @@
         <v>10</v>
       </c>
       <c r="F595" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G595" s="3" t="s">
         <v>11</v>
@@ -17927,7 +17927,7 @@
         <v>10</v>
       </c>
       <c r="F596">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G596" t="s">
         <v>11</v>
@@ -17950,7 +17950,7 @@
         <v>10</v>
       </c>
       <c r="F597" s="3">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G597" s="3" t="s">
         <v>11</v>
@@ -17973,7 +17973,7 @@
         <v>10</v>
       </c>
       <c r="F598">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G598" t="s">
         <v>11</v>
@@ -17996,7 +17996,7 @@
         <v>10</v>
       </c>
       <c r="F599" s="3">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G599" s="3" t="s">
         <v>11</v>
@@ -18019,7 +18019,7 @@
         <v>10</v>
       </c>
       <c r="F600">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G600" t="s">
         <v>11</v>
@@ -18042,7 +18042,7 @@
         <v>10</v>
       </c>
       <c r="F601" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G601" s="3" t="s">
         <v>11</v>
@@ -18065,7 +18065,7 @@
         <v>10</v>
       </c>
       <c r="F602">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G602" t="s">
         <v>11</v>
@@ -18111,7 +18111,7 @@
         <v>10</v>
       </c>
       <c r="F604">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G604" t="s">
         <v>11</v>
@@ -18134,7 +18134,7 @@
         <v>10</v>
       </c>
       <c r="F605" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G605" s="3" t="s">
         <v>11</v>
@@ -18157,7 +18157,7 @@
         <v>10</v>
       </c>
       <c r="F606">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G606" t="s">
         <v>11</v>
@@ -18180,7 +18180,7 @@
         <v>10</v>
       </c>
       <c r="F607" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G607" s="3" t="s">
         <v>11</v>
@@ -18203,7 +18203,7 @@
         <v>10</v>
       </c>
       <c r="F608">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G608" t="s">
         <v>11</v>
@@ -18249,7 +18249,7 @@
         <v>10</v>
       </c>
       <c r="F610">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G610" t="s">
         <v>11</v>
@@ -18295,7 +18295,7 @@
         <v>10</v>
       </c>
       <c r="F612">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G612" t="s">
         <v>11</v>
@@ -18318,7 +18318,7 @@
         <v>10</v>
       </c>
       <c r="F613" s="3">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G613" s="3" t="s">
         <v>11</v>
@@ -18341,7 +18341,7 @@
         <v>10</v>
       </c>
       <c r="F614">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G614" t="s">
         <v>11</v>
@@ -18364,7 +18364,7 @@
         <v>10</v>
       </c>
       <c r="F615" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G615" s="3" t="s">
         <v>11</v>
@@ -18387,7 +18387,7 @@
         <v>10</v>
       </c>
       <c r="F616">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G616" t="s">
         <v>11</v>
@@ -18410,7 +18410,7 @@
         <v>10</v>
       </c>
       <c r="F617" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G617" s="3" t="s">
         <v>11</v>
@@ -18433,7 +18433,7 @@
         <v>10</v>
       </c>
       <c r="F618">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G618" t="s">
         <v>11</v>
@@ -18456,7 +18456,7 @@
         <v>10</v>
       </c>
       <c r="F619" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G619" s="3" t="s">
         <v>11</v>
@@ -18479,7 +18479,7 @@
         <v>10</v>
       </c>
       <c r="F620">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G620" t="s">
         <v>11</v>
@@ -18502,7 +18502,7 @@
         <v>10</v>
       </c>
       <c r="F621" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G621" s="3" t="s">
         <v>11</v>
@@ -18525,7 +18525,7 @@
         <v>10</v>
       </c>
       <c r="F622">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G622" t="s">
         <v>11</v>
@@ -18548,7 +18548,7 @@
         <v>10</v>
       </c>
       <c r="F623" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G623" s="3" t="s">
         <v>11</v>
@@ -18571,7 +18571,7 @@
         <v>10</v>
       </c>
       <c r="F624">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G624" t="s">
         <v>11</v>
@@ -18594,7 +18594,7 @@
         <v>10</v>
       </c>
       <c r="F625" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G625" s="3" t="s">
         <v>11</v>
@@ -18617,7 +18617,7 @@
         <v>10</v>
       </c>
       <c r="F626">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G626" t="s">
         <v>11</v>
@@ -18663,7 +18663,7 @@
         <v>10</v>
       </c>
       <c r="F628">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G628" t="s">
         <v>11</v>
@@ -18709,7 +18709,7 @@
         <v>10</v>
       </c>
       <c r="F630">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G630" t="s">
         <v>11</v>
@@ -18732,7 +18732,7 @@
         <v>10</v>
       </c>
       <c r="F631" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G631" s="3" t="s">
         <v>11</v>
@@ -18755,7 +18755,7 @@
         <v>10</v>
       </c>
       <c r="F632">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G632" t="s">
         <v>11</v>
@@ -18801,7 +18801,7 @@
         <v>10</v>
       </c>
       <c r="F634">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G634" t="s">
         <v>11</v>
@@ -18824,7 +18824,7 @@
         <v>10</v>
       </c>
       <c r="F635" s="3">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G635" s="3" t="s">
         <v>11</v>
@@ -18847,7 +18847,7 @@
         <v>10</v>
       </c>
       <c r="F636">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G636" t="s">
         <v>11</v>
@@ -18870,7 +18870,7 @@
         <v>10</v>
       </c>
       <c r="F637" s="3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G637" s="3" t="s">
         <v>11</v>
@@ -18893,7 +18893,7 @@
         <v>10</v>
       </c>
       <c r="F638">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G638" t="s">
         <v>11</v>
@@ -18916,7 +18916,7 @@
         <v>10</v>
       </c>
       <c r="F639" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G639" s="3" t="s">
         <v>11</v>
@@ -18962,7 +18962,7 @@
         <v>10</v>
       </c>
       <c r="F641" s="3">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G641" s="3" t="s">
         <v>11</v>
@@ -18985,7 +18985,7 @@
         <v>10</v>
       </c>
       <c r="F642">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G642" t="s">
         <v>11</v>
@@ -19008,7 +19008,7 @@
         <v>10</v>
       </c>
       <c r="F643" s="3">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G643" s="3" t="s">
         <v>11</v>
@@ -19031,7 +19031,7 @@
         <v>10</v>
       </c>
       <c r="F644">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G644" t="s">
         <v>11</v>
@@ -19054,7 +19054,7 @@
         <v>10</v>
       </c>
       <c r="F645" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G645" s="3" t="s">
         <v>11</v>
@@ -19077,7 +19077,7 @@
         <v>10</v>
       </c>
       <c r="F646">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G646" t="s">
         <v>11</v>
@@ -19100,7 +19100,7 @@
         <v>10</v>
       </c>
       <c r="F647" s="3">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G647" s="3" t="s">
         <v>11</v>
@@ -19123,7 +19123,7 @@
         <v>10</v>
       </c>
       <c r="F648">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G648" t="s">
         <v>11</v>
@@ -19146,7 +19146,7 @@
         <v>10</v>
       </c>
       <c r="F649" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G649" s="3" t="s">
         <v>11</v>
@@ -19192,7 +19192,7 @@
         <v>10</v>
       </c>
       <c r="F651" s="3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G651" s="3" t="s">
         <v>11</v>
@@ -19215,7 +19215,7 @@
         <v>10</v>
       </c>
       <c r="F652">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G652" t="s">
         <v>11</v>
@@ -19238,7 +19238,7 @@
         <v>10</v>
       </c>
       <c r="F653" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G653" s="3" t="s">
         <v>11</v>
@@ -19284,7 +19284,7 @@
         <v>10</v>
       </c>
       <c r="F655" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G655" s="3" t="s">
         <v>11</v>
@@ -19307,7 +19307,7 @@
         <v>10</v>
       </c>
       <c r="F656">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G656" t="s">
         <v>11</v>
@@ -19330,7 +19330,7 @@
         <v>10</v>
       </c>
       <c r="F657" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G657" s="3" t="s">
         <v>11</v>
@@ -19353,7 +19353,7 @@
         <v>10</v>
       </c>
       <c r="F658">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G658" t="s">
         <v>11</v>
@@ -19376,7 +19376,7 @@
         <v>10</v>
       </c>
       <c r="F659" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G659" s="3" t="s">
         <v>11</v>
@@ -19399,7 +19399,7 @@
         <v>10</v>
       </c>
       <c r="F660">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G660" t="s">
         <v>11</v>
@@ -19422,7 +19422,7 @@
         <v>10</v>
       </c>
       <c r="F661" s="3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G661" s="3" t="s">
         <v>11</v>
@@ -19445,7 +19445,7 @@
         <v>10</v>
       </c>
       <c r="F662">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G662" t="s">
         <v>11</v>
@@ -19468,7 +19468,7 @@
         <v>10</v>
       </c>
       <c r="F663" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G663" s="3" t="s">
         <v>11</v>
@@ -19491,7 +19491,7 @@
         <v>10</v>
       </c>
       <c r="F664">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G664" t="s">
         <v>11</v>
@@ -19537,7 +19537,7 @@
         <v>10</v>
       </c>
       <c r="F666">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G666" t="s">
         <v>11</v>
@@ -19560,7 +19560,7 @@
         <v>10</v>
       </c>
       <c r="F667" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G667" s="3" t="s">
         <v>11</v>
@@ -19583,7 +19583,7 @@
         <v>10</v>
       </c>
       <c r="F668">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G668" t="s">
         <v>11</v>
@@ -19606,7 +19606,7 @@
         <v>10</v>
       </c>
       <c r="F669" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G669" s="3" t="s">
         <v>11</v>
@@ -19629,7 +19629,7 @@
         <v>10</v>
       </c>
       <c r="F670">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G670" t="s">
         <v>11</v>
@@ -19675,7 +19675,7 @@
         <v>10</v>
       </c>
       <c r="F672">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G672" t="s">
         <v>11</v>
@@ -19698,7 +19698,7 @@
         <v>10</v>
       </c>
       <c r="F673" s="3">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G673" s="3" t="s">
         <v>11</v>
@@ -19721,7 +19721,7 @@
         <v>10</v>
       </c>
       <c r="F674">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G674" t="s">
         <v>11</v>
@@ -19744,7 +19744,7 @@
         <v>10</v>
       </c>
       <c r="F675" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G675" s="3" t="s">
         <v>11</v>
@@ -19767,7 +19767,7 @@
         <v>10</v>
       </c>
       <c r="F676">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G676" t="s">
         <v>11</v>
@@ -19790,7 +19790,7 @@
         <v>10</v>
       </c>
       <c r="F677" s="3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G677" s="3" t="s">
         <v>11</v>
@@ -19813,7 +19813,7 @@
         <v>10</v>
       </c>
       <c r="F678">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G678" t="s">
         <v>11</v>
@@ -19836,7 +19836,7 @@
         <v>10</v>
       </c>
       <c r="F679" s="3">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G679" s="3" t="s">
         <v>11</v>
@@ -19859,7 +19859,7 @@
         <v>10</v>
       </c>
       <c r="F680">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G680" t="s">
         <v>11</v>
@@ -19882,7 +19882,7 @@
         <v>10</v>
       </c>
       <c r="F681" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G681" s="3" t="s">
         <v>11</v>
@@ -19905,7 +19905,7 @@
         <v>10</v>
       </c>
       <c r="F682">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G682" t="s">
         <v>11</v>
@@ -19928,7 +19928,7 @@
         <v>10</v>
       </c>
       <c r="F683" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G683" s="3" t="s">
         <v>11</v>
@@ -19951,7 +19951,7 @@
         <v>10</v>
       </c>
       <c r="F684">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G684" t="s">
         <v>11</v>
@@ -19974,7 +19974,7 @@
         <v>10</v>
       </c>
       <c r="F685" s="3">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G685" s="3" t="s">
         <v>11</v>
@@ -19997,7 +19997,7 @@
         <v>10</v>
       </c>
       <c r="F686">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G686" t="s">
         <v>11</v>
@@ -20043,7 +20043,7 @@
         <v>10</v>
       </c>
       <c r="F688">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G688" t="s">
         <v>11</v>
@@ -20066,7 +20066,7 @@
         <v>10</v>
       </c>
       <c r="F689" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G689" s="3" t="s">
         <v>11</v>
@@ -20089,7 +20089,7 @@
         <v>10</v>
       </c>
       <c r="F690">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G690" t="s">
         <v>11</v>
@@ -20112,7 +20112,7 @@
         <v>10</v>
       </c>
       <c r="F691" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G691" s="3" t="s">
         <v>11</v>
@@ -20135,7 +20135,7 @@
         <v>10</v>
       </c>
       <c r="F692">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G692" t="s">
         <v>11</v>
@@ -20158,7 +20158,7 @@
         <v>10</v>
       </c>
       <c r="F693" s="3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G693" s="3" t="s">
         <v>11</v>
@@ -20181,7 +20181,7 @@
         <v>10</v>
       </c>
       <c r="F694">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G694" t="s">
         <v>11</v>
@@ -20204,7 +20204,7 @@
         <v>10</v>
       </c>
       <c r="F695" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G695" s="3" t="s">
         <v>11</v>
@@ -20227,7 +20227,7 @@
         <v>10</v>
       </c>
       <c r="F696">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G696" t="s">
         <v>11</v>
@@ -20250,7 +20250,7 @@
         <v>10</v>
       </c>
       <c r="F697" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G697" s="3" t="s">
         <v>11</v>
@@ -20273,7 +20273,7 @@
         <v>10</v>
       </c>
       <c r="F698">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G698" t="s">
         <v>11</v>
@@ -20296,7 +20296,7 @@
         <v>10</v>
       </c>
       <c r="F699" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G699" s="3" t="s">
         <v>11</v>
@@ -20319,7 +20319,7 @@
         <v>10</v>
       </c>
       <c r="F700">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G700" t="s">
         <v>11</v>
@@ -20365,7 +20365,7 @@
         <v>10</v>
       </c>
       <c r="F702">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G702" t="s">
         <v>11</v>
@@ -20388,7 +20388,7 @@
         <v>10</v>
       </c>
       <c r="F703" s="3">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G703" s="3" t="s">
         <v>11</v>
@@ -20411,7 +20411,7 @@
         <v>10</v>
       </c>
       <c r="F704">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G704" t="s">
         <v>11</v>
@@ -20434,7 +20434,7 @@
         <v>10</v>
       </c>
       <c r="F705" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G705" s="3" t="s">
         <v>11</v>
@@ -20457,7 +20457,7 @@
         <v>10</v>
       </c>
       <c r="F706">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G706" t="s">
         <v>11</v>
@@ -20480,7 +20480,7 @@
         <v>10</v>
       </c>
       <c r="F707" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G707" s="3" t="s">
         <v>11</v>
@@ -20526,7 +20526,7 @@
         <v>10</v>
       </c>
       <c r="F709" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G709" s="3" t="s">
         <v>11</v>
@@ -20549,7 +20549,7 @@
         <v>10</v>
       </c>
       <c r="F710">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G710" t="s">
         <v>11</v>
@@ -20572,7 +20572,7 @@
         <v>10</v>
       </c>
       <c r="F711" s="3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G711" s="3" t="s">
         <v>11</v>
@@ -20595,7 +20595,7 @@
         <v>10</v>
       </c>
       <c r="F712">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G712" t="s">
         <v>11</v>
@@ -20618,7 +20618,7 @@
         <v>10</v>
       </c>
       <c r="F713" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G713" s="3" t="s">
         <v>11</v>
@@ -20664,7 +20664,7 @@
         <v>10</v>
       </c>
       <c r="F715" s="3">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G715" s="3" t="s">
         <v>11</v>
@@ -20687,7 +20687,7 @@
         <v>10</v>
       </c>
       <c r="F716">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G716" t="s">
         <v>11</v>
@@ -20710,7 +20710,7 @@
         <v>10</v>
       </c>
       <c r="F717" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G717" s="3" t="s">
         <v>11</v>
@@ -20733,7 +20733,7 @@
         <v>10</v>
       </c>
       <c r="F718">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G718" t="s">
         <v>11</v>
@@ -20756,7 +20756,7 @@
         <v>10</v>
       </c>
       <c r="F719" s="3">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G719" s="3" t="s">
         <v>11</v>
@@ -20779,7 +20779,7 @@
         <v>10</v>
       </c>
       <c r="F720">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G720" t="s">
         <v>11</v>
@@ -20802,7 +20802,7 @@
         <v>10</v>
       </c>
       <c r="F721" s="3">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G721" s="3" t="s">
         <v>11</v>
@@ -20825,7 +20825,7 @@
         <v>10</v>
       </c>
       <c r="F722">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G722" t="s">
         <v>11</v>
@@ -20848,7 +20848,7 @@
         <v>10</v>
       </c>
       <c r="F723" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G723" s="3" t="s">
         <v>11</v>
@@ -20871,7 +20871,7 @@
         <v>10</v>
       </c>
       <c r="F724">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G724" t="s">
         <v>11</v>
@@ -20894,7 +20894,7 @@
         <v>10</v>
       </c>
       <c r="F725" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G725" s="3" t="s">
         <v>11</v>
@@ -20917,7 +20917,7 @@
         <v>10</v>
       </c>
       <c r="F726">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G726" t="s">
         <v>11</v>
@@ -20940,7 +20940,7 @@
         <v>10</v>
       </c>
       <c r="F727" s="3">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G727" s="3" t="s">
         <v>11</v>
@@ -20963,7 +20963,7 @@
         <v>10</v>
       </c>
       <c r="F728">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G728" t="s">
         <v>11</v>
@@ -20986,7 +20986,7 @@
         <v>10</v>
       </c>
       <c r="F729" s="3">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G729" s="3" t="s">
         <v>11</v>
@@ -21009,7 +21009,7 @@
         <v>10</v>
       </c>
       <c r="F730">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G730" t="s">
         <v>11</v>
@@ -21032,7 +21032,7 @@
         <v>10</v>
       </c>
       <c r="F731" s="3">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G731" s="3" t="s">
         <v>11</v>
@@ -21055,7 +21055,7 @@
         <v>10</v>
       </c>
       <c r="F732">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G732" t="s">
         <v>11</v>
@@ -21078,7 +21078,7 @@
         <v>10</v>
       </c>
       <c r="F733" s="3">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G733" s="3" t="s">
         <v>11</v>
@@ -21101,7 +21101,7 @@
         <v>10</v>
       </c>
       <c r="F734">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G734" t="s">
         <v>11</v>
@@ -21124,7 +21124,7 @@
         <v>10</v>
       </c>
       <c r="F735" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G735" s="3" t="s">
         <v>11</v>
@@ -21193,7 +21193,7 @@
         <v>10</v>
       </c>
       <c r="F738">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G738" t="s">
         <v>11</v>
@@ -21216,7 +21216,7 @@
         <v>10</v>
       </c>
       <c r="F739" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G739" s="3" t="s">
         <v>11</v>
@@ -21239,7 +21239,7 @@
         <v>10</v>
       </c>
       <c r="F740">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G740" t="s">
         <v>11</v>
@@ -21285,7 +21285,7 @@
         <v>10</v>
       </c>
       <c r="F742">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G742" t="s">
         <v>11</v>
@@ -21331,7 +21331,7 @@
         <v>10</v>
       </c>
       <c r="F744">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G744" t="s">
         <v>11</v>
@@ -21354,7 +21354,7 @@
         <v>10</v>
       </c>
       <c r="F745" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G745" s="3" t="s">
         <v>11</v>
@@ -21377,7 +21377,7 @@
         <v>10</v>
       </c>
       <c r="F746">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G746" t="s">
         <v>11</v>
@@ -21400,7 +21400,7 @@
         <v>10</v>
       </c>
       <c r="F747" s="3">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G747" s="3" t="s">
         <v>11</v>
@@ -21446,7 +21446,7 @@
         <v>10</v>
       </c>
       <c r="F749" s="3">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G749" s="3" t="s">
         <v>11</v>
@@ -21469,7 +21469,7 @@
         <v>10</v>
       </c>
       <c r="F750">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G750" t="s">
         <v>11</v>
@@ -21492,7 +21492,7 @@
         <v>10</v>
       </c>
       <c r="F751" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G751" s="3" t="s">
         <v>11</v>
@@ -21515,7 +21515,7 @@
         <v>10</v>
       </c>
       <c r="F752">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G752" t="s">
         <v>11</v>
@@ -21538,7 +21538,7 @@
         <v>10</v>
       </c>
       <c r="F753" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G753" s="3" t="s">
         <v>11</v>
@@ -21561,7 +21561,7 @@
         <v>10</v>
       </c>
       <c r="F754">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G754" t="s">
         <v>11</v>
@@ -21584,7 +21584,7 @@
         <v>10</v>
       </c>
       <c r="F755" s="3">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G755" s="3" t="s">
         <v>11</v>
@@ -21607,7 +21607,7 @@
         <v>10</v>
       </c>
       <c r="F756">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G756" t="s">
         <v>11</v>
@@ -21630,7 +21630,7 @@
         <v>10</v>
       </c>
       <c r="F757" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G757" s="3" t="s">
         <v>11</v>
@@ -21653,7 +21653,7 @@
         <v>10</v>
       </c>
       <c r="F758">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G758" t="s">
         <v>11</v>
@@ -21676,7 +21676,7 @@
         <v>10</v>
       </c>
       <c r="F759" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G759" s="3" t="s">
         <v>11</v>
@@ -21699,7 +21699,7 @@
         <v>10</v>
       </c>
       <c r="F760">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G760" t="s">
         <v>11</v>
@@ -21745,7 +21745,7 @@
         <v>10</v>
       </c>
       <c r="F762">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G762" t="s">
         <v>11</v>
@@ -21768,7 +21768,7 @@
         <v>10</v>
       </c>
       <c r="F763" s="3">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G763" s="3" t="s">
         <v>11</v>
@@ -21791,7 +21791,7 @@
         <v>10</v>
       </c>
       <c r="F764">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G764" t="s">
         <v>11</v>
@@ -21814,7 +21814,7 @@
         <v>10</v>
       </c>
       <c r="F765" s="3">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G765" s="3" t="s">
         <v>11</v>
@@ -21837,7 +21837,7 @@
         <v>10</v>
       </c>
       <c r="F766">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G766" t="s">
         <v>11</v>
@@ -21860,7 +21860,7 @@
         <v>10</v>
       </c>
       <c r="F767" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G767" s="3" t="s">
         <v>11</v>
@@ -21906,7 +21906,7 @@
         <v>10</v>
       </c>
       <c r="F769" s="3">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G769" s="3" t="s">
         <v>11</v>
@@ -21929,7 +21929,7 @@
         <v>10</v>
       </c>
       <c r="F770">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G770" t="s">
         <v>11</v>
@@ -21952,7 +21952,7 @@
         <v>10</v>
       </c>
       <c r="F771" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G771" s="3" t="s">
         <v>11</v>
@@ -21975,7 +21975,7 @@
         <v>10</v>
       </c>
       <c r="F772">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G772" t="s">
         <v>11</v>
@@ -22021,7 +22021,7 @@
         <v>10</v>
       </c>
       <c r="F774">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G774" t="s">
         <v>11</v>
@@ -22044,7 +22044,7 @@
         <v>10</v>
       </c>
       <c r="F775" s="3">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G775" s="3" t="s">
         <v>11</v>
@@ -22067,7 +22067,7 @@
         <v>10</v>
       </c>
       <c r="F776">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G776" t="s">
         <v>11</v>
@@ -22136,7 +22136,7 @@
         <v>10</v>
       </c>
       <c r="F779" s="3">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G779" s="3" t="s">
         <v>11</v>
@@ -22159,7 +22159,7 @@
         <v>10</v>
       </c>
       <c r="F780">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G780" t="s">
         <v>11</v>
@@ -22182,7 +22182,7 @@
         <v>10</v>
       </c>
       <c r="F781" s="3">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G781" s="3" t="s">
         <v>11</v>
@@ -22205,7 +22205,7 @@
         <v>10</v>
       </c>
       <c r="F782">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G782" t="s">
         <v>11</v>
@@ -22228,7 +22228,7 @@
         <v>10</v>
       </c>
       <c r="F783" s="3">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G783" s="3" t="s">
         <v>11</v>
@@ -22251,7 +22251,7 @@
         <v>10</v>
       </c>
       <c r="F784">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G784" t="s">
         <v>11</v>
@@ -22274,7 +22274,7 @@
         <v>10</v>
       </c>
       <c r="F785" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G785" s="3" t="s">
         <v>11</v>
@@ -22297,7 +22297,7 @@
         <v>10</v>
       </c>
       <c r="F786">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G786" t="s">
         <v>11</v>
@@ -22320,7 +22320,7 @@
         <v>10</v>
       </c>
       <c r="F787" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G787" s="3" t="s">
         <v>11</v>
@@ -22343,7 +22343,7 @@
         <v>10</v>
       </c>
       <c r="F788">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G788" t="s">
         <v>11</v>
@@ -22366,7 +22366,7 @@
         <v>10</v>
       </c>
       <c r="F789" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G789" s="3" t="s">
         <v>11</v>
@@ -22389,7 +22389,7 @@
         <v>10</v>
       </c>
       <c r="F790">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G790" t="s">
         <v>11</v>
@@ -22412,7 +22412,7 @@
         <v>10</v>
       </c>
       <c r="F791" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G791" s="3" t="s">
         <v>11</v>
@@ -22435,7 +22435,7 @@
         <v>10</v>
       </c>
       <c r="F792">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G792" t="s">
         <v>11</v>
@@ -22458,7 +22458,7 @@
         <v>10</v>
       </c>
       <c r="F793" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G793" s="3" t="s">
         <v>11</v>
@@ -22481,7 +22481,7 @@
         <v>10</v>
       </c>
       <c r="F794">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G794" t="s">
         <v>11</v>
@@ -22527,7 +22527,7 @@
         <v>10</v>
       </c>
       <c r="F796">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G796" t="s">
         <v>11</v>
@@ -22550,7 +22550,7 @@
         <v>10</v>
       </c>
       <c r="F797" s="3">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G797" s="3" t="s">
         <v>11</v>
@@ -22573,7 +22573,7 @@
         <v>10</v>
       </c>
       <c r="F798">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G798" t="s">
         <v>11</v>
@@ -22596,7 +22596,7 @@
         <v>10</v>
       </c>
       <c r="F799" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G799" s="3" t="s">
         <v>11</v>
@@ -22619,7 +22619,7 @@
         <v>10</v>
       </c>
       <c r="F800">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G800" t="s">
         <v>11</v>
@@ -22642,7 +22642,7 @@
         <v>10</v>
       </c>
       <c r="F801" s="3">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G801" s="3" t="s">
         <v>11</v>
@@ -22665,7 +22665,7 @@
         <v>10</v>
       </c>
       <c r="F802">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G802" t="s">
         <v>11</v>
@@ -22688,7 +22688,7 @@
         <v>10</v>
       </c>
       <c r="F803" s="3">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G803" s="3" t="s">
         <v>11</v>
@@ -22711,7 +22711,7 @@
         <v>10</v>
       </c>
       <c r="F804">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G804" t="s">
         <v>11</v>
@@ -22734,7 +22734,7 @@
         <v>10</v>
       </c>
       <c r="F805" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G805" s="3" t="s">
         <v>11</v>
@@ -22757,7 +22757,7 @@
         <v>10</v>
       </c>
       <c r="F806">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G806" t="s">
         <v>11</v>
@@ -22780,7 +22780,7 @@
         <v>10</v>
       </c>
       <c r="F807" s="3">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G807" s="3" t="s">
         <v>11</v>
@@ -22803,7 +22803,7 @@
         <v>10</v>
       </c>
       <c r="F808">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G808" t="s">
         <v>11</v>
@@ -22826,7 +22826,7 @@
         <v>10</v>
       </c>
       <c r="F809" s="3">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G809" s="3" t="s">
         <v>11</v>
@@ -22849,7 +22849,7 @@
         <v>10</v>
       </c>
       <c r="F810">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G810" t="s">
         <v>11</v>
@@ -22895,7 +22895,7 @@
         <v>10</v>
       </c>
       <c r="F812">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G812" t="s">
         <v>11</v>
@@ -22918,7 +22918,7 @@
         <v>10</v>
       </c>
       <c r="F813" s="3">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G813" s="3" t="s">
         <v>11</v>
@@ -22941,7 +22941,7 @@
         <v>10</v>
       </c>
       <c r="F814">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G814" t="s">
         <v>11</v>
@@ -22964,7 +22964,7 @@
         <v>10</v>
       </c>
       <c r="F815" s="3">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G815" s="3" t="s">
         <v>11</v>
@@ -22987,7 +22987,7 @@
         <v>10</v>
       </c>
       <c r="F816">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G816" t="s">
         <v>11</v>
@@ -23010,7 +23010,7 @@
         <v>10</v>
       </c>
       <c r="F817" s="3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G817" s="3" t="s">
         <v>11</v>
@@ -23033,7 +23033,7 @@
         <v>10</v>
       </c>
       <c r="F818">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G818" t="s">
         <v>11</v>
@@ -23056,7 +23056,7 @@
         <v>10</v>
       </c>
       <c r="F819" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G819" s="3" t="s">
         <v>11</v>
@@ -23079,7 +23079,7 @@
         <v>10</v>
       </c>
       <c r="F820">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G820" t="s">
         <v>11</v>
@@ -23125,7 +23125,7 @@
         <v>10</v>
       </c>
       <c r="F822">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G822" t="s">
         <v>11</v>
@@ -23148,7 +23148,7 @@
         <v>10</v>
       </c>
       <c r="F823" s="3">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G823" s="3" t="s">
         <v>11</v>
@@ -23171,7 +23171,7 @@
         <v>10</v>
       </c>
       <c r="F824">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G824" t="s">
         <v>11</v>
@@ -23194,7 +23194,7 @@
         <v>10</v>
       </c>
       <c r="F825" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G825" s="3" t="s">
         <v>11</v>
@@ -23217,7 +23217,7 @@
         <v>10</v>
       </c>
       <c r="F826">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G826" t="s">
         <v>11</v>
@@ -23240,7 +23240,7 @@
         <v>10</v>
       </c>
       <c r="F827" s="3">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G827" s="3" t="s">
         <v>11</v>
@@ -23263,7 +23263,7 @@
         <v>10</v>
       </c>
       <c r="F828">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G828" t="s">
         <v>11</v>
@@ -23286,7 +23286,7 @@
         <v>10</v>
       </c>
       <c r="F829" s="3">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G829" s="3" t="s">
         <v>11</v>
@@ -23309,7 +23309,7 @@
         <v>10</v>
       </c>
       <c r="F830">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G830" t="s">
         <v>11</v>
@@ -23332,7 +23332,7 @@
         <v>10</v>
       </c>
       <c r="F831" s="3">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G831" s="3" t="s">
         <v>11</v>
@@ -23355,7 +23355,7 @@
         <v>10</v>
       </c>
       <c r="F832">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G832" t="s">
         <v>11</v>
@@ -23378,7 +23378,7 @@
         <v>10</v>
       </c>
       <c r="F833" s="3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G833" s="3" t="s">
         <v>11</v>
@@ -23401,7 +23401,7 @@
         <v>10</v>
       </c>
       <c r="F834">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G834" t="s">
         <v>11</v>
@@ -23447,7 +23447,7 @@
         <v>10</v>
       </c>
       <c r="F836">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G836" t="s">
         <v>11</v>
@@ -23493,7 +23493,7 @@
         <v>10</v>
       </c>
       <c r="F838">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G838" t="s">
         <v>11</v>
@@ -23516,7 +23516,7 @@
         <v>10</v>
       </c>
       <c r="F839" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G839" s="3" t="s">
         <v>11</v>
@@ -23539,7 +23539,7 @@
         <v>10</v>
       </c>
       <c r="F840">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G840" t="s">
         <v>11</v>
@@ -23562,7 +23562,7 @@
         <v>10</v>
       </c>
       <c r="F841" s="3">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G841" s="3" t="s">
         <v>11</v>
@@ -23585,7 +23585,7 @@
         <v>10</v>
       </c>
       <c r="F842">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G842" t="s">
         <v>11</v>
@@ -23608,7 +23608,7 @@
         <v>10</v>
       </c>
       <c r="F843" s="3">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G843" s="3" t="s">
         <v>11</v>
@@ -23631,7 +23631,7 @@
         <v>10</v>
       </c>
       <c r="F844">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G844" t="s">
         <v>11</v>
@@ -23654,7 +23654,7 @@
         <v>10</v>
       </c>
       <c r="F845" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G845" s="3" t="s">
         <v>11</v>
@@ -23677,7 +23677,7 @@
         <v>10</v>
       </c>
       <c r="F846">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G846" t="s">
         <v>11</v>
@@ -23700,7 +23700,7 @@
         <v>10</v>
       </c>
       <c r="F847" s="3">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G847" s="3" t="s">
         <v>11</v>
@@ -23746,7 +23746,7 @@
         <v>10</v>
       </c>
       <c r="F849" s="3">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G849" s="3" t="s">
         <v>11</v>
@@ -23769,7 +23769,7 @@
         <v>10</v>
       </c>
       <c r="F850">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G850" t="s">
         <v>11</v>
@@ -23792,7 +23792,7 @@
         <v>10</v>
       </c>
       <c r="F851" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G851" s="3" t="s">
         <v>11</v>
@@ -23815,7 +23815,7 @@
         <v>10</v>
       </c>
       <c r="F852">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G852" t="s">
         <v>11</v>
@@ -23838,7 +23838,7 @@
         <v>10</v>
       </c>
       <c r="F853" s="3">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G853" s="3" t="s">
         <v>11</v>
@@ -23861,7 +23861,7 @@
         <v>10</v>
       </c>
       <c r="F854">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G854" t="s">
         <v>11</v>
@@ -23884,7 +23884,7 @@
         <v>10</v>
       </c>
       <c r="F855" s="3">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G855" s="3" t="s">
         <v>11</v>
@@ -23930,7 +23930,7 @@
         <v>10</v>
       </c>
       <c r="F857" s="3">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G857" s="3" t="s">
         <v>11</v>
@@ -23953,7 +23953,7 @@
         <v>10</v>
       </c>
       <c r="F858">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G858" t="s">
         <v>11</v>
@@ -23976,7 +23976,7 @@
         <v>10</v>
       </c>
       <c r="F859" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G859" s="3" t="s">
         <v>11</v>
@@ -23999,7 +23999,7 @@
         <v>10</v>
       </c>
       <c r="F860">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G860" t="s">
         <v>11</v>
@@ -24022,7 +24022,7 @@
         <v>10</v>
       </c>
       <c r="F861" s="3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G861" s="3" t="s">
         <v>11</v>
@@ -24068,7 +24068,7 @@
         <v>10</v>
       </c>
       <c r="F863" s="3">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G863" s="3" t="s">
         <v>11</v>
@@ -24091,7 +24091,7 @@
         <v>10</v>
       </c>
       <c r="F864">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G864" t="s">
         <v>11</v>
@@ -24114,7 +24114,7 @@
         <v>10</v>
       </c>
       <c r="F865" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G865" s="3" t="s">
         <v>11</v>
@@ -24137,7 +24137,7 @@
         <v>10</v>
       </c>
       <c r="F866">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G866" t="s">
         <v>11</v>
@@ -24160,7 +24160,7 @@
         <v>10</v>
       </c>
       <c r="F867" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G867" s="3" t="s">
         <v>11</v>
@@ -24183,7 +24183,7 @@
         <v>10</v>
       </c>
       <c r="F868">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G868" t="s">
         <v>11</v>
@@ -24229,7 +24229,7 @@
         <v>10</v>
       </c>
       <c r="F870">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G870" t="s">
         <v>11</v>
@@ -24252,7 +24252,7 @@
         <v>10</v>
       </c>
       <c r="F871" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G871" s="3" t="s">
         <v>11</v>
@@ -24275,7 +24275,7 @@
         <v>10</v>
       </c>
       <c r="F872">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G872" t="s">
         <v>11</v>
@@ -24321,7 +24321,7 @@
         <v>10</v>
       </c>
       <c r="F874">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G874" t="s">
         <v>11</v>
@@ -24344,7 +24344,7 @@
         <v>10</v>
       </c>
       <c r="F875" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G875" s="3" t="s">
         <v>11</v>
@@ -24367,7 +24367,7 @@
         <v>10</v>
       </c>
       <c r="F876">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G876" t="s">
         <v>11</v>
@@ -24390,7 +24390,7 @@
         <v>10</v>
       </c>
       <c r="F877" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G877" s="3" t="s">
         <v>11</v>
@@ -24413,7 +24413,7 @@
         <v>10</v>
       </c>
       <c r="F878">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G878" t="s">
         <v>11</v>
@@ -24436,7 +24436,7 @@
         <v>10</v>
       </c>
       <c r="F879" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G879" s="3" t="s">
         <v>11</v>
@@ -24459,7 +24459,7 @@
         <v>10</v>
       </c>
       <c r="F880">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G880" t="s">
         <v>11</v>
@@ -24482,7 +24482,7 @@
         <v>10</v>
       </c>
       <c r="F881" s="3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G881" s="3" t="s">
         <v>11</v>
@@ -24505,7 +24505,7 @@
         <v>10</v>
       </c>
       <c r="F882">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G882" t="s">
         <v>11</v>
@@ -24528,7 +24528,7 @@
         <v>10</v>
       </c>
       <c r="F883" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G883" s="3" t="s">
         <v>11</v>
@@ -24551,7 +24551,7 @@
         <v>10</v>
       </c>
       <c r="F884">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G884" t="s">
         <v>11</v>
@@ -24574,7 +24574,7 @@
         <v>10</v>
       </c>
       <c r="F885" s="3">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G885" s="3" t="s">
         <v>11</v>
@@ -24597,7 +24597,7 @@
         <v>10</v>
       </c>
       <c r="F886">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G886" t="s">
         <v>11</v>
@@ -24643,7 +24643,7 @@
         <v>10</v>
       </c>
       <c r="F888">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G888" t="s">
         <v>11</v>
@@ -24666,7 +24666,7 @@
         <v>10</v>
       </c>
       <c r="F889" s="3">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G889" s="3" t="s">
         <v>11</v>
@@ -24689,7 +24689,7 @@
         <v>10</v>
       </c>
       <c r="F890">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G890" t="s">
         <v>11</v>
@@ -24712,7 +24712,7 @@
         <v>10</v>
       </c>
       <c r="F891" s="3">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G891" s="3" t="s">
         <v>11</v>
@@ -24735,7 +24735,7 @@
         <v>10</v>
       </c>
       <c r="F892">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G892" t="s">
         <v>11</v>
@@ -24758,7 +24758,7 @@
         <v>10</v>
       </c>
       <c r="F893" s="3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G893" s="3" t="s">
         <v>11</v>
@@ -24781,7 +24781,7 @@
         <v>10</v>
       </c>
       <c r="F894">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G894" t="s">
         <v>11</v>
@@ -24827,7 +24827,7 @@
         <v>10</v>
       </c>
       <c r="F896">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G896" t="s">
         <v>11</v>
@@ -24850,7 +24850,7 @@
         <v>10</v>
       </c>
       <c r="F897" s="3">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G897" s="3" t="s">
         <v>11</v>
@@ -24873,7 +24873,7 @@
         <v>10</v>
       </c>
       <c r="F898">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G898" t="s">
         <v>11</v>
@@ -24942,7 +24942,7 @@
         <v>10</v>
       </c>
       <c r="F901" s="3">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G901" s="3" t="s">
         <v>11</v>
@@ -24965,7 +24965,7 @@
         <v>10</v>
       </c>
       <c r="F902">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G902" t="s">
         <v>11</v>
@@ -24988,7 +24988,7 @@
         <v>10</v>
       </c>
       <c r="F903" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G903" s="3" t="s">
         <v>11</v>
@@ -25011,7 +25011,7 @@
         <v>10</v>
       </c>
       <c r="F904">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G904" t="s">
         <v>11</v>
@@ -25034,7 +25034,7 @@
         <v>10</v>
       </c>
       <c r="F905" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G905" s="3" t="s">
         <v>11</v>
@@ -25057,7 +25057,7 @@
         <v>10</v>
       </c>
       <c r="F906">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G906" t="s">
         <v>11</v>
@@ -25080,7 +25080,7 @@
         <v>10</v>
       </c>
       <c r="F907" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G907" s="3" t="s">
         <v>11</v>
@@ -25103,7 +25103,7 @@
         <v>10</v>
       </c>
       <c r="F908">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G908" t="s">
         <v>11</v>
@@ -25149,7 +25149,7 @@
         <v>10</v>
       </c>
       <c r="F910">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G910" t="s">
         <v>11</v>
@@ -25172,7 +25172,7 @@
         <v>10</v>
       </c>
       <c r="F911" s="3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G911" s="3" t="s">
         <v>11</v>
@@ -25195,7 +25195,7 @@
         <v>10</v>
       </c>
       <c r="F912">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G912" t="s">
         <v>11</v>
@@ -25218,7 +25218,7 @@
         <v>10</v>
       </c>
       <c r="F913" s="3">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G913" s="3" t="s">
         <v>11</v>
@@ -25241,7 +25241,7 @@
         <v>10</v>
       </c>
       <c r="F914">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G914" t="s">
         <v>11</v>
@@ -25264,7 +25264,7 @@
         <v>10</v>
       </c>
       <c r="F915" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G915" s="3" t="s">
         <v>11</v>
@@ -25287,7 +25287,7 @@
         <v>10</v>
       </c>
       <c r="F916">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G916" t="s">
         <v>11</v>
@@ -25310,7 +25310,7 @@
         <v>10</v>
       </c>
       <c r="F917" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G917" s="3" t="s">
         <v>11</v>
@@ -25333,7 +25333,7 @@
         <v>10</v>
       </c>
       <c r="F918">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G918" t="s">
         <v>11</v>
@@ -25356,7 +25356,7 @@
         <v>10</v>
       </c>
       <c r="F919" s="3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G919" s="3" t="s">
         <v>11</v>
@@ -25379,7 +25379,7 @@
         <v>10</v>
       </c>
       <c r="F920">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G920" t="s">
         <v>11</v>
@@ -25425,7 +25425,7 @@
         <v>10</v>
       </c>
       <c r="F922">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G922" t="s">
         <v>11</v>
@@ -25448,7 +25448,7 @@
         <v>10</v>
       </c>
       <c r="F923" s="3">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G923" s="3" t="s">
         <v>11</v>
@@ -25471,7 +25471,7 @@
         <v>10</v>
       </c>
       <c r="F924">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G924" t="s">
         <v>11</v>
@@ -25494,7 +25494,7 @@
         <v>10</v>
       </c>
       <c r="F925" s="3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G925" s="3" t="s">
         <v>11</v>
@@ -25517,7 +25517,7 @@
         <v>10</v>
       </c>
       <c r="F926">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G926" t="s">
         <v>11</v>
@@ -25540,7 +25540,7 @@
         <v>10</v>
       </c>
       <c r="F927" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G927" s="3" t="s">
         <v>11</v>
@@ -25563,7 +25563,7 @@
         <v>10</v>
       </c>
       <c r="F928">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G928" t="s">
         <v>11</v>
@@ -25586,7 +25586,7 @@
         <v>10</v>
       </c>
       <c r="F929" s="3">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G929" s="3" t="s">
         <v>11</v>
@@ -25609,7 +25609,7 @@
         <v>10</v>
       </c>
       <c r="F930">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G930" t="s">
         <v>11</v>
@@ -25655,7 +25655,7 @@
         <v>10</v>
       </c>
       <c r="F932">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G932" t="s">
         <v>11</v>
@@ -25701,7 +25701,7 @@
         <v>10</v>
       </c>
       <c r="F934">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G934" t="s">
         <v>11</v>
@@ -25724,7 +25724,7 @@
         <v>10</v>
       </c>
       <c r="F935" s="3">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G935" s="3" t="s">
         <v>11</v>
@@ -25747,7 +25747,7 @@
         <v>10</v>
       </c>
       <c r="F936">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G936" t="s">
         <v>11</v>
@@ -25770,7 +25770,7 @@
         <v>10</v>
       </c>
       <c r="F937" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G937" s="3" t="s">
         <v>11</v>
@@ -25793,7 +25793,7 @@
         <v>10</v>
       </c>
       <c r="F938">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G938" t="s">
         <v>11</v>
@@ -25816,7 +25816,7 @@
         <v>10</v>
       </c>
       <c r="F939" s="3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G939" s="3" t="s">
         <v>11</v>
@@ -25839,7 +25839,7 @@
         <v>10</v>
       </c>
       <c r="F940">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G940" t="s">
         <v>11</v>
@@ -25862,7 +25862,7 @@
         <v>10</v>
       </c>
       <c r="F941" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G941" s="3" t="s">
         <v>11</v>
@@ -25885,7 +25885,7 @@
         <v>10</v>
       </c>
       <c r="F942">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G942" t="s">
         <v>11</v>
@@ -25908,7 +25908,7 @@
         <v>10</v>
       </c>
       <c r="F943" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G943" s="3" t="s">
         <v>11</v>
@@ -25931,7 +25931,7 @@
         <v>10</v>
       </c>
       <c r="F944">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G944" t="s">
         <v>11</v>
@@ -25954,7 +25954,7 @@
         <v>10</v>
       </c>
       <c r="F945" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G945" s="3" t="s">
         <v>11</v>
@@ -25977,7 +25977,7 @@
         <v>10</v>
       </c>
       <c r="F946">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G946" t="s">
         <v>11</v>
@@ -26000,7 +26000,7 @@
         <v>10</v>
       </c>
       <c r="F947" s="3">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G947" s="3" t="s">
         <v>11</v>
@@ -26023,7 +26023,7 @@
         <v>10</v>
       </c>
       <c r="F948">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G948" t="s">
         <v>11</v>
@@ -26046,7 +26046,7 @@
         <v>10</v>
       </c>
       <c r="F949" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G949" s="3" t="s">
         <v>11</v>
@@ -26069,7 +26069,7 @@
         <v>10</v>
       </c>
       <c r="F950">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G950" t="s">
         <v>11</v>
@@ -26115,7 +26115,7 @@
         <v>10</v>
       </c>
       <c r="F952">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G952" t="s">
         <v>11</v>
@@ -26138,7 +26138,7 @@
         <v>10</v>
       </c>
       <c r="F953" s="3">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G953" s="3" t="s">
         <v>11</v>
@@ -26161,7 +26161,7 @@
         <v>10</v>
       </c>
       <c r="F954">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G954" t="s">
         <v>11</v>
@@ -26184,7 +26184,7 @@
         <v>10</v>
       </c>
       <c r="F955" s="3">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G955" s="3" t="s">
         <v>11</v>
@@ -26207,7 +26207,7 @@
         <v>10</v>
       </c>
       <c r="F956">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G956" t="s">
         <v>11</v>
@@ -26253,7 +26253,7 @@
         <v>10</v>
       </c>
       <c r="F958">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G958" t="s">
         <v>11</v>
@@ -26276,7 +26276,7 @@
         <v>10</v>
       </c>
       <c r="F959" s="3">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G959" s="3" t="s">
         <v>11</v>
@@ -26299,7 +26299,7 @@
         <v>10</v>
       </c>
       <c r="F960">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G960" t="s">
         <v>11</v>
@@ -26322,7 +26322,7 @@
         <v>10</v>
       </c>
       <c r="F961" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G961" s="3" t="s">
         <v>11</v>
@@ -26345,7 +26345,7 @@
         <v>10</v>
       </c>
       <c r="F962">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G962" t="s">
         <v>11</v>
@@ -26368,7 +26368,7 @@
         <v>10</v>
       </c>
       <c r="F963" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G963" s="3" t="s">
         <v>11</v>
@@ -26391,7 +26391,7 @@
         <v>10</v>
       </c>
       <c r="F964">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G964" t="s">
         <v>11</v>
@@ -26414,7 +26414,7 @@
         <v>10</v>
       </c>
       <c r="F965" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G965" s="3" t="s">
         <v>11</v>
@@ -26437,7 +26437,7 @@
         <v>10</v>
       </c>
       <c r="F966">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G966" t="s">
         <v>11</v>
@@ -26460,7 +26460,7 @@
         <v>10</v>
       </c>
       <c r="F967" s="3">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G967" s="3" t="s">
         <v>11</v>
@@ -26483,7 +26483,7 @@
         <v>10</v>
       </c>
       <c r="F968">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G968" t="s">
         <v>11</v>
@@ -26506,7 +26506,7 @@
         <v>10</v>
       </c>
       <c r="F969" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G969" s="3" t="s">
         <v>11</v>
@@ -26529,7 +26529,7 @@
         <v>10</v>
       </c>
       <c r="F970">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G970" t="s">
         <v>11</v>
@@ -26552,7 +26552,7 @@
         <v>10</v>
       </c>
       <c r="F971" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G971" s="3" t="s">
         <v>11</v>
@@ -26575,7 +26575,7 @@
         <v>10</v>
       </c>
       <c r="F972">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G972" t="s">
         <v>11</v>
@@ -26598,7 +26598,7 @@
         <v>10</v>
       </c>
       <c r="F973" s="3">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G973" s="3" t="s">
         <v>11</v>
@@ -26644,7 +26644,7 @@
         <v>10</v>
       </c>
       <c r="F975" s="3">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G975" s="3" t="s">
         <v>11</v>
@@ -26667,7 +26667,7 @@
         <v>10</v>
       </c>
       <c r="F976">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G976" t="s">
         <v>11</v>
@@ -26690,7 +26690,7 @@
         <v>10</v>
       </c>
       <c r="F977" s="3">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G977" s="3" t="s">
         <v>11</v>
@@ -26713,7 +26713,7 @@
         <v>10</v>
       </c>
       <c r="F978">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G978" t="s">
         <v>11</v>
@@ -26736,7 +26736,7 @@
         <v>10</v>
       </c>
       <c r="F979" s="3">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G979" s="3" t="s">
         <v>11</v>
@@ -26759,7 +26759,7 @@
         <v>10</v>
       </c>
       <c r="F980">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G980" t="s">
         <v>11</v>
@@ -26782,7 +26782,7 @@
         <v>10</v>
       </c>
       <c r="F981" s="3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G981" s="3" t="s">
         <v>11</v>
@@ -26805,7 +26805,7 @@
         <v>10</v>
       </c>
       <c r="F982">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G982" t="s">
         <v>11</v>
@@ -26828,7 +26828,7 @@
         <v>10</v>
       </c>
       <c r="F983" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G983" s="3" t="s">
         <v>11</v>
@@ -26874,7 +26874,7 @@
         <v>10</v>
       </c>
       <c r="F985" s="3">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G985" s="3" t="s">
         <v>11</v>
@@ -26897,7 +26897,7 @@
         <v>10</v>
       </c>
       <c r="F986">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G986" t="s">
         <v>11</v>
@@ -26920,7 +26920,7 @@
         <v>10</v>
       </c>
       <c r="F987" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G987" s="3" t="s">
         <v>11</v>
@@ -26943,7 +26943,7 @@
         <v>10</v>
       </c>
       <c r="F988">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G988" t="s">
         <v>11</v>
@@ -26966,7 +26966,7 @@
         <v>10</v>
       </c>
       <c r="F989" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G989" s="3" t="s">
         <v>11</v>
@@ -26989,7 +26989,7 @@
         <v>10</v>
       </c>
       <c r="F990">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G990" t="s">
         <v>11</v>
@@ -27012,7 +27012,7 @@
         <v>10</v>
       </c>
       <c r="F991" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G991" s="3" t="s">
         <v>11</v>
@@ -27035,7 +27035,7 @@
         <v>10</v>
       </c>
       <c r="F992">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G992" t="s">
         <v>11</v>
@@ -27058,7 +27058,7 @@
         <v>10</v>
       </c>
       <c r="F993" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G993" s="3" t="s">
         <v>11</v>
@@ -27127,7 +27127,7 @@
         <v>10</v>
       </c>
       <c r="F996">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G996" t="s">
         <v>11</v>
@@ -27150,7 +27150,7 @@
         <v>10</v>
       </c>
       <c r="F997" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G997" s="3" t="s">
         <v>11</v>
@@ -27173,7 +27173,7 @@
         <v>10</v>
       </c>
       <c r="F998">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G998" t="s">
         <v>11</v>
@@ -27196,7 +27196,7 @@
         <v>10</v>
       </c>
       <c r="F999" s="3">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G999" s="3" t="s">
         <v>11</v>
@@ -27219,7 +27219,7 @@
         <v>10</v>
       </c>
       <c r="F1000">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G1000" t="s">
         <v>11</v>
@@ -27242,7 +27242,7 @@
         <v>10</v>
       </c>
       <c r="F1001" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G1001" s="3" t="s">
         <v>11</v>
@@ -27265,7 +27265,7 @@
         <v>10</v>
       </c>
       <c r="F1002">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G1002" t="s">
         <v>11</v>
@@ -27288,7 +27288,7 @@
         <v>10</v>
       </c>
       <c r="F1003" s="3">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G1003" s="3" t="s">
         <v>11</v>
@@ -27311,7 +27311,7 @@
         <v>10</v>
       </c>
       <c r="F1004">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G1004" t="s">
         <v>11</v>
@@ -27334,7 +27334,7 @@
         <v>10</v>
       </c>
       <c r="F1005" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1005" s="3" t="s">
         <v>11</v>
@@ -27357,7 +27357,7 @@
         <v>10</v>
       </c>
       <c r="F1006">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G1006" t="s">
         <v>11</v>
@@ -27380,7 +27380,7 @@
         <v>10</v>
       </c>
       <c r="F1007" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G1007" s="3" t="s">
         <v>11</v>
@@ -27403,7 +27403,7 @@
         <v>10</v>
       </c>
       <c r="F1008">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G1008" t="s">
         <v>11</v>
@@ -27426,7 +27426,7 @@
         <v>10</v>
       </c>
       <c r="F1009" s="3">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G1009" s="3" t="s">
         <v>11</v>
@@ -27449,7 +27449,7 @@
         <v>10</v>
       </c>
       <c r="F1010">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G1010" t="s">
         <v>11</v>
@@ -27472,7 +27472,7 @@
         <v>10</v>
       </c>
       <c r="F1011" s="3">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G1011" s="3" t="s">
         <v>11</v>
@@ -27541,7 +27541,7 @@
         <v>10</v>
       </c>
       <c r="F1014">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G1014" t="s">
         <v>11</v>
@@ -27564,7 +27564,7 @@
         <v>10</v>
       </c>
       <c r="F1015" s="3">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G1015" s="3" t="s">
         <v>11</v>
@@ -27587,7 +27587,7 @@
         <v>10</v>
       </c>
       <c r="F1016">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G1016" t="s">
         <v>11</v>
@@ -27610,7 +27610,7 @@
         <v>10</v>
       </c>
       <c r="F1017" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G1017" s="3" t="s">
         <v>11</v>
@@ -27633,7 +27633,7 @@
         <v>10</v>
       </c>
       <c r="F1018">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G1018" t="s">
         <v>11</v>
@@ -27656,7 +27656,7 @@
         <v>10</v>
       </c>
       <c r="F1019" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G1019" s="3" t="s">
         <v>11</v>
@@ -27702,7 +27702,7 @@
         <v>10</v>
       </c>
       <c r="F1021" s="3">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G1021" s="3" t="s">
         <v>11</v>
@@ -27725,7 +27725,7 @@
         <v>10</v>
       </c>
       <c r="F1022">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G1022" t="s">
         <v>11</v>
@@ -27748,7 +27748,7 @@
         <v>10</v>
       </c>
       <c r="F1023" s="3">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G1023" s="3" t="s">
         <v>11</v>
@@ -27771,7 +27771,7 @@
         <v>10</v>
       </c>
       <c r="F1024">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G1024" t="s">
         <v>11</v>
@@ -27794,7 +27794,7 @@
         <v>10</v>
       </c>
       <c r="F1025" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G1025" s="3" t="s">
         <v>11</v>
@@ -27840,7 +27840,7 @@
         <v>10</v>
       </c>
       <c r="F1027" s="3">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G1027" s="3" t="s">
         <v>11</v>
@@ -27863,7 +27863,7 @@
         <v>10</v>
       </c>
       <c r="F1028">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1028" t="s">
         <v>11</v>
@@ -27886,7 +27886,7 @@
         <v>10</v>
       </c>
       <c r="F1029" s="3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G1029" s="3" t="s">
         <v>11</v>
@@ -27909,7 +27909,7 @@
         <v>10</v>
       </c>
       <c r="F1030">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G1030" t="s">
         <v>11</v>
@@ -27932,7 +27932,7 @@
         <v>10</v>
       </c>
       <c r="F1031" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G1031" s="3" t="s">
         <v>11</v>
@@ -27955,7 +27955,7 @@
         <v>10</v>
       </c>
       <c r="F1032">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1032" t="s">
         <v>11</v>
@@ -27978,7 +27978,7 @@
         <v>10</v>
       </c>
       <c r="F1033" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G1033" s="3" t="s">
         <v>11</v>
@@ -28001,7 +28001,7 @@
         <v>10</v>
       </c>
       <c r="F1034">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G1034" t="s">
         <v>11</v>
@@ -28024,7 +28024,7 @@
         <v>10</v>
       </c>
       <c r="F1035" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G1035" s="3" t="s">
         <v>11</v>
@@ -28047,7 +28047,7 @@
         <v>10</v>
       </c>
       <c r="F1036">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G1036" t="s">
         <v>11</v>
@@ -28070,7 +28070,7 @@
         <v>10</v>
       </c>
       <c r="F1037" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G1037" s="3" t="s">
         <v>11</v>
@@ -28116,7 +28116,7 @@
         <v>10</v>
       </c>
       <c r="F1039" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G1039" s="3" t="s">
         <v>11</v>
@@ -28139,7 +28139,7 @@
         <v>10</v>
       </c>
       <c r="F1040">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G1040" t="s">
         <v>11</v>
@@ -28162,7 +28162,7 @@
         <v>10</v>
       </c>
       <c r="F1041" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1041" s="3" t="s">
         <v>11</v>
@@ -28208,7 +28208,7 @@
         <v>10</v>
       </c>
       <c r="F1043" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G1043" s="3" t="s">
         <v>11</v>
@@ -28231,7 +28231,7 @@
         <v>10</v>
       </c>
       <c r="F1044">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G1044" t="s">
         <v>11</v>
@@ -28254,7 +28254,7 @@
         <v>10</v>
       </c>
       <c r="F1045" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G1045" s="3" t="s">
         <v>11</v>
@@ -28277,7 +28277,7 @@
         <v>10</v>
       </c>
       <c r="F1046">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G1046" t="s">
         <v>11</v>
@@ -28323,7 +28323,7 @@
         <v>10</v>
       </c>
       <c r="F1048">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1048" t="s">
         <v>11</v>
@@ -28346,7 +28346,7 @@
         <v>10</v>
       </c>
       <c r="F1049" s="3">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G1049" s="3" t="s">
         <v>11</v>
@@ -28369,7 +28369,7 @@
         <v>10</v>
       </c>
       <c r="F1050">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G1050" t="s">
         <v>11</v>
@@ -28392,7 +28392,7 @@
         <v>10</v>
       </c>
       <c r="F1051" s="3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G1051" s="3" t="s">
         <v>11</v>
@@ -28415,7 +28415,7 @@
         <v>10</v>
       </c>
       <c r="F1052">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G1052" t="s">
         <v>11</v>
@@ -28438,7 +28438,7 @@
         <v>10</v>
       </c>
       <c r="F1053" s="3">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G1053" s="3" t="s">
         <v>11</v>
@@ -28461,7 +28461,7 @@
         <v>10</v>
       </c>
       <c r="F1054">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G1054" t="s">
         <v>11</v>
@@ -28484,7 +28484,7 @@
         <v>10</v>
       </c>
       <c r="F1055" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G1055" s="3" t="s">
         <v>11</v>
@@ -28507,7 +28507,7 @@
         <v>10</v>
       </c>
       <c r="F1056">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G1056" t="s">
         <v>11</v>
@@ -28530,7 +28530,7 @@
         <v>10</v>
       </c>
       <c r="F1057" s="3">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G1057" s="3" t="s">
         <v>11</v>
@@ -28553,7 +28553,7 @@
         <v>10</v>
       </c>
       <c r="F1058">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G1058" t="s">
         <v>11</v>
@@ -28576,7 +28576,7 @@
         <v>10</v>
       </c>
       <c r="F1059" s="3">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G1059" s="3" t="s">
         <v>11</v>
@@ -28599,7 +28599,7 @@
         <v>10</v>
       </c>
       <c r="F1060">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G1060" t="s">
         <v>11</v>
@@ -28622,7 +28622,7 @@
         <v>10</v>
       </c>
       <c r="F1061" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G1061" s="3" t="s">
         <v>11</v>
@@ -28645,7 +28645,7 @@
         <v>10</v>
       </c>
       <c r="F1062">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G1062" t="s">
         <v>11</v>
@@ -28668,7 +28668,7 @@
         <v>10</v>
       </c>
       <c r="F1063" s="3">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G1063" s="3" t="s">
         <v>11</v>
@@ -28691,7 +28691,7 @@
         <v>10</v>
       </c>
       <c r="F1064">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G1064" t="s">
         <v>11</v>
@@ -28714,7 +28714,7 @@
         <v>10</v>
       </c>
       <c r="F1065" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G1065" s="3" t="s">
         <v>11</v>
@@ -28760,7 +28760,7 @@
         <v>10</v>
       </c>
       <c r="F1067" s="3">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G1067" s="3" t="s">
         <v>11</v>
@@ -28783,7 +28783,7 @@
         <v>10</v>
       </c>
       <c r="F1068">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G1068" t="s">
         <v>11</v>
@@ -28806,7 +28806,7 @@
         <v>10</v>
       </c>
       <c r="F1069" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G1069" s="3" t="s">
         <v>11</v>
@@ -28829,7 +28829,7 @@
         <v>10</v>
       </c>
       <c r="F1070">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G1070" t="s">
         <v>11</v>
@@ -28852,7 +28852,7 @@
         <v>10</v>
       </c>
       <c r="F1071" s="3">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G1071" s="3" t="s">
         <v>11</v>
@@ -28875,7 +28875,7 @@
         <v>10</v>
       </c>
       <c r="F1072">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G1072" t="s">
         <v>11</v>
@@ -28898,7 +28898,7 @@
         <v>10</v>
       </c>
       <c r="F1073" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G1073" s="3" t="s">
         <v>11</v>
@@ -28921,7 +28921,7 @@
         <v>10</v>
       </c>
       <c r="F1074">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1074" t="s">
         <v>11</v>
@@ -28944,7 +28944,7 @@
         <v>10</v>
       </c>
       <c r="F1075" s="3">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G1075" s="3" t="s">
         <v>11</v>
@@ -28967,7 +28967,7 @@
         <v>10</v>
       </c>
       <c r="F1076">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G1076" t="s">
         <v>11</v>
@@ -28990,7 +28990,7 @@
         <v>10</v>
       </c>
       <c r="F1077" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1077" s="3" t="s">
         <v>11</v>
@@ -29013,7 +29013,7 @@
         <v>10</v>
       </c>
       <c r="F1078">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G1078" t="s">
         <v>11</v>
@@ -29036,7 +29036,7 @@
         <v>10</v>
       </c>
       <c r="F1079" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1079" s="3" t="s">
         <v>11</v>
@@ -29059,7 +29059,7 @@
         <v>10</v>
       </c>
       <c r="F1080">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G1080" t="s">
         <v>11</v>
@@ -29082,7 +29082,7 @@
         <v>10</v>
       </c>
       <c r="F1081" s="3">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G1081" s="3" t="s">
         <v>11</v>
@@ -29128,7 +29128,7 @@
         <v>10</v>
       </c>
       <c r="F1083" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G1083" s="3" t="s">
         <v>11</v>
@@ -29174,7 +29174,7 @@
         <v>10</v>
       </c>
       <c r="F1085" s="3">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G1085" s="3" t="s">
         <v>11</v>
@@ -29197,7 +29197,7 @@
         <v>10</v>
       </c>
       <c r="F1086">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G1086" t="s">
         <v>11</v>
@@ -29220,7 +29220,7 @@
         <v>10</v>
       </c>
       <c r="F1087" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G1087" s="3" t="s">
         <v>11</v>
@@ -29243,7 +29243,7 @@
         <v>10</v>
       </c>
       <c r="F1088">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G1088" t="s">
         <v>11</v>
@@ -29266,7 +29266,7 @@
         <v>10</v>
       </c>
       <c r="F1089" s="3">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G1089" s="3" t="s">
         <v>11</v>
@@ -29335,7 +29335,7 @@
         <v>10</v>
       </c>
       <c r="F1092">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G1092" t="s">
         <v>11</v>
@@ -29358,7 +29358,7 @@
         <v>10</v>
       </c>
       <c r="F1093" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G1093" s="3" t="s">
         <v>11</v>
@@ -29381,7 +29381,7 @@
         <v>10</v>
       </c>
       <c r="F1094">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G1094" t="s">
         <v>11</v>
@@ -29404,7 +29404,7 @@
         <v>10</v>
       </c>
       <c r="F1095" s="3">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G1095" s="3" t="s">
         <v>11</v>
@@ -29427,7 +29427,7 @@
         <v>10</v>
       </c>
       <c r="F1096">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G1096" t="s">
         <v>11</v>
@@ -29450,7 +29450,7 @@
         <v>10</v>
       </c>
       <c r="F1097" s="3">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G1097" s="3" t="s">
         <v>11</v>
@@ -29473,7 +29473,7 @@
         <v>10</v>
       </c>
       <c r="F1098">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G1098" t="s">
         <v>11</v>
@@ -29496,7 +29496,7 @@
         <v>10</v>
       </c>
       <c r="F1099" s="3">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G1099" s="3" t="s">
         <v>11</v>
@@ -29519,7 +29519,7 @@
         <v>10</v>
       </c>
       <c r="F1100">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G1100" t="s">
         <v>11</v>
@@ -29542,7 +29542,7 @@
         <v>10</v>
       </c>
       <c r="F1101" s="3">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G1101" s="3" t="s">
         <v>11</v>
